--- a/excel-template/PO-template.xlsx
+++ b/excel-template/PO-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\exportcrm\excel-template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C20080F4-20A9-4DD5-AB4F-F7A7B854281D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8A17243-928F-4647-BAD1-F437845C793E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="813" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <definedName name="Excel_BuiltIn_Print_Titles_1_1">#REF!</definedName>
     <definedName name="LISCO_LIMITED_UNIT_1603__16_F.__YEN_SHENG_CENTRE__64_HOI_YUEN_ROAD__KWUN_TONG__KOWLOON__HONG_KONG">#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">contract!$A$1:$G$57</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">PO!$A$1:$I$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">PO!$A$1:$I$25</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="77">
   <si>
     <t>VAT 91500109MADTT20C92</t>
   </si>
@@ -93,30 +93,6 @@
   </si>
   <si>
     <t>Material must be palletized</t>
-  </si>
-  <si>
-    <t>China Office</t>
-  </si>
-  <si>
-    <t>Spain Office</t>
-  </si>
-  <si>
-    <t>No.194,Jiarui Avenue,Beibei District, 400707 Chongqing, China</t>
-  </si>
-  <si>
-    <t>Valencia 264 Principal, 08007 Barcelona, Spain</t>
-  </si>
-  <si>
-    <t>Tel: +86 15923354664</t>
-  </si>
-  <si>
-    <t>Tel: (+34) 607630594</t>
-  </si>
-  <si>
-    <t>Email: z.zela@alustars.com</t>
-  </si>
-  <si>
-    <t>Email: c.feliu@alustars.com</t>
   </si>
   <si>
     <t>SALES CONTRACT</t>
@@ -293,18 +269,6 @@
     <phoneticPr fontId="26" type="noConversion"/>
   </si>
   <si>
-    <t>PO-A2604-001</t>
-    <phoneticPr fontId="26" type="noConversion"/>
-  </si>
-  <si>
-    <t>0080-2062-0843</t>
-    <phoneticPr fontId="26" type="noConversion"/>
-  </si>
-  <si>
-    <t>PILOT LIGHT TORCH TUBE</t>
-    <phoneticPr fontId="26" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -338,19 +302,6 @@
         <charset val="134"/>
       </rPr>
       <t>日期：</t>
-    </r>
-    <phoneticPr fontId="26" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="DengXian"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>维君康（深圳）科技有限公司</t>
     </r>
     <phoneticPr fontId="26" type="noConversion"/>
   </si>
@@ -462,30 +413,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="10"/>
-        <rFont val="DengXian"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>点火器外壳</t>
-    </r>
-    <phoneticPr fontId="26" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="DengXian"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>个</t>
-    </r>
-    <phoneticPr fontId="26" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
         <b/>
         <sz val="12"/>
         <rFont val="DengXian"/>
@@ -493,115 +420,6 @@
         <charset val="134"/>
       </rPr>
       <t>备注：</t>
-    </r>
-    <phoneticPr fontId="26" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="DengXian"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>交货期：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="DengXian"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>第一批</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>500</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="DengXian"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>套，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>2026.4.25</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="DengXian"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>交付。第二批</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>500</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="DengXian"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>套，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>2026.5.15</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="DengXian"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>交付。</t>
-    </r>
-    <phoneticPr fontId="26" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="DengXian"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>供应商需严格执行买卖双方已签署的通用《金属加工件采购协议（精简执行版）》及《金属加工件质量协议（精简执行版）》之规定。</t>
     </r>
     <phoneticPr fontId="26" type="noConversion"/>
   </si>
@@ -646,31 +464,11 @@
     <phoneticPr fontId="26" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="DengXian"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>以上单价不含税，开票时付税金。</t>
-    </r>
+    <t>供应商：</t>
     <phoneticPr fontId="26" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="DengXian"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>支付方式：发货前支付全款。</t>
-    </r>
-    <phoneticPr fontId="26" type="noConversion"/>
-  </si>
-  <si>
-    <t>供应商：</t>
+    <t>以上单价不含税，开票时付税金。</t>
     <phoneticPr fontId="26" type="noConversion"/>
   </si>
 </sst>
@@ -928,7 +726,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -1096,24 +894,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="2" tint="-9.985656300546282E-2"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1339,18 +1119,6 @@
     <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="14" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="14" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1393,10 +1161,6 @@
     <xf numFmtId="181" fontId="14" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1440,9 +1204,6 @@
     <xf numFmtId="43" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="14" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1479,9 +1240,6 @@
     <xf numFmtId="43" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="43" fontId="14" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="3" fontId="16" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1521,6 +1279,9 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1611,6 +1372,23 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="14" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="43" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1980,117 +1758,115 @@
   <sheetData>
     <row r="1" spans="1:20" s="55" customFormat="1" ht="66" customHeight="1">
       <c r="A1" s="68" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="B1" s="68"/>
       <c r="C1" s="68"/>
       <c r="D1" s="68"/>
       <c r="E1" s="68"/>
       <c r="F1" s="68"/>
-      <c r="G1" s="125" t="s">
-        <v>88</v>
-      </c>
-      <c r="H1" s="125"/>
-      <c r="I1" s="125"/>
-      <c r="O1" s="96"/>
-      <c r="P1" s="96"/>
+      <c r="G1" s="117" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="O1" s="90"/>
+      <c r="P1" s="90"/>
     </row>
     <row r="2" spans="1:20" ht="26.25" customHeight="1">
       <c r="A2" s="69" t="s">
         <v>0</v>
       </c>
-      <c r="H2" s="126" t="s">
-        <v>70</v>
-      </c>
-      <c r="I2" s="126"/>
-    </row>
-    <row r="3" spans="1:20" s="56" customFormat="1" ht="21.75" customHeight="1" thickBot="1">
-      <c r="A3" s="70" t="s">
+      <c r="H2" s="118" t="s">
+        <v>59</v>
+      </c>
+      <c r="I2" s="118"/>
+    </row>
+    <row r="3" spans="1:20" s="56" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A3" s="155" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="71"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="118" t="s">
-        <v>75</v>
-      </c>
-      <c r="I3" s="105">
-        <v>46134</v>
-      </c>
-      <c r="O3" s="75"/>
-      <c r="P3" s="75"/>
+      <c r="B3" s="156"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="108" t="s">
+        <v>64</v>
+      </c>
+      <c r="I3" s="157" t="s">
+        <v>59</v>
+      </c>
+      <c r="O3" s="71"/>
+      <c r="P3" s="71"/>
     </row>
     <row r="4" spans="1:20" s="56" customFormat="1" ht="21.75" customHeight="1">
       <c r="A4" s="69"/>
-      <c r="B4" s="74"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="K4" s="82"/>
-      <c r="L4" s="78"/>
-      <c r="M4" s="82"/>
+      <c r="B4" s="70"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
+      <c r="K4" s="78"/>
+      <c r="L4" s="74"/>
+      <c r="M4" s="78"/>
       <c r="N4" s="57"/>
-      <c r="O4" s="81"/>
-      <c r="P4" s="81"/>
-      <c r="Q4" s="81"/>
-      <c r="R4" s="81"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="77"/>
+      <c r="Q4" s="77"/>
+      <c r="R4" s="77"/>
     </row>
     <row r="5" spans="1:20" s="57" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A5" s="122" t="s">
-        <v>93</v>
-      </c>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="79"/>
+      <c r="A5" s="114" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="75"/>
       <c r="K5" s="61"/>
       <c r="L5" s="61"/>
       <c r="M5" s="61"/>
       <c r="N5" s="61"/>
       <c r="O5" s="61"/>
       <c r="P5" s="61"/>
-      <c r="Q5" s="97"/>
+      <c r="Q5" s="91"/>
       <c r="R5" s="61"/>
       <c r="S5" s="61"/>
     </row>
     <row r="6" spans="1:20" s="57" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A6" s="80" t="s">
-        <v>76</v>
-      </c>
-      <c r="F6" s="106"/>
-      <c r="G6" s="106"/>
-      <c r="H6" s="106"/>
-      <c r="I6" s="106"/>
-      <c r="J6" s="81"/>
-      <c r="K6" s="98"/>
-      <c r="L6" s="81"/>
-      <c r="M6" s="98"/>
-      <c r="N6" s="81"/>
-      <c r="O6" s="98"/>
-      <c r="P6" s="81"/>
-      <c r="Q6" s="99"/>
-      <c r="R6" s="100"/>
-      <c r="S6" s="98"/>
+      <c r="A6" s="76"/>
+      <c r="F6" s="99"/>
+      <c r="G6" s="99"/>
+      <c r="H6" s="99"/>
+      <c r="I6" s="99"/>
+      <c r="J6" s="77"/>
+      <c r="K6" s="92"/>
+      <c r="L6" s="77"/>
+      <c r="M6" s="92"/>
+      <c r="N6" s="77"/>
+      <c r="O6" s="92"/>
+      <c r="P6" s="77"/>
+      <c r="Q6" s="93"/>
+      <c r="R6" s="94"/>
+      <c r="S6" s="92"/>
     </row>
     <row r="7" spans="1:20" s="57" customFormat="1" ht="24" customHeight="1">
-      <c r="A7" s="83"/>
-      <c r="B7" s="84"/>
-      <c r="C7" s="85"/>
-      <c r="D7" s="85"/>
-      <c r="E7" s="85"/>
-      <c r="F7" s="106"/>
-      <c r="G7" s="106"/>
-      <c r="H7" s="106"/>
-      <c r="I7" s="106"/>
-      <c r="J7" s="81"/>
-      <c r="K7" s="81"/>
-      <c r="L7" s="81"/>
+      <c r="A7" s="79"/>
+      <c r="B7" s="80"/>
+      <c r="C7" s="81"/>
+      <c r="D7" s="81"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="99"/>
+      <c r="G7" s="99"/>
+      <c r="H7" s="99"/>
+      <c r="I7" s="99"/>
+      <c r="J7" s="77"/>
+      <c r="K7" s="77"/>
+      <c r="L7" s="77"/>
       <c r="M7" s="56"/>
       <c r="N7" s="60"/>
       <c r="O7" s="60"/>
@@ -2101,158 +1877,141 @@
       <c r="T7" s="58"/>
     </row>
     <row r="8" spans="1:20" s="59" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A8" s="107" t="s">
+      <c r="A8" s="100" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="119" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" s="120"/>
+      <c r="D8" s="82" t="s">
+        <v>65</v>
+      </c>
+      <c r="E8" s="82" t="s">
+        <v>66</v>
+      </c>
+      <c r="F8" s="82" t="s">
+        <v>67</v>
+      </c>
+      <c r="G8" s="82" t="s">
         <v>68</v>
       </c>
-      <c r="B8" s="127" t="s">
+      <c r="H8" s="82" t="s">
         <v>69</v>
       </c>
-      <c r="C8" s="128"/>
-      <c r="D8" s="86" t="s">
-        <v>77</v>
-      </c>
-      <c r="E8" s="86" t="s">
-        <v>78</v>
-      </c>
-      <c r="F8" s="86" t="s">
-        <v>79</v>
-      </c>
-      <c r="G8" s="86" t="s">
-        <v>80</v>
-      </c>
-      <c r="H8" s="86" t="s">
-        <v>81</v>
-      </c>
-      <c r="I8" s="86" t="s">
-        <v>82</v>
-      </c>
-      <c r="M8" s="123"/>
-      <c r="N8" s="123"/>
-      <c r="O8" s="123"/>
-      <c r="P8" s="123"/>
-      <c r="Q8" s="123"/>
-      <c r="R8" s="123"/>
-      <c r="S8" s="123"/>
-      <c r="T8" s="123"/>
+      <c r="I8" s="82" t="s">
+        <v>70</v>
+      </c>
+      <c r="M8" s="115"/>
+      <c r="N8" s="115"/>
+      <c r="O8" s="115"/>
+      <c r="P8" s="115"/>
+      <c r="Q8" s="115"/>
+      <c r="R8" s="115"/>
+      <c r="S8" s="115"/>
+      <c r="T8" s="115"/>
     </row>
     <row r="9" spans="1:20" s="58" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A9" s="108">
-        <v>1</v>
-      </c>
-      <c r="B9" s="124" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" s="124"/>
-      <c r="D9" s="108" t="s">
-        <v>72</v>
-      </c>
-      <c r="E9" s="108" t="s">
-        <v>83</v>
-      </c>
-      <c r="F9" s="110">
-        <v>250</v>
-      </c>
-      <c r="G9" s="110" t="s">
-        <v>84</v>
-      </c>
-      <c r="H9" s="111">
-        <v>80</v>
-      </c>
-      <c r="I9" s="111">
-        <f>H9*F9</f>
-        <v>20000</v>
-      </c>
-      <c r="L9" s="101"/>
+      <c r="A9" s="101"/>
+      <c r="B9" s="116"/>
+      <c r="C9" s="116"/>
+      <c r="D9" s="101"/>
+      <c r="E9" s="101"/>
+      <c r="F9" s="103"/>
+      <c r="G9" s="103"/>
+      <c r="H9" s="104"/>
+      <c r="I9" s="104"/>
+      <c r="L9" s="95"/>
       <c r="O9" s="60"/>
       <c r="P9" s="60"/>
-      <c r="Q9" s="102"/>
-      <c r="R9" s="102"/>
+      <c r="Q9" s="96"/>
+      <c r="R9" s="96"/>
     </row>
     <row r="10" spans="1:20" s="58" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A10" s="108"/>
-      <c r="B10" s="124"/>
-      <c r="C10" s="124"/>
-      <c r="D10" s="108"/>
-      <c r="E10" s="108"/>
-      <c r="F10" s="110"/>
-      <c r="G10" s="110"/>
-      <c r="H10" s="111"/>
-      <c r="I10" s="111"/>
-      <c r="L10" s="101"/>
+      <c r="A10" s="101"/>
+      <c r="B10" s="116"/>
+      <c r="C10" s="116"/>
+      <c r="D10" s="101"/>
+      <c r="E10" s="101"/>
+      <c r="F10" s="103"/>
+      <c r="G10" s="103"/>
+      <c r="H10" s="104"/>
+      <c r="I10" s="104"/>
+      <c r="L10" s="95"/>
       <c r="O10" s="60"/>
       <c r="P10" s="60"/>
-      <c r="Q10" s="102"/>
-      <c r="R10" s="102"/>
+      <c r="Q10" s="96"/>
+      <c r="R10" s="96"/>
     </row>
     <row r="11" spans="1:20" s="58" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A11" s="108"/>
-      <c r="B11" s="124"/>
-      <c r="C11" s="124"/>
-      <c r="D11" s="114"/>
-      <c r="E11" s="108"/>
-      <c r="F11" s="110"/>
-      <c r="G11" s="110"/>
-      <c r="H11" s="111"/>
-      <c r="I11" s="111"/>
-      <c r="L11" s="101"/>
+      <c r="A11" s="101"/>
+      <c r="B11" s="116"/>
+      <c r="C11" s="116"/>
+      <c r="D11" s="107"/>
+      <c r="E11" s="101"/>
+      <c r="F11" s="103"/>
+      <c r="G11" s="103"/>
+      <c r="H11" s="104"/>
+      <c r="I11" s="104"/>
+      <c r="L11" s="95"/>
       <c r="O11" s="60"/>
       <c r="P11" s="60"/>
-      <c r="Q11" s="102"/>
-      <c r="R11" s="102"/>
+      <c r="Q11" s="96"/>
+      <c r="R11" s="96"/>
     </row>
     <row r="12" spans="1:20" s="58" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A12" s="108"/>
-      <c r="B12" s="124"/>
-      <c r="C12" s="124"/>
-      <c r="D12" s="114"/>
-      <c r="E12" s="109"/>
-      <c r="F12" s="110"/>
-      <c r="G12" s="110"/>
-      <c r="H12" s="111"/>
-      <c r="I12" s="111"/>
-      <c r="L12" s="101"/>
+      <c r="A12" s="101"/>
+      <c r="B12" s="116"/>
+      <c r="C12" s="116"/>
+      <c r="D12" s="107"/>
+      <c r="E12" s="102"/>
+      <c r="F12" s="103"/>
+      <c r="G12" s="103"/>
+      <c r="H12" s="104"/>
+      <c r="I12" s="104"/>
+      <c r="L12" s="95"/>
       <c r="O12" s="60"/>
       <c r="P12" s="60"/>
-      <c r="Q12" s="102"/>
-      <c r="R12" s="102"/>
+      <c r="Q12" s="96"/>
+      <c r="R12" s="96"/>
     </row>
     <row r="13" spans="1:20" s="58" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A13" s="108"/>
-      <c r="B13" s="124"/>
-      <c r="C13" s="124"/>
-      <c r="D13" s="114"/>
-      <c r="E13" s="109"/>
-      <c r="F13" s="110"/>
-      <c r="G13" s="110"/>
-      <c r="H13" s="112" t="s">
-        <v>90</v>
-      </c>
-      <c r="I13" s="111">
+      <c r="A13" s="101"/>
+      <c r="B13" s="116"/>
+      <c r="C13" s="116"/>
+      <c r="D13" s="107"/>
+      <c r="E13" s="102"/>
+      <c r="F13" s="103"/>
+      <c r="G13" s="103"/>
+      <c r="H13" s="105" t="s">
+        <v>74</v>
+      </c>
+      <c r="I13" s="104">
         <f>SUM(I9:I12)</f>
-        <v>20000</v>
-      </c>
-      <c r="L13" s="101"/>
+        <v>0</v>
+      </c>
+      <c r="L13" s="95"/>
       <c r="O13" s="60"/>
       <c r="P13" s="60"/>
-      <c r="Q13" s="102"/>
-      <c r="R13" s="102"/>
+      <c r="Q13" s="96"/>
+      <c r="R13" s="96"/>
     </row>
     <row r="14" spans="1:20" s="58" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A14" s="108"/>
-      <c r="B14" s="124"/>
-      <c r="C14" s="124"/>
-      <c r="D14" s="114"/>
-      <c r="E14" s="109"/>
-      <c r="F14" s="110"/>
-      <c r="G14" s="110"/>
-      <c r="H14" s="112" t="s">
-        <v>89</v>
-      </c>
-      <c r="I14" s="111">
+      <c r="A14" s="101"/>
+      <c r="B14" s="116"/>
+      <c r="C14" s="116"/>
+      <c r="D14" s="107"/>
+      <c r="E14" s="102"/>
+      <c r="F14" s="103"/>
+      <c r="G14" s="103"/>
+      <c r="H14" s="105" t="s">
+        <v>73</v>
+      </c>
+      <c r="I14" s="104">
         <f>I13*0.13</f>
-        <v>2600</v>
-      </c>
-      <c r="L14" s="101"/>
+        <v>0</v>
+      </c>
+      <c r="L14" s="95"/>
       <c r="M14" s="60"/>
       <c r="N14" s="60"/>
       <c r="O14" s="60"/>
@@ -2263,164 +2022,158 @@
       <c r="T14" s="60"/>
     </row>
     <row r="15" spans="1:20" s="60" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A15" s="120" t="s">
-        <v>67</v>
-      </c>
-      <c r="B15" s="120"/>
-      <c r="C15" s="120"/>
-      <c r="D15" s="108"/>
-      <c r="E15" s="108"/>
-      <c r="F15" s="119" t="s">
+      <c r="A15" s="112" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="112"/>
+      <c r="C15" s="112"/>
+      <c r="D15" s="101"/>
+      <c r="E15" s="101"/>
+      <c r="F15" s="111" t="s">
         <v>14</v>
       </c>
-      <c r="G15" s="113"/>
-      <c r="H15" s="120" t="s">
-        <v>73</v>
-      </c>
-      <c r="I15" s="121">
+      <c r="G15" s="106"/>
+      <c r="H15" s="112" t="s">
+        <v>62</v>
+      </c>
+      <c r="I15" s="113">
         <f>I14+I13</f>
-        <v>22600</v>
-      </c>
-      <c r="J15" s="87"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="83"/>
     </row>
     <row r="16" spans="1:20" s="60" customFormat="1" ht="30" customHeight="1">
-      <c r="A16" s="131" t="s">
-        <v>85</v>
-      </c>
-      <c r="B16" s="131"/>
-      <c r="C16" s="131"/>
-      <c r="D16" s="131"/>
-      <c r="E16" s="131"/>
-      <c r="F16" s="131"/>
-      <c r="G16" s="131"/>
-      <c r="H16" s="131"/>
-      <c r="I16" s="131"/>
-      <c r="L16" s="103"/>
-    </row>
-    <row r="17" spans="1:20" s="115" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A17" s="129" t="s">
-        <v>91</v>
-      </c>
-      <c r="B17" s="129"/>
-      <c r="C17" s="129"/>
-      <c r="D17" s="129"/>
-      <c r="E17" s="129"/>
-      <c r="F17" s="129"/>
-      <c r="G17" s="129"/>
-      <c r="H17" s="129"/>
-      <c r="I17" s="129"/>
-      <c r="L17" s="116"/>
-      <c r="M17" s="117"/>
-      <c r="N17" s="117"/>
-      <c r="O17" s="117"/>
-      <c r="P17" s="117"/>
-      <c r="Q17" s="117"/>
-      <c r="R17" s="117"/>
-      <c r="S17" s="117"/>
-      <c r="T17" s="117"/>
-    </row>
-    <row r="18" spans="1:20" s="117" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A18" s="129" t="s">
-        <v>92</v>
-      </c>
-      <c r="B18" s="129"/>
-      <c r="C18" s="129"/>
-      <c r="D18" s="129"/>
-      <c r="E18" s="129"/>
-      <c r="F18" s="129"/>
-      <c r="G18" s="129"/>
-      <c r="H18" s="129"/>
-      <c r="I18" s="129"/>
-    </row>
-    <row r="19" spans="1:20" s="117" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A19" s="129" t="s">
-        <v>86</v>
-      </c>
-      <c r="B19" s="129"/>
-      <c r="C19" s="129"/>
-      <c r="D19" s="129"/>
-      <c r="E19" s="129"/>
-      <c r="F19" s="129"/>
-      <c r="G19" s="129"/>
-      <c r="H19" s="129"/>
-      <c r="I19" s="129"/>
-      <c r="M19" s="115"/>
-      <c r="N19" s="115"/>
-      <c r="O19" s="115"/>
-      <c r="P19" s="115"/>
-      <c r="Q19" s="115"/>
-      <c r="R19" s="115"/>
-      <c r="S19" s="115"/>
-      <c r="T19" s="115"/>
-    </row>
-    <row r="20" spans="1:20" s="115" customFormat="1" ht="35.25" customHeight="1">
-      <c r="A20" s="129" t="s">
-        <v>87</v>
-      </c>
-      <c r="B20" s="129"/>
-      <c r="C20" s="129"/>
-      <c r="D20" s="129"/>
-      <c r="E20" s="129"/>
-      <c r="F20" s="129"/>
-      <c r="G20" s="129"/>
-      <c r="H20" s="129"/>
-      <c r="I20" s="129"/>
-      <c r="L20" s="116"/>
-    </row>
-    <row r="21" spans="1:20" s="115" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A21" s="130" t="s">
-        <v>67</v>
-      </c>
-      <c r="B21" s="130"/>
-      <c r="C21" s="130"/>
-      <c r="D21" s="130"/>
-      <c r="E21" s="130"/>
-      <c r="F21" s="130"/>
-      <c r="G21" s="130"/>
-      <c r="H21" s="130"/>
-      <c r="I21" s="130"/>
-      <c r="L21" s="116"/>
+      <c r="A16" s="123" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" s="123"/>
+      <c r="C16" s="123"/>
+      <c r="D16" s="123"/>
+      <c r="E16" s="123"/>
+      <c r="F16" s="123"/>
+      <c r="G16" s="123"/>
+      <c r="H16" s="123"/>
+      <c r="I16" s="123"/>
+      <c r="L16" s="97"/>
+    </row>
+    <row r="17" spans="1:20" s="108" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A17" s="124" t="s">
+        <v>76</v>
+      </c>
+      <c r="B17" s="121"/>
+      <c r="C17" s="121"/>
+      <c r="D17" s="121"/>
+      <c r="E17" s="121"/>
+      <c r="F17" s="121"/>
+      <c r="G17" s="121"/>
+      <c r="H17" s="121"/>
+      <c r="I17" s="121"/>
+      <c r="L17" s="109"/>
+      <c r="M17" s="110"/>
+      <c r="N17" s="110"/>
+      <c r="O17" s="110"/>
+      <c r="P17" s="110"/>
+      <c r="Q17" s="110"/>
+      <c r="R17" s="110"/>
+      <c r="S17" s="110"/>
+      <c r="T17" s="110"/>
+    </row>
+    <row r="18" spans="1:20" s="110" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A18" s="121"/>
+      <c r="B18" s="121"/>
+      <c r="C18" s="121"/>
+      <c r="D18" s="121"/>
+      <c r="E18" s="121"/>
+      <c r="F18" s="121"/>
+      <c r="G18" s="121"/>
+      <c r="H18" s="121"/>
+      <c r="I18" s="121"/>
+    </row>
+    <row r="19" spans="1:20" s="110" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A19" s="121"/>
+      <c r="B19" s="121"/>
+      <c r="C19" s="121"/>
+      <c r="D19" s="121"/>
+      <c r="E19" s="121"/>
+      <c r="F19" s="121"/>
+      <c r="G19" s="121"/>
+      <c r="H19" s="121"/>
+      <c r="I19" s="121"/>
+      <c r="M19" s="108"/>
+      <c r="N19" s="108"/>
+      <c r="O19" s="108"/>
+      <c r="P19" s="108"/>
+      <c r="Q19" s="108"/>
+      <c r="R19" s="108"/>
+      <c r="S19" s="108"/>
+      <c r="T19" s="108"/>
+    </row>
+    <row r="20" spans="1:20" s="108" customFormat="1" ht="35.25" customHeight="1">
+      <c r="A20" s="121"/>
+      <c r="B20" s="121"/>
+      <c r="C20" s="121"/>
+      <c r="D20" s="121"/>
+      <c r="E20" s="121"/>
+      <c r="F20" s="121"/>
+      <c r="G20" s="121"/>
+      <c r="H20" s="121"/>
+      <c r="I20" s="121"/>
+      <c r="L20" s="109"/>
+    </row>
+    <row r="21" spans="1:20" s="108" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A21" s="122" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" s="122"/>
+      <c r="C21" s="122"/>
+      <c r="D21" s="122"/>
+      <c r="E21" s="122"/>
+      <c r="F21" s="122"/>
+      <c r="G21" s="122"/>
+      <c r="H21" s="122"/>
+      <c r="I21" s="122"/>
+      <c r="L21" s="109"/>
     </row>
     <row r="22" spans="1:20" s="62" customFormat="1" ht="53.25" customHeight="1">
-      <c r="A22" s="106"/>
-      <c r="B22" s="106"/>
-      <c r="C22" s="106"/>
-      <c r="D22" s="106"/>
-      <c r="E22" s="106"/>
-      <c r="F22" s="106"/>
-      <c r="G22" s="106"/>
-      <c r="H22" s="106"/>
-      <c r="I22" s="106"/>
-      <c r="O22" s="104"/>
-      <c r="P22" s="104"/>
-    </row>
-    <row r="23" spans="1:20" s="62" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A23" s="88"/>
-      <c r="B23" s="88"/>
-      <c r="C23" s="88"/>
-      <c r="D23" s="88"/>
-      <c r="E23" s="88"/>
-      <c r="F23" s="88"/>
-      <c r="G23" s="88"/>
-      <c r="H23" s="88"/>
-      <c r="I23" s="88"/>
-      <c r="O23" s="104"/>
-      <c r="P23" s="104"/>
-    </row>
-    <row r="24" spans="1:20" s="62" customFormat="1" ht="19.5" hidden="1" customHeight="1">
-      <c r="A24" s="89" t="s">
-        <v>18</v>
-      </c>
-      <c r="B24" s="90"/>
-      <c r="C24" s="90"/>
-      <c r="D24" s="56"/>
-      <c r="E24" s="56"/>
-      <c r="F24" s="89" t="s">
-        <v>19</v>
-      </c>
-      <c r="G24" s="89"/>
-      <c r="H24" s="91"/>
-      <c r="I24" s="92"/>
+      <c r="A22" s="99"/>
+      <c r="B22" s="99"/>
+      <c r="C22" s="99"/>
+      <c r="D22" s="99"/>
+      <c r="E22" s="99"/>
+      <c r="F22" s="99"/>
+      <c r="G22" s="99"/>
+      <c r="H22" s="99"/>
+      <c r="I22" s="99"/>
+      <c r="O22" s="98"/>
+      <c r="P22" s="98"/>
+    </row>
+    <row r="23" spans="1:20" s="62" customFormat="1" ht="24" customHeight="1">
+      <c r="A23" s="158"/>
+      <c r="B23" s="158"/>
+      <c r="C23" s="158"/>
+      <c r="D23" s="158"/>
+      <c r="E23" s="158"/>
+      <c r="F23" s="158"/>
+      <c r="G23" s="158"/>
+      <c r="H23" s="158"/>
+      <c r="I23" s="158"/>
+      <c r="J23" s="159"/>
+      <c r="K23" s="159"/>
+      <c r="O23" s="98"/>
+      <c r="P23" s="98"/>
+    </row>
+    <row r="24" spans="1:20" s="62" customFormat="1" ht="19.5" customHeight="1">
+      <c r="A24" s="160"/>
+      <c r="B24" s="84"/>
+      <c r="C24" s="84"/>
+      <c r="D24" s="58"/>
+      <c r="E24" s="58"/>
+      <c r="F24" s="160"/>
+      <c r="G24" s="160"/>
+      <c r="H24" s="85"/>
+      <c r="I24" s="161"/>
+      <c r="J24" s="159"/>
+      <c r="K24" s="159"/>
       <c r="M24" s="64"/>
       <c r="N24" s="64"/>
       <c r="O24" s="67"/>
@@ -2430,52 +2183,40 @@
       <c r="S24" s="64"/>
       <c r="T24" s="64"/>
     </row>
-    <row r="25" spans="1:20" hidden="1">
-      <c r="A25" s="93" t="s">
-        <v>20</v>
-      </c>
-      <c r="C25" s="94"/>
-      <c r="D25" s="95"/>
-      <c r="E25" s="95"/>
-      <c r="F25" s="93" t="s">
-        <v>21</v>
-      </c>
-      <c r="G25" s="93"/>
-      <c r="I25" s="92"/>
-    </row>
-    <row r="26" spans="1:20" hidden="1">
-      <c r="A26" s="93" t="s">
-        <v>22</v>
-      </c>
-      <c r="C26" s="94"/>
-      <c r="D26" s="95"/>
-      <c r="E26" s="95"/>
-      <c r="F26" s="93" t="s">
-        <v>23</v>
-      </c>
-      <c r="G26" s="93"/>
-      <c r="I26" s="92"/>
-    </row>
-    <row r="27" spans="1:20" hidden="1">
-      <c r="A27" s="93" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="94"/>
-      <c r="D27" s="95"/>
-      <c r="E27" s="95"/>
-      <c r="F27" s="93" t="s">
-        <v>25</v>
-      </c>
-      <c r="G27" s="93"/>
-      <c r="I27" s="92"/>
-    </row>
-    <row r="28" spans="1:20" hidden="1">
+    <row r="25" spans="1:20">
+      <c r="A25" s="87"/>
+      <c r="C25" s="88"/>
+      <c r="D25" s="89"/>
+      <c r="E25" s="89"/>
+      <c r="F25" s="87"/>
+      <c r="G25" s="87"/>
+      <c r="I25" s="86"/>
+    </row>
+    <row r="26" spans="1:20">
+      <c r="A26" s="87"/>
+      <c r="C26" s="88"/>
+      <c r="D26" s="89"/>
+      <c r="E26" s="89"/>
+      <c r="F26" s="87"/>
+      <c r="G26" s="87"/>
+      <c r="I26" s="86"/>
+    </row>
+    <row r="27" spans="1:20">
+      <c r="A27" s="87"/>
+      <c r="C27" s="88"/>
+      <c r="D27" s="89"/>
+      <c r="E27" s="89"/>
+      <c r="F27" s="87"/>
+      <c r="G27" s="87"/>
+      <c r="I27" s="86"/>
+    </row>
+    <row r="28" spans="1:20">
       <c r="A28" s="55"/>
       <c r="F28" s="55"/>
       <c r="G28" s="55"/>
-      <c r="I28" s="92"/>
-    </row>
-    <row r="29" spans="1:20" hidden="1">
+      <c r="I28" s="86"/>
+    </row>
+    <row r="29" spans="1:20">
       <c r="A29" s="69"/>
     </row>
   </sheetData>
@@ -2533,21 +2274,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A1" s="132" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
-      <c r="F1" s="132"/>
-      <c r="G1" s="132"/>
+      <c r="A1" s="125" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="125"/>
+      <c r="C1" s="125"/>
+      <c r="D1" s="125"/>
+      <c r="E1" s="125"/>
+      <c r="F1" s="125"/>
+      <c r="G1" s="125"/>
       <c r="M1" s="45"/>
       <c r="N1" s="45"/>
     </row>
     <row r="2" spans="1:15" ht="13.5" customHeight="1">
       <c r="F2" s="12" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G2" s="13" t="s">
         <v>2</v>
@@ -2558,18 +2299,18 @@
     </row>
     <row r="3" spans="1:15" ht="15" customHeight="1">
       <c r="F3" s="12" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="14" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C4" s="15"/>
       <c r="D4" s="15"/>
@@ -2579,14 +2320,14 @@
     </row>
     <row r="5" spans="1:15" s="2" customFormat="1" ht="33" customHeight="1">
       <c r="A5" s="17"/>
-      <c r="B5" s="133" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="133"/>
-      <c r="D5" s="133"/>
-      <c r="E5" s="133"/>
-      <c r="F5" s="133"/>
-      <c r="G5" s="133"/>
+      <c r="B5" s="126" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="126"/>
+      <c r="D5" s="126"/>
+      <c r="E5" s="126"/>
+      <c r="F5" s="126"/>
+      <c r="G5" s="126"/>
       <c r="H5" s="18"/>
       <c r="M5" s="46"/>
       <c r="N5" s="46"/>
@@ -2604,29 +2345,29 @@
     </row>
     <row r="7" spans="1:15" s="2" customFormat="1">
       <c r="A7" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="134" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="127" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="134"/>
-      <c r="D7" s="134"/>
-      <c r="E7" s="134"/>
-      <c r="F7" s="134"/>
+      <c r="C7" s="127"/>
+      <c r="D7" s="127"/>
+      <c r="E7" s="127"/>
+      <c r="F7" s="127"/>
       <c r="G7" s="20"/>
       <c r="M7" s="46"/>
       <c r="N7" s="46"/>
     </row>
     <row r="8" spans="1:15" s="2" customFormat="1" ht="54" customHeight="1">
       <c r="A8" s="17"/>
-      <c r="B8" s="135" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="135"/>
-      <c r="D8" s="135"/>
-      <c r="E8" s="135"/>
-      <c r="F8" s="135"/>
-      <c r="G8" s="135"/>
+      <c r="B8" s="128" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="128"/>
+      <c r="D8" s="128"/>
+      <c r="E8" s="128"/>
+      <c r="F8" s="128"/>
+      <c r="G8" s="128"/>
       <c r="M8" s="46"/>
       <c r="N8" s="46"/>
     </row>
@@ -2642,39 +2383,39 @@
       <c r="N9" s="46"/>
     </row>
     <row r="10" spans="1:15" s="3" customFormat="1" ht="49.5" customHeight="1">
-      <c r="A10" s="136" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" s="136"/>
-      <c r="C10" s="136"/>
-      <c r="D10" s="136"/>
-      <c r="E10" s="136"/>
-      <c r="F10" s="136"/>
-      <c r="G10" s="136"/>
+      <c r="A10" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="129"/>
+      <c r="C10" s="129"/>
+      <c r="D10" s="129"/>
+      <c r="E10" s="129"/>
+      <c r="F10" s="129"/>
+      <c r="G10" s="129"/>
       <c r="M10" s="4"/>
       <c r="N10" s="4"/>
     </row>
     <row r="11" spans="1:15" s="3" customFormat="1" ht="27" customHeight="1">
-      <c r="A11" s="137" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" s="137"/>
-      <c r="C11" s="137"/>
-      <c r="D11" s="137"/>
-      <c r="E11" s="137"/>
-      <c r="F11" s="137"/>
-      <c r="G11" s="137"/>
+      <c r="A11" s="130" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="130"/>
+      <c r="C11" s="130"/>
+      <c r="D11" s="130"/>
+      <c r="E11" s="130"/>
+      <c r="F11" s="130"/>
+      <c r="G11" s="130"/>
       <c r="M11" s="4"/>
       <c r="N11" s="4"/>
     </row>
     <row r="12" spans="1:15" s="4" customFormat="1" ht="30.75" customHeight="1">
       <c r="A12" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="138" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="131" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="139"/>
+      <c r="C12" s="132"/>
       <c r="D12" s="23" t="s">
         <v>5</v>
       </c>
@@ -2682,24 +2423,24 @@
         <v>6</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G12" s="24" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="L12" s="47"/>
       <c r="M12" s="48"/>
       <c r="N12" s="49"/>
-      <c r="O12" s="150"/>
+      <c r="O12" s="143"/>
     </row>
     <row r="13" spans="1:15" s="3" customFormat="1" ht="18" customHeight="1">
       <c r="A13" s="25">
         <v>1</v>
       </c>
-      <c r="B13" s="140">
+      <c r="B13" s="133">
         <v>50655</v>
       </c>
-      <c r="C13" s="141"/>
+      <c r="C13" s="134"/>
       <c r="D13" s="26" t="s">
         <v>7</v>
       </c>
@@ -2716,16 +2457,16 @@
       <c r="J13" s="51"/>
       <c r="M13" s="4"/>
       <c r="N13" s="4"/>
-      <c r="O13" s="150"/>
+      <c r="O13" s="143"/>
     </row>
     <row r="14" spans="1:15" s="3" customFormat="1" ht="18" customHeight="1">
       <c r="A14" s="25">
         <v>2</v>
       </c>
-      <c r="B14" s="140">
+      <c r="B14" s="133">
         <v>50755</v>
       </c>
-      <c r="C14" s="141"/>
+      <c r="C14" s="134"/>
       <c r="D14" s="26" t="s">
         <v>8</v>
       </c>
@@ -2748,10 +2489,10 @@
       <c r="A15" s="25">
         <v>3</v>
       </c>
-      <c r="B15" s="140">
+      <c r="B15" s="133">
         <v>50665</v>
       </c>
-      <c r="C15" s="141"/>
+      <c r="C15" s="134"/>
       <c r="D15" s="26" t="s">
         <v>9</v>
       </c>
@@ -2774,10 +2515,10 @@
       <c r="A16" s="25">
         <v>4</v>
       </c>
-      <c r="B16" s="140">
+      <c r="B16" s="133">
         <v>50765</v>
       </c>
-      <c r="C16" s="141"/>
+      <c r="C16" s="134"/>
       <c r="D16" s="26" t="s">
         <v>10</v>
       </c>
@@ -2800,10 +2541,10 @@
       <c r="A17" s="25">
         <v>5</v>
       </c>
-      <c r="B17" s="140">
+      <c r="B17" s="133">
         <v>50720</v>
       </c>
-      <c r="C17" s="141"/>
+      <c r="C17" s="134"/>
       <c r="D17" s="26" t="s">
         <v>11</v>
       </c>
@@ -2826,10 +2567,10 @@
       <c r="A18" s="30">
         <v>6</v>
       </c>
-      <c r="B18" s="140">
+      <c r="B18" s="133">
         <v>50730</v>
       </c>
-      <c r="C18" s="141"/>
+      <c r="C18" s="134"/>
       <c r="D18" s="31" t="s">
         <v>12</v>
       </c>
@@ -2849,54 +2590,54 @@
       <c r="O18" s="50"/>
     </row>
     <row r="19" spans="1:15" s="4" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A19" s="151" t="s">
+      <c r="A19" s="144" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="152"/>
-      <c r="C19" s="153"/>
+      <c r="B19" s="145"/>
+      <c r="C19" s="146"/>
       <c r="D19" s="32"/>
-      <c r="E19" s="144">
+      <c r="E19" s="137">
         <f>SUM(E13:E18)</f>
         <v>6000</v>
       </c>
-      <c r="F19" s="146"/>
-      <c r="G19" s="148">
+      <c r="F19" s="139"/>
+      <c r="G19" s="141">
         <f>SUM(G13:G18)</f>
         <v>73120</v>
       </c>
       <c r="H19" s="33"/>
     </row>
     <row r="20" spans="1:15" s="4" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A20" s="154"/>
-      <c r="B20" s="155"/>
-      <c r="C20" s="156"/>
+      <c r="A20" s="147"/>
+      <c r="B20" s="148"/>
+      <c r="C20" s="149"/>
       <c r="D20" s="34"/>
-      <c r="E20" s="145"/>
-      <c r="F20" s="147"/>
-      <c r="G20" s="149"/>
+      <c r="E20" s="138"/>
+      <c r="F20" s="140"/>
+      <c r="G20" s="142"/>
     </row>
     <row r="21" spans="1:15" s="4" customFormat="1" ht="30" hidden="1" customHeight="1">
-      <c r="A21" s="142" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="142"/>
-      <c r="C21" s="142"/>
-      <c r="D21" s="142"/>
-      <c r="E21" s="142"/>
-      <c r="F21" s="142"/>
-      <c r="G21" s="142"/>
+      <c r="A21" s="135" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="135"/>
+      <c r="C21" s="135"/>
+      <c r="D21" s="135"/>
+      <c r="E21" s="135"/>
+      <c r="F21" s="135"/>
+      <c r="G21" s="135"/>
       <c r="J21" s="52"/>
     </row>
     <row r="22" spans="1:15" s="4" customFormat="1" ht="30" customHeight="1">
-      <c r="A22" s="143" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22" s="143"/>
-      <c r="C22" s="143"/>
-      <c r="D22" s="143"/>
-      <c r="E22" s="143"/>
-      <c r="F22" s="143"/>
-      <c r="G22" s="143"/>
+      <c r="A22" s="136" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="136"/>
+      <c r="C22" s="136"/>
+      <c r="D22" s="136"/>
+      <c r="E22" s="136"/>
+      <c r="F22" s="136"/>
+      <c r="G22" s="136"/>
       <c r="J22" s="52"/>
     </row>
     <row r="23" spans="1:15" s="4" customFormat="1" ht="21.75" customHeight="1">
@@ -2946,20 +2687,20 @@
       <c r="J26" s="52"/>
     </row>
     <row r="27" spans="1:15" s="4" customFormat="1" ht="30" customHeight="1">
-      <c r="A27" s="143" t="s">
-        <v>42</v>
-      </c>
-      <c r="B27" s="143"/>
-      <c r="C27" s="143"/>
-      <c r="D27" s="143"/>
-      <c r="E27" s="143"/>
-      <c r="F27" s="143"/>
-      <c r="G27" s="143"/>
+      <c r="A27" s="136" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="136"/>
+      <c r="C27" s="136"/>
+      <c r="D27" s="136"/>
+      <c r="E27" s="136"/>
+      <c r="F27" s="136"/>
+      <c r="G27" s="136"/>
       <c r="J27" s="52"/>
     </row>
     <row r="28" spans="1:15" s="5" customFormat="1" ht="19.5" customHeight="1">
       <c r="A28" s="36" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C28" s="36"/>
       <c r="D28" s="36"/>
@@ -2969,7 +2710,7 @@
     </row>
     <row r="29" spans="1:15" s="5" customFormat="1" ht="19.5" customHeight="1">
       <c r="A29" s="36" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C29" s="36"/>
       <c r="D29" s="36"/>
@@ -2979,7 +2720,7 @@
     </row>
     <row r="30" spans="1:15" s="6" customFormat="1" ht="19.5" customHeight="1">
       <c r="A30" s="36" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C30" s="37"/>
       <c r="D30" s="37"/>
@@ -2989,7 +2730,7 @@
     </row>
     <row r="31" spans="1:15" s="6" customFormat="1" ht="19.5" customHeight="1">
       <c r="A31" s="36" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C31" s="36"/>
       <c r="D31" s="36"/>
@@ -2999,7 +2740,7 @@
     </row>
     <row r="32" spans="1:15" s="6" customFormat="1" ht="19.5" customHeight="1">
       <c r="A32" s="36" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C32" s="36"/>
       <c r="D32" s="36"/>
@@ -3009,7 +2750,7 @@
     </row>
     <row r="33" spans="1:14" s="6" customFormat="1" ht="19.5" customHeight="1">
       <c r="A33" s="36" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C33" s="36"/>
       <c r="D33" s="36"/>
@@ -3018,20 +2759,20 @@
       <c r="N33" s="54"/>
     </row>
     <row r="34" spans="1:14" s="4" customFormat="1" ht="30" customHeight="1">
-      <c r="A34" s="143" t="s">
-        <v>49</v>
-      </c>
-      <c r="B34" s="143"/>
-      <c r="C34" s="143"/>
-      <c r="D34" s="143"/>
-      <c r="E34" s="143"/>
-      <c r="F34" s="143"/>
-      <c r="G34" s="143"/>
+      <c r="A34" s="136" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="136"/>
+      <c r="C34" s="136"/>
+      <c r="D34" s="136"/>
+      <c r="E34" s="136"/>
+      <c r="F34" s="136"/>
+      <c r="G34" s="136"/>
       <c r="J34" s="52"/>
     </row>
     <row r="35" spans="1:14" s="5" customFormat="1" ht="19.5" customHeight="1">
       <c r="A35" s="36" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C35" s="36"/>
       <c r="D35" s="36"/>
@@ -3041,7 +2782,7 @@
     </row>
     <row r="36" spans="1:14" s="5" customFormat="1" ht="19.5" customHeight="1">
       <c r="A36" s="36" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C36" s="36"/>
       <c r="D36" s="36"/>
@@ -3050,20 +2791,20 @@
       <c r="N36" s="53"/>
     </row>
     <row r="37" spans="1:14" s="4" customFormat="1" ht="30" customHeight="1">
-      <c r="A37" s="143" t="s">
-        <v>52</v>
-      </c>
-      <c r="B37" s="143"/>
-      <c r="C37" s="143"/>
-      <c r="D37" s="143"/>
-      <c r="E37" s="143"/>
-      <c r="F37" s="143"/>
-      <c r="G37" s="143"/>
+      <c r="A37" s="136" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="136"/>
+      <c r="C37" s="136"/>
+      <c r="D37" s="136"/>
+      <c r="E37" s="136"/>
+      <c r="F37" s="136"/>
+      <c r="G37" s="136"/>
       <c r="J37" s="52"/>
     </row>
     <row r="38" spans="1:14" s="6" customFormat="1" ht="19.5" customHeight="1">
       <c r="A38" s="36" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C38" s="36"/>
       <c r="D38" s="36"/>
@@ -3073,7 +2814,7 @@
     </row>
     <row r="39" spans="1:14" s="6" customFormat="1" ht="19.5" customHeight="1">
       <c r="A39" s="36" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C39" s="36"/>
       <c r="D39" s="36"/>
@@ -3082,40 +2823,40 @@
       <c r="N39" s="54"/>
     </row>
     <row r="40" spans="1:14" s="4" customFormat="1" ht="30" customHeight="1">
-      <c r="A40" s="143" t="s">
-        <v>55</v>
-      </c>
-      <c r="B40" s="143"/>
-      <c r="C40" s="143"/>
-      <c r="D40" s="143"/>
-      <c r="E40" s="143"/>
-      <c r="F40" s="143"/>
-      <c r="G40" s="143"/>
+      <c r="A40" s="136" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="136"/>
+      <c r="C40" s="136"/>
+      <c r="D40" s="136"/>
+      <c r="E40" s="136"/>
+      <c r="F40" s="136"/>
+      <c r="G40" s="136"/>
       <c r="J40" s="52"/>
     </row>
     <row r="41" spans="1:14" s="6" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A41" s="161" t="s">
-        <v>56</v>
-      </c>
-      <c r="B41" s="161"/>
-      <c r="C41" s="161"/>
-      <c r="D41" s="161"/>
-      <c r="E41" s="161"/>
-      <c r="F41" s="161"/>
-      <c r="G41" s="161"/>
+      <c r="A41" s="154" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="154"/>
+      <c r="C41" s="154"/>
+      <c r="D41" s="154"/>
+      <c r="E41" s="154"/>
+      <c r="F41" s="154"/>
+      <c r="G41" s="154"/>
       <c r="M41" s="54"/>
       <c r="N41" s="54"/>
     </row>
     <row r="42" spans="1:14" s="6" customFormat="1" ht="44.25" customHeight="1">
-      <c r="A42" s="157" t="s">
-        <v>57</v>
-      </c>
-      <c r="B42" s="157"/>
-      <c r="C42" s="157"/>
-      <c r="D42" s="157"/>
-      <c r="E42" s="157"/>
-      <c r="F42" s="157"/>
-      <c r="G42" s="157"/>
+      <c r="A42" s="150" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="150"/>
+      <c r="C42" s="150"/>
+      <c r="D42" s="150"/>
+      <c r="E42" s="150"/>
+      <c r="F42" s="150"/>
+      <c r="G42" s="150"/>
       <c r="M42" s="54"/>
       <c r="N42" s="54"/>
     </row>
@@ -3130,27 +2871,27 @@
       <c r="J43" s="52"/>
     </row>
     <row r="44" spans="1:14" s="4" customFormat="1" ht="30" customHeight="1">
-      <c r="A44" s="143" t="s">
-        <v>58</v>
-      </c>
-      <c r="B44" s="143"/>
-      <c r="C44" s="143"/>
-      <c r="D44" s="143"/>
-      <c r="E44" s="143"/>
-      <c r="F44" s="143"/>
-      <c r="G44" s="143"/>
+      <c r="A44" s="136" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" s="136"/>
+      <c r="C44" s="136"/>
+      <c r="D44" s="136"/>
+      <c r="E44" s="136"/>
+      <c r="F44" s="136"/>
+      <c r="G44" s="136"/>
       <c r="J44" s="52"/>
     </row>
     <row r="45" spans="1:14" s="6" customFormat="1" ht="58.5" customHeight="1">
-      <c r="A45" s="158" t="s">
-        <v>59</v>
-      </c>
-      <c r="B45" s="159"/>
-      <c r="C45" s="159"/>
-      <c r="D45" s="159"/>
-      <c r="E45" s="159"/>
-      <c r="F45" s="159"/>
-      <c r="G45" s="159"/>
+      <c r="A45" s="151" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="152"/>
+      <c r="C45" s="152"/>
+      <c r="D45" s="152"/>
+      <c r="E45" s="152"/>
+      <c r="F45" s="152"/>
+      <c r="G45" s="152"/>
       <c r="M45" s="54"/>
       <c r="N45" s="54"/>
     </row>
@@ -3165,27 +2906,27 @@
       <c r="J46" s="52"/>
     </row>
     <row r="47" spans="1:14" s="4" customFormat="1" ht="30" customHeight="1">
-      <c r="A47" s="143" t="s">
-        <v>60</v>
-      </c>
-      <c r="B47" s="143"/>
-      <c r="C47" s="143"/>
-      <c r="D47" s="143"/>
-      <c r="E47" s="143"/>
-      <c r="F47" s="143"/>
-      <c r="G47" s="143"/>
+      <c r="A47" s="136" t="s">
+        <v>52</v>
+      </c>
+      <c r="B47" s="136"/>
+      <c r="C47" s="136"/>
+      <c r="D47" s="136"/>
+      <c r="E47" s="136"/>
+      <c r="F47" s="136"/>
+      <c r="G47" s="136"/>
       <c r="J47" s="52"/>
     </row>
     <row r="48" spans="1:14" s="6" customFormat="1" ht="46.5" customHeight="1">
-      <c r="A48" s="160" t="s">
-        <v>61</v>
-      </c>
-      <c r="B48" s="160"/>
-      <c r="C48" s="160"/>
-      <c r="D48" s="160"/>
-      <c r="E48" s="160"/>
-      <c r="F48" s="160"/>
-      <c r="G48" s="160"/>
+      <c r="A48" s="153" t="s">
+        <v>53</v>
+      </c>
+      <c r="B48" s="153"/>
+      <c r="C48" s="153"/>
+      <c r="D48" s="153"/>
+      <c r="E48" s="153"/>
+      <c r="F48" s="153"/>
+      <c r="G48" s="153"/>
       <c r="M48" s="54"/>
       <c r="N48" s="54"/>
     </row>
@@ -3198,27 +2939,27 @@
       <c r="N49" s="54"/>
     </row>
     <row r="50" spans="1:14" s="6" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A50" s="143" t="s">
-        <v>62</v>
-      </c>
-      <c r="B50" s="143"/>
-      <c r="C50" s="143"/>
-      <c r="D50" s="143"/>
-      <c r="E50" s="143"/>
-      <c r="F50" s="143"/>
-      <c r="G50" s="143"/>
+      <c r="A50" s="136" t="s">
+        <v>54</v>
+      </c>
+      <c r="B50" s="136"/>
+      <c r="C50" s="136"/>
+      <c r="D50" s="136"/>
+      <c r="E50" s="136"/>
+      <c r="F50" s="136"/>
+      <c r="G50" s="136"/>
       <c r="M50" s="54"/>
       <c r="N50" s="54"/>
     </row>
     <row r="51" spans="1:14" s="6" customFormat="1" ht="19.5" customHeight="1">
       <c r="A51" s="39" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="B51" s="39"/>
       <c r="C51" s="39"/>
       <c r="D51" s="39"/>
       <c r="E51" s="39" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="F51" s="39"/>
       <c r="G51" s="39"/>
@@ -3243,21 +2984,21 @@
     </row>
     <row r="53" spans="1:14">
       <c r="A53" s="36" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C53" s="43"/>
       <c r="D53" s="2"/>
       <c r="E53" s="36" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="G53" s="44"/>
     </row>
     <row r="54" spans="1:14">
       <c r="A54" s="36" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E54" s="36" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/excel-template/PO-template.xlsx
+++ b/excel-template/PO-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\exportcrm\excel-template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8A17243-928F-4647-BAD1-F437845C793E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A73E2B2-5D05-4E2A-8F74-D1D234C848C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="813" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -912,7 +912,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="162">
+  <cellXfs count="159">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1161,12 +1161,6 @@
     <xf numFmtId="181" fontId="14" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="14" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1">
       <alignment vertical="center"/>
@@ -1252,8 +1246,26 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="43" fontId="19" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="14" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="178" fontId="16" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1270,17 +1282,83 @@
     <xf numFmtId="43" fontId="15" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="43" fontId="19" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="11" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="11" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1297,98 +1375,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="11" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="11" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="14" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="43" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1765,37 +1758,37 @@
       <c r="D1" s="68"/>
       <c r="E1" s="68"/>
       <c r="F1" s="68"/>
-      <c r="G1" s="117" t="s">
+      <c r="G1" s="121" t="s">
         <v>72</v>
       </c>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
-      <c r="O1" s="90"/>
-      <c r="P1" s="90"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="O1" s="88"/>
+      <c r="P1" s="88"/>
     </row>
     <row r="2" spans="1:20" ht="26.25" customHeight="1">
       <c r="A2" s="69" t="s">
         <v>0</v>
       </c>
-      <c r="H2" s="118" t="s">
+      <c r="H2" s="122" t="s">
         <v>59</v>
       </c>
-      <c r="I2" s="118"/>
+      <c r="I2" s="122"/>
     </row>
     <row r="3" spans="1:20" s="56" customFormat="1" ht="21.75" customHeight="1">
-      <c r="A3" s="155" t="s">
+      <c r="A3" s="113" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="156"/>
+      <c r="B3" s="70"/>
       <c r="C3" s="58"/>
       <c r="D3" s="60"/>
       <c r="E3" s="60"/>
       <c r="F3" s="58"/>
       <c r="G3" s="58"/>
-      <c r="H3" s="108" t="s">
+      <c r="H3" s="106" t="s">
         <v>64</v>
       </c>
-      <c r="I3" s="157" t="s">
+      <c r="I3" s="114" t="s">
         <v>59</v>
       </c>
       <c r="O3" s="71"/>
@@ -1816,7 +1809,7 @@
       <c r="R4" s="77"/>
     </row>
     <row r="5" spans="1:20" s="57" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A5" s="114" t="s">
+      <c r="A5" s="112" t="s">
         <v>75</v>
       </c>
       <c r="C5" s="72"/>
@@ -1833,26 +1826,26 @@
       <c r="N5" s="61"/>
       <c r="O5" s="61"/>
       <c r="P5" s="61"/>
-      <c r="Q5" s="91"/>
+      <c r="Q5" s="89"/>
       <c r="R5" s="61"/>
       <c r="S5" s="61"/>
     </row>
     <row r="6" spans="1:20" s="57" customFormat="1" ht="24.9" customHeight="1">
       <c r="A6" s="76"/>
-      <c r="F6" s="99"/>
-      <c r="G6" s="99"/>
-      <c r="H6" s="99"/>
-      <c r="I6" s="99"/>
+      <c r="F6" s="97"/>
+      <c r="G6" s="97"/>
+      <c r="H6" s="97"/>
+      <c r="I6" s="97"/>
       <c r="J6" s="77"/>
-      <c r="K6" s="92"/>
+      <c r="K6" s="90"/>
       <c r="L6" s="77"/>
-      <c r="M6" s="92"/>
+      <c r="M6" s="90"/>
       <c r="N6" s="77"/>
-      <c r="O6" s="92"/>
+      <c r="O6" s="90"/>
       <c r="P6" s="77"/>
-      <c r="Q6" s="93"/>
-      <c r="R6" s="94"/>
-      <c r="S6" s="92"/>
+      <c r="Q6" s="91"/>
+      <c r="R6" s="92"/>
+      <c r="S6" s="90"/>
     </row>
     <row r="7" spans="1:20" s="57" customFormat="1" ht="24" customHeight="1">
       <c r="A7" s="79"/>
@@ -1860,10 +1853,10 @@
       <c r="C7" s="81"/>
       <c r="D7" s="81"/>
       <c r="E7" s="81"/>
-      <c r="F7" s="99"/>
-      <c r="G7" s="99"/>
-      <c r="H7" s="99"/>
-      <c r="I7" s="99"/>
+      <c r="F7" s="97"/>
+      <c r="G7" s="97"/>
+      <c r="H7" s="97"/>
+      <c r="I7" s="97"/>
       <c r="J7" s="77"/>
       <c r="K7" s="77"/>
       <c r="L7" s="77"/>
@@ -1877,13 +1870,13 @@
       <c r="T7" s="58"/>
     </row>
     <row r="8" spans="1:20" s="59" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A8" s="100" t="s">
+      <c r="A8" s="98" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="119" t="s">
+      <c r="B8" s="123" t="s">
         <v>61</v>
       </c>
-      <c r="C8" s="120"/>
+      <c r="C8" s="124"/>
       <c r="D8" s="82" t="s">
         <v>65</v>
       </c>
@@ -1902,116 +1895,116 @@
       <c r="I8" s="82" t="s">
         <v>70</v>
       </c>
-      <c r="M8" s="115"/>
-      <c r="N8" s="115"/>
-      <c r="O8" s="115"/>
-      <c r="P8" s="115"/>
-      <c r="Q8" s="115"/>
-      <c r="R8" s="115"/>
-      <c r="S8" s="115"/>
-      <c r="T8" s="115"/>
+      <c r="M8" s="125"/>
+      <c r="N8" s="125"/>
+      <c r="O8" s="125"/>
+      <c r="P8" s="125"/>
+      <c r="Q8" s="125"/>
+      <c r="R8" s="125"/>
+      <c r="S8" s="125"/>
+      <c r="T8" s="125"/>
     </row>
     <row r="9" spans="1:20" s="58" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A9" s="101"/>
-      <c r="B9" s="116"/>
-      <c r="C9" s="116"/>
-      <c r="D9" s="101"/>
-      <c r="E9" s="101"/>
-      <c r="F9" s="103"/>
-      <c r="G9" s="103"/>
-      <c r="H9" s="104"/>
-      <c r="I9" s="104"/>
-      <c r="L9" s="95"/>
+      <c r="A9" s="99"/>
+      <c r="B9" s="120"/>
+      <c r="C9" s="120"/>
+      <c r="D9" s="99"/>
+      <c r="E9" s="99"/>
+      <c r="F9" s="101"/>
+      <c r="G9" s="101"/>
+      <c r="H9" s="102"/>
+      <c r="I9" s="102"/>
+      <c r="L9" s="93"/>
       <c r="O9" s="60"/>
       <c r="P9" s="60"/>
-      <c r="Q9" s="96"/>
-      <c r="R9" s="96"/>
+      <c r="Q9" s="94"/>
+      <c r="R9" s="94"/>
     </row>
     <row r="10" spans="1:20" s="58" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A10" s="101"/>
-      <c r="B10" s="116"/>
-      <c r="C10" s="116"/>
-      <c r="D10" s="101"/>
-      <c r="E10" s="101"/>
-      <c r="F10" s="103"/>
-      <c r="G10" s="103"/>
-      <c r="H10" s="104"/>
-      <c r="I10" s="104"/>
-      <c r="L10" s="95"/>
+      <c r="A10" s="99"/>
+      <c r="B10" s="120"/>
+      <c r="C10" s="120"/>
+      <c r="D10" s="99"/>
+      <c r="E10" s="99"/>
+      <c r="F10" s="101"/>
+      <c r="G10" s="101"/>
+      <c r="H10" s="102"/>
+      <c r="I10" s="102"/>
+      <c r="L10" s="93"/>
       <c r="O10" s="60"/>
       <c r="P10" s="60"/>
-      <c r="Q10" s="96"/>
-      <c r="R10" s="96"/>
+      <c r="Q10" s="94"/>
+      <c r="R10" s="94"/>
     </row>
     <row r="11" spans="1:20" s="58" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A11" s="101"/>
-      <c r="B11" s="116"/>
-      <c r="C11" s="116"/>
-      <c r="D11" s="107"/>
-      <c r="E11" s="101"/>
-      <c r="F11" s="103"/>
-      <c r="G11" s="103"/>
-      <c r="H11" s="104"/>
-      <c r="I11" s="104"/>
-      <c r="L11" s="95"/>
+      <c r="A11" s="99"/>
+      <c r="B11" s="120"/>
+      <c r="C11" s="120"/>
+      <c r="D11" s="105"/>
+      <c r="E11" s="99"/>
+      <c r="F11" s="101"/>
+      <c r="G11" s="101"/>
+      <c r="H11" s="102"/>
+      <c r="I11" s="102"/>
+      <c r="L11" s="93"/>
       <c r="O11" s="60"/>
       <c r="P11" s="60"/>
-      <c r="Q11" s="96"/>
-      <c r="R11" s="96"/>
+      <c r="Q11" s="94"/>
+      <c r="R11" s="94"/>
     </row>
     <row r="12" spans="1:20" s="58" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A12" s="101"/>
-      <c r="B12" s="116"/>
-      <c r="C12" s="116"/>
-      <c r="D12" s="107"/>
-      <c r="E12" s="102"/>
-      <c r="F12" s="103"/>
-      <c r="G12" s="103"/>
-      <c r="H12" s="104"/>
-      <c r="I12" s="104"/>
-      <c r="L12" s="95"/>
+      <c r="A12" s="99"/>
+      <c r="B12" s="120"/>
+      <c r="C12" s="120"/>
+      <c r="D12" s="105"/>
+      <c r="E12" s="100"/>
+      <c r="F12" s="101"/>
+      <c r="G12" s="101"/>
+      <c r="H12" s="102"/>
+      <c r="I12" s="102"/>
+      <c r="L12" s="93"/>
       <c r="O12" s="60"/>
       <c r="P12" s="60"/>
-      <c r="Q12" s="96"/>
-      <c r="R12" s="96"/>
+      <c r="Q12" s="94"/>
+      <c r="R12" s="94"/>
     </row>
     <row r="13" spans="1:20" s="58" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A13" s="101"/>
-      <c r="B13" s="116"/>
-      <c r="C13" s="116"/>
-      <c r="D13" s="107"/>
-      <c r="E13" s="102"/>
-      <c r="F13" s="103"/>
-      <c r="G13" s="103"/>
-      <c r="H13" s="105" t="s">
+      <c r="A13" s="99"/>
+      <c r="B13" s="120"/>
+      <c r="C13" s="120"/>
+      <c r="D13" s="105"/>
+      <c r="E13" s="100"/>
+      <c r="F13" s="101"/>
+      <c r="G13" s="101"/>
+      <c r="H13" s="103" t="s">
         <v>74</v>
       </c>
-      <c r="I13" s="104">
+      <c r="I13" s="102">
         <f>SUM(I9:I12)</f>
         <v>0</v>
       </c>
-      <c r="L13" s="95"/>
+      <c r="L13" s="93"/>
       <c r="O13" s="60"/>
       <c r="P13" s="60"/>
-      <c r="Q13" s="96"/>
-      <c r="R13" s="96"/>
+      <c r="Q13" s="94"/>
+      <c r="R13" s="94"/>
     </row>
     <row r="14" spans="1:20" s="58" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A14" s="101"/>
-      <c r="B14" s="116"/>
-      <c r="C14" s="116"/>
-      <c r="D14" s="107"/>
-      <c r="E14" s="102"/>
-      <c r="F14" s="103"/>
-      <c r="G14" s="103"/>
-      <c r="H14" s="105" t="s">
+      <c r="A14" s="99"/>
+      <c r="B14" s="120"/>
+      <c r="C14" s="120"/>
+      <c r="D14" s="105"/>
+      <c r="E14" s="100"/>
+      <c r="F14" s="101"/>
+      <c r="G14" s="101"/>
+      <c r="H14" s="103" t="s">
         <v>73</v>
       </c>
-      <c r="I14" s="104">
+      <c r="I14" s="102">
         <f>I13*0.13</f>
         <v>0</v>
       </c>
-      <c r="L14" s="95"/>
+      <c r="L14" s="93"/>
       <c r="M14" s="60"/>
       <c r="N14" s="60"/>
       <c r="O14" s="60"/>
@@ -2022,158 +2015,165 @@
       <c r="T14" s="60"/>
     </row>
     <row r="15" spans="1:20" s="60" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A15" s="112" t="s">
+      <c r="A15" s="110" t="s">
         <v>59</v>
       </c>
-      <c r="B15" s="112"/>
-      <c r="C15" s="112"/>
-      <c r="D15" s="101"/>
-      <c r="E15" s="101"/>
-      <c r="F15" s="111" t="s">
+      <c r="B15" s="110"/>
+      <c r="C15" s="110"/>
+      <c r="D15" s="99"/>
+      <c r="E15" s="99"/>
+      <c r="F15" s="109" t="s">
         <v>14</v>
       </c>
-      <c r="G15" s="106"/>
-      <c r="H15" s="112" t="s">
+      <c r="G15" s="104"/>
+      <c r="H15" s="110" t="s">
         <v>62</v>
       </c>
-      <c r="I15" s="113">
+      <c r="I15" s="111">
         <f>I14+I13</f>
         <v>0</v>
       </c>
       <c r="J15" s="83"/>
     </row>
     <row r="16" spans="1:20" s="60" customFormat="1" ht="30" customHeight="1">
-      <c r="A16" s="123" t="s">
+      <c r="A16" s="118" t="s">
         <v>71</v>
       </c>
-      <c r="B16" s="123"/>
-      <c r="C16" s="123"/>
-      <c r="D16" s="123"/>
-      <c r="E16" s="123"/>
-      <c r="F16" s="123"/>
-      <c r="G16" s="123"/>
-      <c r="H16" s="123"/>
-      <c r="I16" s="123"/>
-      <c r="L16" s="97"/>
-    </row>
-    <row r="17" spans="1:20" s="108" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A17" s="124" t="s">
+      <c r="B16" s="118"/>
+      <c r="C16" s="118"/>
+      <c r="D16" s="118"/>
+      <c r="E16" s="118"/>
+      <c r="F16" s="118"/>
+      <c r="G16" s="118"/>
+      <c r="H16" s="118"/>
+      <c r="I16" s="118"/>
+      <c r="L16" s="95"/>
+    </row>
+    <row r="17" spans="1:20" s="106" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A17" s="119" t="s">
         <v>76</v>
       </c>
-      <c r="B17" s="121"/>
-      <c r="C17" s="121"/>
-      <c r="D17" s="121"/>
-      <c r="E17" s="121"/>
-      <c r="F17" s="121"/>
-      <c r="G17" s="121"/>
-      <c r="H17" s="121"/>
-      <c r="I17" s="121"/>
-      <c r="L17" s="109"/>
-      <c r="M17" s="110"/>
-      <c r="N17" s="110"/>
-      <c r="O17" s="110"/>
-      <c r="P17" s="110"/>
-      <c r="Q17" s="110"/>
-      <c r="R17" s="110"/>
-      <c r="S17" s="110"/>
-      <c r="T17" s="110"/>
-    </row>
-    <row r="18" spans="1:20" s="110" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A18" s="121"/>
-      <c r="B18" s="121"/>
-      <c r="C18" s="121"/>
-      <c r="D18" s="121"/>
-      <c r="E18" s="121"/>
-      <c r="F18" s="121"/>
-      <c r="G18" s="121"/>
-      <c r="H18" s="121"/>
-      <c r="I18" s="121"/>
-    </row>
-    <row r="19" spans="1:20" s="110" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A19" s="121"/>
-      <c r="B19" s="121"/>
-      <c r="C19" s="121"/>
-      <c r="D19" s="121"/>
-      <c r="E19" s="121"/>
-      <c r="F19" s="121"/>
-      <c r="G19" s="121"/>
-      <c r="H19" s="121"/>
-      <c r="I19" s="121"/>
-      <c r="M19" s="108"/>
-      <c r="N19" s="108"/>
-      <c r="O19" s="108"/>
-      <c r="P19" s="108"/>
-      <c r="Q19" s="108"/>
-      <c r="R19" s="108"/>
-      <c r="S19" s="108"/>
-      <c r="T19" s="108"/>
-    </row>
-    <row r="20" spans="1:20" s="108" customFormat="1" ht="35.25" customHeight="1">
-      <c r="A20" s="121"/>
-      <c r="B20" s="121"/>
-      <c r="C20" s="121"/>
-      <c r="D20" s="121"/>
-      <c r="E20" s="121"/>
-      <c r="F20" s="121"/>
-      <c r="G20" s="121"/>
-      <c r="H20" s="121"/>
-      <c r="I20" s="121"/>
-      <c r="L20" s="109"/>
-    </row>
-    <row r="21" spans="1:20" s="108" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A21" s="122" t="s">
+      <c r="B17" s="116"/>
+      <c r="C17" s="116"/>
+      <c r="D17" s="116"/>
+      <c r="E17" s="116"/>
+      <c r="F17" s="116"/>
+      <c r="G17" s="116"/>
+      <c r="H17" s="116"/>
+      <c r="I17" s="116"/>
+      <c r="L17" s="107"/>
+      <c r="M17" s="108"/>
+      <c r="N17" s="108"/>
+      <c r="O17" s="108"/>
+      <c r="P17" s="108"/>
+      <c r="Q17" s="108"/>
+      <c r="R17" s="108"/>
+      <c r="S17" s="108"/>
+      <c r="T17" s="108"/>
+    </row>
+    <row r="18" spans="1:20" s="106" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A18" s="119"/>
+      <c r="B18" s="119"/>
+      <c r="C18" s="119"/>
+      <c r="D18" s="119"/>
+      <c r="E18" s="119"/>
+      <c r="F18" s="119"/>
+      <c r="G18" s="119"/>
+      <c r="H18" s="119"/>
+      <c r="I18" s="119"/>
+      <c r="L18" s="107"/>
+      <c r="M18" s="108"/>
+      <c r="N18" s="108"/>
+      <c r="O18" s="108"/>
+      <c r="P18" s="108"/>
+      <c r="Q18" s="108"/>
+      <c r="R18" s="108"/>
+      <c r="S18" s="108"/>
+      <c r="T18" s="108"/>
+    </row>
+    <row r="19" spans="1:20" s="108" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A19" s="116"/>
+      <c r="B19" s="116"/>
+      <c r="C19" s="116"/>
+      <c r="D19" s="116"/>
+      <c r="E19" s="116"/>
+      <c r="F19" s="116"/>
+      <c r="G19" s="116"/>
+      <c r="H19" s="116"/>
+      <c r="I19" s="116"/>
+    </row>
+    <row r="20" spans="1:20" s="108" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A20" s="116"/>
+      <c r="B20" s="116"/>
+      <c r="C20" s="116"/>
+      <c r="D20" s="116"/>
+      <c r="E20" s="116"/>
+      <c r="F20" s="116"/>
+      <c r="G20" s="116"/>
+      <c r="H20" s="116"/>
+      <c r="I20" s="116"/>
+      <c r="M20" s="106"/>
+      <c r="N20" s="106"/>
+      <c r="O20" s="106"/>
+      <c r="P20" s="106"/>
+      <c r="Q20" s="106"/>
+      <c r="R20" s="106"/>
+      <c r="S20" s="106"/>
+      <c r="T20" s="106"/>
+    </row>
+    <row r="21" spans="1:20" s="106" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A21" s="116"/>
+      <c r="B21" s="116"/>
+      <c r="C21" s="116"/>
+      <c r="D21" s="116"/>
+      <c r="E21" s="116"/>
+      <c r="F21" s="116"/>
+      <c r="G21" s="116"/>
+      <c r="H21" s="116"/>
+      <c r="I21" s="116"/>
+      <c r="L21" s="107"/>
+    </row>
+    <row r="22" spans="1:20" s="106" customFormat="1" ht="24.9" customHeight="1">
+      <c r="A22" s="117" t="s">
         <v>59</v>
       </c>
-      <c r="B21" s="122"/>
-      <c r="C21" s="122"/>
-      <c r="D21" s="122"/>
-      <c r="E21" s="122"/>
-      <c r="F21" s="122"/>
-      <c r="G21" s="122"/>
-      <c r="H21" s="122"/>
-      <c r="I21" s="122"/>
-      <c r="L21" s="109"/>
-    </row>
-    <row r="22" spans="1:20" s="62" customFormat="1" ht="53.25" customHeight="1">
-      <c r="A22" s="99"/>
-      <c r="B22" s="99"/>
-      <c r="C22" s="99"/>
-      <c r="D22" s="99"/>
-      <c r="E22" s="99"/>
-      <c r="F22" s="99"/>
-      <c r="G22" s="99"/>
-      <c r="H22" s="99"/>
-      <c r="I22" s="99"/>
-      <c r="O22" s="98"/>
-      <c r="P22" s="98"/>
+      <c r="B22" s="117"/>
+      <c r="C22" s="117"/>
+      <c r="D22" s="117"/>
+      <c r="E22" s="117"/>
+      <c r="F22" s="117"/>
+      <c r="G22" s="117"/>
+      <c r="H22" s="117"/>
+      <c r="I22" s="117"/>
+      <c r="L22" s="107"/>
     </row>
     <row r="23" spans="1:20" s="62" customFormat="1" ht="24" customHeight="1">
-      <c r="A23" s="158"/>
-      <c r="B23" s="158"/>
-      <c r="C23" s="158"/>
-      <c r="D23" s="158"/>
-      <c r="E23" s="158"/>
-      <c r="F23" s="158"/>
-      <c r="G23" s="158"/>
-      <c r="H23" s="158"/>
-      <c r="I23" s="158"/>
-      <c r="J23" s="159"/>
-      <c r="K23" s="159"/>
-      <c r="O23" s="98"/>
-      <c r="P23" s="98"/>
+      <c r="A23" s="156"/>
+      <c r="B23" s="156"/>
+      <c r="C23" s="156"/>
+      <c r="D23" s="156"/>
+      <c r="E23" s="156"/>
+      <c r="F23" s="156"/>
+      <c r="G23" s="156"/>
+      <c r="H23" s="156"/>
+      <c r="I23" s="156"/>
+      <c r="J23" s="115"/>
+      <c r="K23" s="115"/>
+      <c r="O23" s="96"/>
+      <c r="P23" s="96"/>
     </row>
     <row r="24" spans="1:20" s="62" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A24" s="160"/>
-      <c r="B24" s="84"/>
-      <c r="C24" s="84"/>
-      <c r="D24" s="58"/>
-      <c r="E24" s="58"/>
-      <c r="F24" s="160"/>
-      <c r="G24" s="160"/>
-      <c r="H24" s="85"/>
-      <c r="I24" s="161"/>
-      <c r="J24" s="159"/>
-      <c r="K24" s="159"/>
+      <c r="A24" s="157"/>
+      <c r="B24" s="157"/>
+      <c r="C24" s="157"/>
+      <c r="D24" s="157"/>
+      <c r="E24" s="157"/>
+      <c r="F24" s="157"/>
+      <c r="G24" s="157"/>
+      <c r="H24" s="157"/>
+      <c r="I24" s="157"/>
+      <c r="J24" s="115"/>
+      <c r="K24" s="115"/>
       <c r="M24" s="64"/>
       <c r="N24" s="64"/>
       <c r="O24" s="67"/>
@@ -2184,59 +2184,65 @@
       <c r="T24" s="64"/>
     </row>
     <row r="25" spans="1:20">
-      <c r="A25" s="87"/>
-      <c r="C25" s="88"/>
-      <c r="D25" s="89"/>
-      <c r="E25" s="89"/>
-      <c r="F25" s="87"/>
-      <c r="G25" s="87"/>
-      <c r="I25" s="86"/>
+      <c r="A25" s="158"/>
+      <c r="B25" s="158"/>
+      <c r="C25" s="158"/>
+      <c r="D25" s="158"/>
+      <c r="E25" s="158"/>
+      <c r="F25" s="158"/>
+      <c r="G25" s="158"/>
+      <c r="H25" s="158"/>
+      <c r="I25" s="158"/>
     </row>
     <row r="26" spans="1:20">
-      <c r="A26" s="87"/>
-      <c r="C26" s="88"/>
-      <c r="D26" s="89"/>
-      <c r="E26" s="89"/>
-      <c r="F26" s="87"/>
-      <c r="G26" s="87"/>
-      <c r="I26" s="86"/>
+      <c r="A26" s="85"/>
+      <c r="C26" s="86"/>
+      <c r="D26" s="87"/>
+      <c r="E26" s="87"/>
+      <c r="F26" s="85"/>
+      <c r="G26" s="85"/>
+      <c r="I26" s="84"/>
     </row>
     <row r="27" spans="1:20">
-      <c r="A27" s="87"/>
-      <c r="C27" s="88"/>
-      <c r="D27" s="89"/>
-      <c r="E27" s="89"/>
-      <c r="F27" s="87"/>
-      <c r="G27" s="87"/>
-      <c r="I27" s="86"/>
+      <c r="A27" s="85"/>
+      <c r="C27" s="86"/>
+      <c r="D27" s="87"/>
+      <c r="E27" s="87"/>
+      <c r="F27" s="85"/>
+      <c r="G27" s="85"/>
+      <c r="I27" s="84"/>
     </row>
     <row r="28" spans="1:20">
       <c r="A28" s="55"/>
       <c r="F28" s="55"/>
       <c r="G28" s="55"/>
-      <c r="I28" s="86"/>
+      <c r="I28" s="84"/>
     </row>
     <row r="29" spans="1:20">
       <c r="A29" s="69"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A20:I20"/>
-    <mergeCell ref="A21:I21"/>
-    <mergeCell ref="A16:I16"/>
-    <mergeCell ref="A17:I17"/>
+  <mergeCells count="20">
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="A24:I24"/>
+    <mergeCell ref="A25:I25"/>
     <mergeCell ref="A18:I18"/>
-    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="M8:T8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="G1:I1"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="M8:T8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A16:I16"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A20:I20"/>
   </mergeCells>
   <phoneticPr fontId="26" type="noConversion"/>
   <hyperlinks>
@@ -2274,15 +2280,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A1" s="125" t="s">
+      <c r="A1" s="151" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="125"/>
-      <c r="D1" s="125"/>
-      <c r="E1" s="125"/>
-      <c r="F1" s="125"/>
-      <c r="G1" s="125"/>
+      <c r="B1" s="151"/>
+      <c r="C1" s="151"/>
+      <c r="D1" s="151"/>
+      <c r="E1" s="151"/>
+      <c r="F1" s="151"/>
+      <c r="G1" s="151"/>
       <c r="M1" s="45"/>
       <c r="N1" s="45"/>
     </row>
@@ -2320,14 +2326,14 @@
     </row>
     <row r="5" spans="1:15" s="2" customFormat="1" ht="33" customHeight="1">
       <c r="A5" s="17"/>
-      <c r="B5" s="126" t="s">
+      <c r="B5" s="152" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="126"/>
-      <c r="D5" s="126"/>
-      <c r="E5" s="126"/>
-      <c r="F5" s="126"/>
-      <c r="G5" s="126"/>
+      <c r="C5" s="152"/>
+      <c r="D5" s="152"/>
+      <c r="E5" s="152"/>
+      <c r="F5" s="152"/>
+      <c r="G5" s="152"/>
       <c r="H5" s="18"/>
       <c r="M5" s="46"/>
       <c r="N5" s="46"/>
@@ -2347,27 +2353,27 @@
       <c r="A7" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="127" t="s">
+      <c r="B7" s="153" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="127"/>
-      <c r="D7" s="127"/>
-      <c r="E7" s="127"/>
-      <c r="F7" s="127"/>
+      <c r="C7" s="153"/>
+      <c r="D7" s="153"/>
+      <c r="E7" s="153"/>
+      <c r="F7" s="153"/>
       <c r="G7" s="20"/>
       <c r="M7" s="46"/>
       <c r="N7" s="46"/>
     </row>
     <row r="8" spans="1:15" s="2" customFormat="1" ht="54" customHeight="1">
       <c r="A8" s="17"/>
-      <c r="B8" s="128" t="s">
+      <c r="B8" s="154" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="128"/>
-      <c r="D8" s="128"/>
-      <c r="E8" s="128"/>
-      <c r="F8" s="128"/>
-      <c r="G8" s="128"/>
+      <c r="C8" s="154"/>
+      <c r="D8" s="154"/>
+      <c r="E8" s="154"/>
+      <c r="F8" s="154"/>
+      <c r="G8" s="154"/>
       <c r="M8" s="46"/>
       <c r="N8" s="46"/>
     </row>
@@ -2383,28 +2389,28 @@
       <c r="N9" s="46"/>
     </row>
     <row r="10" spans="1:15" s="3" customFormat="1" ht="49.5" customHeight="1">
-      <c r="A10" s="129" t="s">
+      <c r="A10" s="155" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="129"/>
-      <c r="C10" s="129"/>
-      <c r="D10" s="129"/>
-      <c r="E10" s="129"/>
-      <c r="F10" s="129"/>
-      <c r="G10" s="129"/>
+      <c r="B10" s="155"/>
+      <c r="C10" s="155"/>
+      <c r="D10" s="155"/>
+      <c r="E10" s="155"/>
+      <c r="F10" s="155"/>
+      <c r="G10" s="155"/>
       <c r="M10" s="4"/>
       <c r="N10" s="4"/>
     </row>
     <row r="11" spans="1:15" s="3" customFormat="1" ht="27" customHeight="1">
-      <c r="A11" s="130" t="s">
+      <c r="A11" s="148" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="130"/>
-      <c r="C11" s="130"/>
-      <c r="D11" s="130"/>
-      <c r="E11" s="130"/>
-      <c r="F11" s="130"/>
-      <c r="G11" s="130"/>
+      <c r="B11" s="148"/>
+      <c r="C11" s="148"/>
+      <c r="D11" s="148"/>
+      <c r="E11" s="148"/>
+      <c r="F11" s="148"/>
+      <c r="G11" s="148"/>
       <c r="M11" s="4"/>
       <c r="N11" s="4"/>
     </row>
@@ -2412,10 +2418,10 @@
       <c r="A12" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="131" t="s">
+      <c r="B12" s="149" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="132"/>
+      <c r="C12" s="150"/>
       <c r="D12" s="23" t="s">
         <v>5</v>
       </c>
@@ -2431,16 +2437,16 @@
       <c r="L12" s="47"/>
       <c r="M12" s="48"/>
       <c r="N12" s="49"/>
-      <c r="O12" s="143"/>
+      <c r="O12" s="133"/>
     </row>
     <row r="13" spans="1:15" s="3" customFormat="1" ht="18" customHeight="1">
       <c r="A13" s="25">
         <v>1</v>
       </c>
-      <c r="B13" s="133">
+      <c r="B13" s="145">
         <v>50655</v>
       </c>
-      <c r="C13" s="134"/>
+      <c r="C13" s="146"/>
       <c r="D13" s="26" t="s">
         <v>7</v>
       </c>
@@ -2457,16 +2463,16 @@
       <c r="J13" s="51"/>
       <c r="M13" s="4"/>
       <c r="N13" s="4"/>
-      <c r="O13" s="143"/>
+      <c r="O13" s="133"/>
     </row>
     <row r="14" spans="1:15" s="3" customFormat="1" ht="18" customHeight="1">
       <c r="A14" s="25">
         <v>2</v>
       </c>
-      <c r="B14" s="133">
+      <c r="B14" s="145">
         <v>50755</v>
       </c>
-      <c r="C14" s="134"/>
+      <c r="C14" s="146"/>
       <c r="D14" s="26" t="s">
         <v>8</v>
       </c>
@@ -2489,10 +2495,10 @@
       <c r="A15" s="25">
         <v>3</v>
       </c>
-      <c r="B15" s="133">
+      <c r="B15" s="145">
         <v>50665</v>
       </c>
-      <c r="C15" s="134"/>
+      <c r="C15" s="146"/>
       <c r="D15" s="26" t="s">
         <v>9</v>
       </c>
@@ -2515,10 +2521,10 @@
       <c r="A16" s="25">
         <v>4</v>
       </c>
-      <c r="B16" s="133">
+      <c r="B16" s="145">
         <v>50765</v>
       </c>
-      <c r="C16" s="134"/>
+      <c r="C16" s="146"/>
       <c r="D16" s="26" t="s">
         <v>10</v>
       </c>
@@ -2541,10 +2547,10 @@
       <c r="A17" s="25">
         <v>5</v>
       </c>
-      <c r="B17" s="133">
+      <c r="B17" s="145">
         <v>50720</v>
       </c>
-      <c r="C17" s="134"/>
+      <c r="C17" s="146"/>
       <c r="D17" s="26" t="s">
         <v>11</v>
       </c>
@@ -2567,10 +2573,10 @@
       <c r="A18" s="30">
         <v>6</v>
       </c>
-      <c r="B18" s="133">
+      <c r="B18" s="145">
         <v>50730</v>
       </c>
-      <c r="C18" s="134"/>
+      <c r="C18" s="146"/>
       <c r="D18" s="31" t="s">
         <v>12</v>
       </c>
@@ -2590,54 +2596,54 @@
       <c r="O18" s="50"/>
     </row>
     <row r="19" spans="1:15" s="4" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A19" s="144" t="s">
+      <c r="A19" s="134" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="145"/>
-      <c r="C19" s="146"/>
+      <c r="B19" s="135"/>
+      <c r="C19" s="136"/>
       <c r="D19" s="32"/>
-      <c r="E19" s="137">
+      <c r="E19" s="127">
         <f>SUM(E13:E18)</f>
         <v>6000</v>
       </c>
-      <c r="F19" s="139"/>
-      <c r="G19" s="141">
+      <c r="F19" s="129"/>
+      <c r="G19" s="131">
         <f>SUM(G13:G18)</f>
         <v>73120</v>
       </c>
       <c r="H19" s="33"/>
     </row>
     <row r="20" spans="1:15" s="4" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A20" s="147"/>
-      <c r="B20" s="148"/>
-      <c r="C20" s="149"/>
+      <c r="A20" s="137"/>
+      <c r="B20" s="138"/>
+      <c r="C20" s="139"/>
       <c r="D20" s="34"/>
-      <c r="E20" s="138"/>
-      <c r="F20" s="140"/>
-      <c r="G20" s="142"/>
+      <c r="E20" s="128"/>
+      <c r="F20" s="130"/>
+      <c r="G20" s="132"/>
     </row>
     <row r="21" spans="1:15" s="4" customFormat="1" ht="30" hidden="1" customHeight="1">
-      <c r="A21" s="135" t="s">
+      <c r="A21" s="147" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="135"/>
-      <c r="C21" s="135"/>
-      <c r="D21" s="135"/>
-      <c r="E21" s="135"/>
-      <c r="F21" s="135"/>
-      <c r="G21" s="135"/>
+      <c r="B21" s="147"/>
+      <c r="C21" s="147"/>
+      <c r="D21" s="147"/>
+      <c r="E21" s="147"/>
+      <c r="F21" s="147"/>
+      <c r="G21" s="147"/>
       <c r="J21" s="52"/>
     </row>
     <row r="22" spans="1:15" s="4" customFormat="1" ht="30" customHeight="1">
-      <c r="A22" s="136" t="s">
+      <c r="A22" s="126" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="136"/>
-      <c r="C22" s="136"/>
-      <c r="D22" s="136"/>
-      <c r="E22" s="136"/>
-      <c r="F22" s="136"/>
-      <c r="G22" s="136"/>
+      <c r="B22" s="126"/>
+      <c r="C22" s="126"/>
+      <c r="D22" s="126"/>
+      <c r="E22" s="126"/>
+      <c r="F22" s="126"/>
+      <c r="G22" s="126"/>
       <c r="J22" s="52"/>
     </row>
     <row r="23" spans="1:15" s="4" customFormat="1" ht="21.75" customHeight="1">
@@ -2687,15 +2693,15 @@
       <c r="J26" s="52"/>
     </row>
     <row r="27" spans="1:15" s="4" customFormat="1" ht="30" customHeight="1">
-      <c r="A27" s="136" t="s">
+      <c r="A27" s="126" t="s">
         <v>34</v>
       </c>
-      <c r="B27" s="136"/>
-      <c r="C27" s="136"/>
-      <c r="D27" s="136"/>
-      <c r="E27" s="136"/>
-      <c r="F27" s="136"/>
-      <c r="G27" s="136"/>
+      <c r="B27" s="126"/>
+      <c r="C27" s="126"/>
+      <c r="D27" s="126"/>
+      <c r="E27" s="126"/>
+      <c r="F27" s="126"/>
+      <c r="G27" s="126"/>
       <c r="J27" s="52"/>
     </row>
     <row r="28" spans="1:15" s="5" customFormat="1" ht="19.5" customHeight="1">
@@ -2759,15 +2765,15 @@
       <c r="N33" s="54"/>
     </row>
     <row r="34" spans="1:14" s="4" customFormat="1" ht="30" customHeight="1">
-      <c r="A34" s="136" t="s">
+      <c r="A34" s="126" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="136"/>
-      <c r="C34" s="136"/>
-      <c r="D34" s="136"/>
-      <c r="E34" s="136"/>
-      <c r="F34" s="136"/>
-      <c r="G34" s="136"/>
+      <c r="B34" s="126"/>
+      <c r="C34" s="126"/>
+      <c r="D34" s="126"/>
+      <c r="E34" s="126"/>
+      <c r="F34" s="126"/>
+      <c r="G34" s="126"/>
       <c r="J34" s="52"/>
     </row>
     <row r="35" spans="1:14" s="5" customFormat="1" ht="19.5" customHeight="1">
@@ -2791,15 +2797,15 @@
       <c r="N36" s="53"/>
     </row>
     <row r="37" spans="1:14" s="4" customFormat="1" ht="30" customHeight="1">
-      <c r="A37" s="136" t="s">
+      <c r="A37" s="126" t="s">
         <v>44</v>
       </c>
-      <c r="B37" s="136"/>
-      <c r="C37" s="136"/>
-      <c r="D37" s="136"/>
-      <c r="E37" s="136"/>
-      <c r="F37" s="136"/>
-      <c r="G37" s="136"/>
+      <c r="B37" s="126"/>
+      <c r="C37" s="126"/>
+      <c r="D37" s="126"/>
+      <c r="E37" s="126"/>
+      <c r="F37" s="126"/>
+      <c r="G37" s="126"/>
       <c r="J37" s="52"/>
     </row>
     <row r="38" spans="1:14" s="6" customFormat="1" ht="19.5" customHeight="1">
@@ -2823,40 +2829,40 @@
       <c r="N39" s="54"/>
     </row>
     <row r="40" spans="1:14" s="4" customFormat="1" ht="30" customHeight="1">
-      <c r="A40" s="136" t="s">
+      <c r="A40" s="126" t="s">
         <v>47</v>
       </c>
-      <c r="B40" s="136"/>
-      <c r="C40" s="136"/>
-      <c r="D40" s="136"/>
-      <c r="E40" s="136"/>
-      <c r="F40" s="136"/>
-      <c r="G40" s="136"/>
+      <c r="B40" s="126"/>
+      <c r="C40" s="126"/>
+      <c r="D40" s="126"/>
+      <c r="E40" s="126"/>
+      <c r="F40" s="126"/>
+      <c r="G40" s="126"/>
       <c r="J40" s="52"/>
     </row>
     <row r="41" spans="1:14" s="6" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A41" s="154" t="s">
+      <c r="A41" s="144" t="s">
         <v>48</v>
       </c>
-      <c r="B41" s="154"/>
-      <c r="C41" s="154"/>
-      <c r="D41" s="154"/>
-      <c r="E41" s="154"/>
-      <c r="F41" s="154"/>
-      <c r="G41" s="154"/>
+      <c r="B41" s="144"/>
+      <c r="C41" s="144"/>
+      <c r="D41" s="144"/>
+      <c r="E41" s="144"/>
+      <c r="F41" s="144"/>
+      <c r="G41" s="144"/>
       <c r="M41" s="54"/>
       <c r="N41" s="54"/>
     </row>
     <row r="42" spans="1:14" s="6" customFormat="1" ht="44.25" customHeight="1">
-      <c r="A42" s="150" t="s">
+      <c r="A42" s="140" t="s">
         <v>49</v>
       </c>
-      <c r="B42" s="150"/>
-      <c r="C42" s="150"/>
-      <c r="D42" s="150"/>
-      <c r="E42" s="150"/>
-      <c r="F42" s="150"/>
-      <c r="G42" s="150"/>
+      <c r="B42" s="140"/>
+      <c r="C42" s="140"/>
+      <c r="D42" s="140"/>
+      <c r="E42" s="140"/>
+      <c r="F42" s="140"/>
+      <c r="G42" s="140"/>
       <c r="M42" s="54"/>
       <c r="N42" s="54"/>
     </row>
@@ -2871,27 +2877,27 @@
       <c r="J43" s="52"/>
     </row>
     <row r="44" spans="1:14" s="4" customFormat="1" ht="30" customHeight="1">
-      <c r="A44" s="136" t="s">
+      <c r="A44" s="126" t="s">
         <v>50</v>
       </c>
-      <c r="B44" s="136"/>
-      <c r="C44" s="136"/>
-      <c r="D44" s="136"/>
-      <c r="E44" s="136"/>
-      <c r="F44" s="136"/>
-      <c r="G44" s="136"/>
+      <c r="B44" s="126"/>
+      <c r="C44" s="126"/>
+      <c r="D44" s="126"/>
+      <c r="E44" s="126"/>
+      <c r="F44" s="126"/>
+      <c r="G44" s="126"/>
       <c r="J44" s="52"/>
     </row>
     <row r="45" spans="1:14" s="6" customFormat="1" ht="58.5" customHeight="1">
-      <c r="A45" s="151" t="s">
+      <c r="A45" s="141" t="s">
         <v>51</v>
       </c>
-      <c r="B45" s="152"/>
-      <c r="C45" s="152"/>
-      <c r="D45" s="152"/>
-      <c r="E45" s="152"/>
-      <c r="F45" s="152"/>
-      <c r="G45" s="152"/>
+      <c r="B45" s="142"/>
+      <c r="C45" s="142"/>
+      <c r="D45" s="142"/>
+      <c r="E45" s="142"/>
+      <c r="F45" s="142"/>
+      <c r="G45" s="142"/>
       <c r="M45" s="54"/>
       <c r="N45" s="54"/>
     </row>
@@ -2906,27 +2912,27 @@
       <c r="J46" s="52"/>
     </row>
     <row r="47" spans="1:14" s="4" customFormat="1" ht="30" customHeight="1">
-      <c r="A47" s="136" t="s">
+      <c r="A47" s="126" t="s">
         <v>52</v>
       </c>
-      <c r="B47" s="136"/>
-      <c r="C47" s="136"/>
-      <c r="D47" s="136"/>
-      <c r="E47" s="136"/>
-      <c r="F47" s="136"/>
-      <c r="G47" s="136"/>
+      <c r="B47" s="126"/>
+      <c r="C47" s="126"/>
+      <c r="D47" s="126"/>
+      <c r="E47" s="126"/>
+      <c r="F47" s="126"/>
+      <c r="G47" s="126"/>
       <c r="J47" s="52"/>
     </row>
     <row r="48" spans="1:14" s="6" customFormat="1" ht="46.5" customHeight="1">
-      <c r="A48" s="153" t="s">
+      <c r="A48" s="143" t="s">
         <v>53</v>
       </c>
-      <c r="B48" s="153"/>
-      <c r="C48" s="153"/>
-      <c r="D48" s="153"/>
-      <c r="E48" s="153"/>
-      <c r="F48" s="153"/>
-      <c r="G48" s="153"/>
+      <c r="B48" s="143"/>
+      <c r="C48" s="143"/>
+      <c r="D48" s="143"/>
+      <c r="E48" s="143"/>
+      <c r="F48" s="143"/>
+      <c r="G48" s="143"/>
       <c r="M48" s="54"/>
       <c r="N48" s="54"/>
     </row>
@@ -2939,15 +2945,15 @@
       <c r="N49" s="54"/>
     </row>
     <row r="50" spans="1:14" s="6" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A50" s="136" t="s">
+      <c r="A50" s="126" t="s">
         <v>54</v>
       </c>
-      <c r="B50" s="136"/>
-      <c r="C50" s="136"/>
-      <c r="D50" s="136"/>
-      <c r="E50" s="136"/>
-      <c r="F50" s="136"/>
-      <c r="G50" s="136"/>
+      <c r="B50" s="126"/>
+      <c r="C50" s="126"/>
+      <c r="D50" s="126"/>
+      <c r="E50" s="126"/>
+      <c r="F50" s="126"/>
+      <c r="G50" s="126"/>
       <c r="M50" s="54"/>
       <c r="N50" s="54"/>
     </row>
@@ -3003,6 +3009,21 @@
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A22:G22"/>
     <mergeCell ref="A50:G50"/>
     <mergeCell ref="E19:E20"/>
     <mergeCell ref="F19:F20"/>
@@ -3019,21 +3040,6 @@
     <mergeCell ref="A37:G37"/>
     <mergeCell ref="A40:G40"/>
     <mergeCell ref="A41:G41"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B8:G8"/>
-    <mergeCell ref="A10:G10"/>
   </mergeCells>
   <phoneticPr fontId="26" type="noConversion"/>
   <printOptions horizontalCentered="1"/>

--- a/excel-template/PO-template.xlsx
+++ b/excel-template/PO-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\exportcrm\excel-template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A73E2B2-5D05-4E2A-8F74-D1D234C848C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C635979A-D64B-4D65-A0D4-F56874E2BD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="813" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1240,9 +1240,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="186" fontId="34" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -1254,126 +1251,6 @@
     </xf>
     <xf numFmtId="43" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="16" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="32" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="15" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="19" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="11" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="11" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1381,6 +1258,129 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="19" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="16" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="32" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="15" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="11" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="11" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="186" fontId="34" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1776,7 +1776,7 @@
       <c r="I2" s="122"/>
     </row>
     <row r="3" spans="1:20" s="56" customFormat="1" ht="21.75" customHeight="1">
-      <c r="A3" s="113" t="s">
+      <c r="A3" s="112" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="70"/>
@@ -1788,7 +1788,7 @@
       <c r="H3" s="106" t="s">
         <v>64</v>
       </c>
-      <c r="I3" s="114" t="s">
+      <c r="I3" s="113" t="s">
         <v>59</v>
       </c>
       <c r="O3" s="71"/>
@@ -1809,7 +1809,7 @@
       <c r="R4" s="77"/>
     </row>
     <row r="5" spans="1:20" s="57" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A5" s="112" t="s">
+      <c r="A5" s="111" t="s">
         <v>75</v>
       </c>
       <c r="C5" s="72"/>
@@ -1895,14 +1895,14 @@
       <c r="I8" s="82" t="s">
         <v>70</v>
       </c>
-      <c r="M8" s="125"/>
-      <c r="N8" s="125"/>
-      <c r="O8" s="125"/>
-      <c r="P8" s="125"/>
-      <c r="Q8" s="125"/>
-      <c r="R8" s="125"/>
-      <c r="S8" s="125"/>
-      <c r="T8" s="125"/>
+      <c r="M8" s="119"/>
+      <c r="N8" s="119"/>
+      <c r="O8" s="119"/>
+      <c r="P8" s="119"/>
+      <c r="Q8" s="119"/>
+      <c r="R8" s="119"/>
+      <c r="S8" s="119"/>
+      <c r="T8" s="119"/>
     </row>
     <row r="9" spans="1:20" s="58" customFormat="1" ht="24.9" customHeight="1">
       <c r="A9" s="99"/>
@@ -2029,38 +2029,38 @@
       <c r="H15" s="110" t="s">
         <v>62</v>
       </c>
-      <c r="I15" s="111">
+      <c r="I15" s="158">
         <f>I14+I13</f>
         <v>0</v>
       </c>
       <c r="J15" s="83"/>
     </row>
     <row r="16" spans="1:20" s="60" customFormat="1" ht="30" customHeight="1">
-      <c r="A16" s="118" t="s">
+      <c r="A16" s="127" t="s">
         <v>71</v>
       </c>
-      <c r="B16" s="118"/>
-      <c r="C16" s="118"/>
-      <c r="D16" s="118"/>
-      <c r="E16" s="118"/>
-      <c r="F16" s="118"/>
-      <c r="G16" s="118"/>
-      <c r="H16" s="118"/>
-      <c r="I16" s="118"/>
+      <c r="B16" s="127"/>
+      <c r="C16" s="127"/>
+      <c r="D16" s="127"/>
+      <c r="E16" s="127"/>
+      <c r="F16" s="127"/>
+      <c r="G16" s="127"/>
+      <c r="H16" s="127"/>
+      <c r="I16" s="127"/>
       <c r="L16" s="95"/>
     </row>
     <row r="17" spans="1:20" s="106" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A17" s="119" t="s">
+      <c r="A17" s="118" t="s">
         <v>76</v>
       </c>
-      <c r="B17" s="116"/>
-      <c r="C17" s="116"/>
-      <c r="D17" s="116"/>
-      <c r="E17" s="116"/>
-      <c r="F17" s="116"/>
-      <c r="G17" s="116"/>
-      <c r="H17" s="116"/>
-      <c r="I17" s="116"/>
+      <c r="B17" s="125"/>
+      <c r="C17" s="125"/>
+      <c r="D17" s="125"/>
+      <c r="E17" s="125"/>
+      <c r="F17" s="125"/>
+      <c r="G17" s="125"/>
+      <c r="H17" s="125"/>
+      <c r="I17" s="125"/>
       <c r="L17" s="107"/>
       <c r="M17" s="108"/>
       <c r="N17" s="108"/>
@@ -2072,15 +2072,15 @@
       <c r="T17" s="108"/>
     </row>
     <row r="18" spans="1:20" s="106" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A18" s="119"/>
-      <c r="B18" s="119"/>
-      <c r="C18" s="119"/>
-      <c r="D18" s="119"/>
-      <c r="E18" s="119"/>
-      <c r="F18" s="119"/>
-      <c r="G18" s="119"/>
-      <c r="H18" s="119"/>
-      <c r="I18" s="119"/>
+      <c r="A18" s="118"/>
+      <c r="B18" s="118"/>
+      <c r="C18" s="118"/>
+      <c r="D18" s="118"/>
+      <c r="E18" s="118"/>
+      <c r="F18" s="118"/>
+      <c r="G18" s="118"/>
+      <c r="H18" s="118"/>
+      <c r="I18" s="118"/>
       <c r="L18" s="107"/>
       <c r="M18" s="108"/>
       <c r="N18" s="108"/>
@@ -2092,26 +2092,26 @@
       <c r="T18" s="108"/>
     </row>
     <row r="19" spans="1:20" s="108" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A19" s="116"/>
-      <c r="B19" s="116"/>
-      <c r="C19" s="116"/>
-      <c r="D19" s="116"/>
-      <c r="E19" s="116"/>
-      <c r="F19" s="116"/>
-      <c r="G19" s="116"/>
-      <c r="H19" s="116"/>
-      <c r="I19" s="116"/>
+      <c r="A19" s="125"/>
+      <c r="B19" s="125"/>
+      <c r="C19" s="125"/>
+      <c r="D19" s="125"/>
+      <c r="E19" s="125"/>
+      <c r="F19" s="125"/>
+      <c r="G19" s="125"/>
+      <c r="H19" s="125"/>
+      <c r="I19" s="125"/>
     </row>
     <row r="20" spans="1:20" s="108" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A20" s="116"/>
-      <c r="B20" s="116"/>
-      <c r="C20" s="116"/>
-      <c r="D20" s="116"/>
-      <c r="E20" s="116"/>
-      <c r="F20" s="116"/>
-      <c r="G20" s="116"/>
-      <c r="H20" s="116"/>
-      <c r="I20" s="116"/>
+      <c r="A20" s="125"/>
+      <c r="B20" s="125"/>
+      <c r="C20" s="125"/>
+      <c r="D20" s="125"/>
+      <c r="E20" s="125"/>
+      <c r="F20" s="125"/>
+      <c r="G20" s="125"/>
+      <c r="H20" s="125"/>
+      <c r="I20" s="125"/>
       <c r="M20" s="106"/>
       <c r="N20" s="106"/>
       <c r="O20" s="106"/>
@@ -2122,58 +2122,58 @@
       <c r="T20" s="106"/>
     </row>
     <row r="21" spans="1:20" s="106" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A21" s="116"/>
-      <c r="B21" s="116"/>
-      <c r="C21" s="116"/>
-      <c r="D21" s="116"/>
-      <c r="E21" s="116"/>
-      <c r="F21" s="116"/>
-      <c r="G21" s="116"/>
-      <c r="H21" s="116"/>
-      <c r="I21" s="116"/>
+      <c r="A21" s="125"/>
+      <c r="B21" s="125"/>
+      <c r="C21" s="125"/>
+      <c r="D21" s="125"/>
+      <c r="E21" s="125"/>
+      <c r="F21" s="125"/>
+      <c r="G21" s="125"/>
+      <c r="H21" s="125"/>
+      <c r="I21" s="125"/>
       <c r="L21" s="107"/>
     </row>
     <row r="22" spans="1:20" s="106" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A22" s="117" t="s">
+      <c r="A22" s="126" t="s">
         <v>59</v>
       </c>
-      <c r="B22" s="117"/>
-      <c r="C22" s="117"/>
-      <c r="D22" s="117"/>
-      <c r="E22" s="117"/>
-      <c r="F22" s="117"/>
-      <c r="G22" s="117"/>
-      <c r="H22" s="117"/>
-      <c r="I22" s="117"/>
+      <c r="B22" s="126"/>
+      <c r="C22" s="126"/>
+      <c r="D22" s="126"/>
+      <c r="E22" s="126"/>
+      <c r="F22" s="126"/>
+      <c r="G22" s="126"/>
+      <c r="H22" s="126"/>
+      <c r="I22" s="126"/>
       <c r="L22" s="107"/>
     </row>
     <row r="23" spans="1:20" s="62" customFormat="1" ht="24" customHeight="1">
-      <c r="A23" s="156"/>
-      <c r="B23" s="156"/>
-      <c r="C23" s="156"/>
-      <c r="D23" s="156"/>
-      <c r="E23" s="156"/>
-      <c r="F23" s="156"/>
-      <c r="G23" s="156"/>
-      <c r="H23" s="156"/>
-      <c r="I23" s="156"/>
-      <c r="J23" s="115"/>
-      <c r="K23" s="115"/>
+      <c r="A23" s="115"/>
+      <c r="B23" s="115"/>
+      <c r="C23" s="115"/>
+      <c r="D23" s="115"/>
+      <c r="E23" s="115"/>
+      <c r="F23" s="115"/>
+      <c r="G23" s="115"/>
+      <c r="H23" s="115"/>
+      <c r="I23" s="115"/>
+      <c r="J23" s="114"/>
+      <c r="K23" s="114"/>
       <c r="O23" s="96"/>
       <c r="P23" s="96"/>
     </row>
     <row r="24" spans="1:20" s="62" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A24" s="157"/>
-      <c r="B24" s="157"/>
-      <c r="C24" s="157"/>
-      <c r="D24" s="157"/>
-      <c r="E24" s="157"/>
-      <c r="F24" s="157"/>
-      <c r="G24" s="157"/>
-      <c r="H24" s="157"/>
-      <c r="I24" s="157"/>
-      <c r="J24" s="115"/>
-      <c r="K24" s="115"/>
+      <c r="A24" s="116"/>
+      <c r="B24" s="116"/>
+      <c r="C24" s="116"/>
+      <c r="D24" s="116"/>
+      <c r="E24" s="116"/>
+      <c r="F24" s="116"/>
+      <c r="G24" s="116"/>
+      <c r="H24" s="116"/>
+      <c r="I24" s="116"/>
+      <c r="J24" s="114"/>
+      <c r="K24" s="114"/>
       <c r="M24" s="64"/>
       <c r="N24" s="64"/>
       <c r="O24" s="67"/>
@@ -2184,15 +2184,15 @@
       <c r="T24" s="64"/>
     </row>
     <row r="25" spans="1:20">
-      <c r="A25" s="158"/>
-      <c r="B25" s="158"/>
-      <c r="C25" s="158"/>
-      <c r="D25" s="158"/>
-      <c r="E25" s="158"/>
-      <c r="F25" s="158"/>
-      <c r="G25" s="158"/>
-      <c r="H25" s="158"/>
-      <c r="I25" s="158"/>
+      <c r="A25" s="117"/>
+      <c r="B25" s="117"/>
+      <c r="C25" s="117"/>
+      <c r="D25" s="117"/>
+      <c r="E25" s="117"/>
+      <c r="F25" s="117"/>
+      <c r="G25" s="117"/>
+      <c r="H25" s="117"/>
+      <c r="I25" s="117"/>
     </row>
     <row r="26" spans="1:20">
       <c r="A26" s="85"/>
@@ -2223,6 +2223,15 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A16:I16"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A20:I20"/>
     <mergeCell ref="A23:I23"/>
     <mergeCell ref="A24:I24"/>
     <mergeCell ref="A25:I25"/>
@@ -2234,15 +2243,6 @@
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="A21:I21"/>
-    <mergeCell ref="A22:I22"/>
-    <mergeCell ref="A16:I16"/>
-    <mergeCell ref="A17:I17"/>
-    <mergeCell ref="A19:I19"/>
-    <mergeCell ref="A20:I20"/>
   </mergeCells>
   <phoneticPr fontId="26" type="noConversion"/>
   <hyperlinks>
@@ -2280,15 +2280,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A1" s="151" t="s">
+      <c r="A1" s="128" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="151"/>
-      <c r="C1" s="151"/>
-      <c r="D1" s="151"/>
-      <c r="E1" s="151"/>
-      <c r="F1" s="151"/>
-      <c r="G1" s="151"/>
+      <c r="B1" s="128"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
+      <c r="E1" s="128"/>
+      <c r="F1" s="128"/>
+      <c r="G1" s="128"/>
       <c r="M1" s="45"/>
       <c r="N1" s="45"/>
     </row>
@@ -2326,14 +2326,14 @@
     </row>
     <row r="5" spans="1:15" s="2" customFormat="1" ht="33" customHeight="1">
       <c r="A5" s="17"/>
-      <c r="B5" s="152" t="s">
+      <c r="B5" s="129" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="152"/>
-      <c r="D5" s="152"/>
-      <c r="E5" s="152"/>
-      <c r="F5" s="152"/>
-      <c r="G5" s="152"/>
+      <c r="C5" s="129"/>
+      <c r="D5" s="129"/>
+      <c r="E5" s="129"/>
+      <c r="F5" s="129"/>
+      <c r="G5" s="129"/>
       <c r="H5" s="18"/>
       <c r="M5" s="46"/>
       <c r="N5" s="46"/>
@@ -2353,27 +2353,27 @@
       <c r="A7" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="153" t="s">
+      <c r="B7" s="130" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="153"/>
-      <c r="D7" s="153"/>
-      <c r="E7" s="153"/>
-      <c r="F7" s="153"/>
+      <c r="C7" s="130"/>
+      <c r="D7" s="130"/>
+      <c r="E7" s="130"/>
+      <c r="F7" s="130"/>
       <c r="G7" s="20"/>
       <c r="M7" s="46"/>
       <c r="N7" s="46"/>
     </row>
     <row r="8" spans="1:15" s="2" customFormat="1" ht="54" customHeight="1">
       <c r="A8" s="17"/>
-      <c r="B8" s="154" t="s">
+      <c r="B8" s="131" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="154"/>
-      <c r="D8" s="154"/>
-      <c r="E8" s="154"/>
-      <c r="F8" s="154"/>
-      <c r="G8" s="154"/>
+      <c r="C8" s="131"/>
+      <c r="D8" s="131"/>
+      <c r="E8" s="131"/>
+      <c r="F8" s="131"/>
+      <c r="G8" s="131"/>
       <c r="M8" s="46"/>
       <c r="N8" s="46"/>
     </row>
@@ -2389,28 +2389,28 @@
       <c r="N9" s="46"/>
     </row>
     <row r="10" spans="1:15" s="3" customFormat="1" ht="49.5" customHeight="1">
-      <c r="A10" s="155" t="s">
+      <c r="A10" s="132" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="155"/>
-      <c r="C10" s="155"/>
-      <c r="D10" s="155"/>
-      <c r="E10" s="155"/>
-      <c r="F10" s="155"/>
-      <c r="G10" s="155"/>
+      <c r="B10" s="132"/>
+      <c r="C10" s="132"/>
+      <c r="D10" s="132"/>
+      <c r="E10" s="132"/>
+      <c r="F10" s="132"/>
+      <c r="G10" s="132"/>
       <c r="M10" s="4"/>
       <c r="N10" s="4"/>
     </row>
     <row r="11" spans="1:15" s="3" customFormat="1" ht="27" customHeight="1">
-      <c r="A11" s="148" t="s">
+      <c r="A11" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="148"/>
-      <c r="C11" s="148"/>
-      <c r="D11" s="148"/>
-      <c r="E11" s="148"/>
-      <c r="F11" s="148"/>
-      <c r="G11" s="148"/>
+      <c r="B11" s="133"/>
+      <c r="C11" s="133"/>
+      <c r="D11" s="133"/>
+      <c r="E11" s="133"/>
+      <c r="F11" s="133"/>
+      <c r="G11" s="133"/>
       <c r="M11" s="4"/>
       <c r="N11" s="4"/>
     </row>
@@ -2418,10 +2418,10 @@
       <c r="A12" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="149" t="s">
+      <c r="B12" s="134" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="150"/>
+      <c r="C12" s="135"/>
       <c r="D12" s="23" t="s">
         <v>5</v>
       </c>
@@ -2437,16 +2437,16 @@
       <c r="L12" s="47"/>
       <c r="M12" s="48"/>
       <c r="N12" s="49"/>
-      <c r="O12" s="133"/>
+      <c r="O12" s="146"/>
     </row>
     <row r="13" spans="1:15" s="3" customFormat="1" ht="18" customHeight="1">
       <c r="A13" s="25">
         <v>1</v>
       </c>
-      <c r="B13" s="145">
+      <c r="B13" s="136">
         <v>50655</v>
       </c>
-      <c r="C13" s="146"/>
+      <c r="C13" s="137"/>
       <c r="D13" s="26" t="s">
         <v>7</v>
       </c>
@@ -2463,16 +2463,16 @@
       <c r="J13" s="51"/>
       <c r="M13" s="4"/>
       <c r="N13" s="4"/>
-      <c r="O13" s="133"/>
+      <c r="O13" s="146"/>
     </row>
     <row r="14" spans="1:15" s="3" customFormat="1" ht="18" customHeight="1">
       <c r="A14" s="25">
         <v>2</v>
       </c>
-      <c r="B14" s="145">
+      <c r="B14" s="136">
         <v>50755</v>
       </c>
-      <c r="C14" s="146"/>
+      <c r="C14" s="137"/>
       <c r="D14" s="26" t="s">
         <v>8</v>
       </c>
@@ -2495,10 +2495,10 @@
       <c r="A15" s="25">
         <v>3</v>
       </c>
-      <c r="B15" s="145">
+      <c r="B15" s="136">
         <v>50665</v>
       </c>
-      <c r="C15" s="146"/>
+      <c r="C15" s="137"/>
       <c r="D15" s="26" t="s">
         <v>9</v>
       </c>
@@ -2521,10 +2521,10 @@
       <c r="A16" s="25">
         <v>4</v>
       </c>
-      <c r="B16" s="145">
+      <c r="B16" s="136">
         <v>50765</v>
       </c>
-      <c r="C16" s="146"/>
+      <c r="C16" s="137"/>
       <c r="D16" s="26" t="s">
         <v>10</v>
       </c>
@@ -2547,10 +2547,10 @@
       <c r="A17" s="25">
         <v>5</v>
       </c>
-      <c r="B17" s="145">
+      <c r="B17" s="136">
         <v>50720</v>
       </c>
-      <c r="C17" s="146"/>
+      <c r="C17" s="137"/>
       <c r="D17" s="26" t="s">
         <v>11</v>
       </c>
@@ -2573,10 +2573,10 @@
       <c r="A18" s="30">
         <v>6</v>
       </c>
-      <c r="B18" s="145">
+      <c r="B18" s="136">
         <v>50730</v>
       </c>
-      <c r="C18" s="146"/>
+      <c r="C18" s="137"/>
       <c r="D18" s="31" t="s">
         <v>12</v>
       </c>
@@ -2596,54 +2596,54 @@
       <c r="O18" s="50"/>
     </row>
     <row r="19" spans="1:15" s="4" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A19" s="134" t="s">
+      <c r="A19" s="147" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="135"/>
-      <c r="C19" s="136"/>
+      <c r="B19" s="148"/>
+      <c r="C19" s="149"/>
       <c r="D19" s="32"/>
-      <c r="E19" s="127">
+      <c r="E19" s="140">
         <f>SUM(E13:E18)</f>
         <v>6000</v>
       </c>
-      <c r="F19" s="129"/>
-      <c r="G19" s="131">
+      <c r="F19" s="142"/>
+      <c r="G19" s="144">
         <f>SUM(G13:G18)</f>
         <v>73120</v>
       </c>
       <c r="H19" s="33"/>
     </row>
     <row r="20" spans="1:15" s="4" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A20" s="137"/>
-      <c r="B20" s="138"/>
-      <c r="C20" s="139"/>
+      <c r="A20" s="150"/>
+      <c r="B20" s="151"/>
+      <c r="C20" s="152"/>
       <c r="D20" s="34"/>
-      <c r="E20" s="128"/>
-      <c r="F20" s="130"/>
-      <c r="G20" s="132"/>
+      <c r="E20" s="141"/>
+      <c r="F20" s="143"/>
+      <c r="G20" s="145"/>
     </row>
     <row r="21" spans="1:15" s="4" customFormat="1" ht="30" hidden="1" customHeight="1">
-      <c r="A21" s="147" t="s">
+      <c r="A21" s="138" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="147"/>
-      <c r="C21" s="147"/>
-      <c r="D21" s="147"/>
-      <c r="E21" s="147"/>
-      <c r="F21" s="147"/>
-      <c r="G21" s="147"/>
+      <c r="B21" s="138"/>
+      <c r="C21" s="138"/>
+      <c r="D21" s="138"/>
+      <c r="E21" s="138"/>
+      <c r="F21" s="138"/>
+      <c r="G21" s="138"/>
       <c r="J21" s="52"/>
     </row>
     <row r="22" spans="1:15" s="4" customFormat="1" ht="30" customHeight="1">
-      <c r="A22" s="126" t="s">
+      <c r="A22" s="139" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="126"/>
-      <c r="C22" s="126"/>
-      <c r="D22" s="126"/>
-      <c r="E22" s="126"/>
-      <c r="F22" s="126"/>
-      <c r="G22" s="126"/>
+      <c r="B22" s="139"/>
+      <c r="C22" s="139"/>
+      <c r="D22" s="139"/>
+      <c r="E22" s="139"/>
+      <c r="F22" s="139"/>
+      <c r="G22" s="139"/>
       <c r="J22" s="52"/>
     </row>
     <row r="23" spans="1:15" s="4" customFormat="1" ht="21.75" customHeight="1">
@@ -2693,15 +2693,15 @@
       <c r="J26" s="52"/>
     </row>
     <row r="27" spans="1:15" s="4" customFormat="1" ht="30" customHeight="1">
-      <c r="A27" s="126" t="s">
+      <c r="A27" s="139" t="s">
         <v>34</v>
       </c>
-      <c r="B27" s="126"/>
-      <c r="C27" s="126"/>
-      <c r="D27" s="126"/>
-      <c r="E27" s="126"/>
-      <c r="F27" s="126"/>
-      <c r="G27" s="126"/>
+      <c r="B27" s="139"/>
+      <c r="C27" s="139"/>
+      <c r="D27" s="139"/>
+      <c r="E27" s="139"/>
+      <c r="F27" s="139"/>
+      <c r="G27" s="139"/>
       <c r="J27" s="52"/>
     </row>
     <row r="28" spans="1:15" s="5" customFormat="1" ht="19.5" customHeight="1">
@@ -2765,15 +2765,15 @@
       <c r="N33" s="54"/>
     </row>
     <row r="34" spans="1:14" s="4" customFormat="1" ht="30" customHeight="1">
-      <c r="A34" s="126" t="s">
+      <c r="A34" s="139" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="126"/>
-      <c r="C34" s="126"/>
-      <c r="D34" s="126"/>
-      <c r="E34" s="126"/>
-      <c r="F34" s="126"/>
-      <c r="G34" s="126"/>
+      <c r="B34" s="139"/>
+      <c r="C34" s="139"/>
+      <c r="D34" s="139"/>
+      <c r="E34" s="139"/>
+      <c r="F34" s="139"/>
+      <c r="G34" s="139"/>
       <c r="J34" s="52"/>
     </row>
     <row r="35" spans="1:14" s="5" customFormat="1" ht="19.5" customHeight="1">
@@ -2797,15 +2797,15 @@
       <c r="N36" s="53"/>
     </row>
     <row r="37" spans="1:14" s="4" customFormat="1" ht="30" customHeight="1">
-      <c r="A37" s="126" t="s">
+      <c r="A37" s="139" t="s">
         <v>44</v>
       </c>
-      <c r="B37" s="126"/>
-      <c r="C37" s="126"/>
-      <c r="D37" s="126"/>
-      <c r="E37" s="126"/>
-      <c r="F37" s="126"/>
-      <c r="G37" s="126"/>
+      <c r="B37" s="139"/>
+      <c r="C37" s="139"/>
+      <c r="D37" s="139"/>
+      <c r="E37" s="139"/>
+      <c r="F37" s="139"/>
+      <c r="G37" s="139"/>
       <c r="J37" s="52"/>
     </row>
     <row r="38" spans="1:14" s="6" customFormat="1" ht="19.5" customHeight="1">
@@ -2829,40 +2829,40 @@
       <c r="N39" s="54"/>
     </row>
     <row r="40" spans="1:14" s="4" customFormat="1" ht="30" customHeight="1">
-      <c r="A40" s="126" t="s">
+      <c r="A40" s="139" t="s">
         <v>47</v>
       </c>
-      <c r="B40" s="126"/>
-      <c r="C40" s="126"/>
-      <c r="D40" s="126"/>
-      <c r="E40" s="126"/>
-      <c r="F40" s="126"/>
-      <c r="G40" s="126"/>
+      <c r="B40" s="139"/>
+      <c r="C40" s="139"/>
+      <c r="D40" s="139"/>
+      <c r="E40" s="139"/>
+      <c r="F40" s="139"/>
+      <c r="G40" s="139"/>
       <c r="J40" s="52"/>
     </row>
     <row r="41" spans="1:14" s="6" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A41" s="144" t="s">
+      <c r="A41" s="157" t="s">
         <v>48</v>
       </c>
-      <c r="B41" s="144"/>
-      <c r="C41" s="144"/>
-      <c r="D41" s="144"/>
-      <c r="E41" s="144"/>
-      <c r="F41" s="144"/>
-      <c r="G41" s="144"/>
+      <c r="B41" s="157"/>
+      <c r="C41" s="157"/>
+      <c r="D41" s="157"/>
+      <c r="E41" s="157"/>
+      <c r="F41" s="157"/>
+      <c r="G41" s="157"/>
       <c r="M41" s="54"/>
       <c r="N41" s="54"/>
     </row>
     <row r="42" spans="1:14" s="6" customFormat="1" ht="44.25" customHeight="1">
-      <c r="A42" s="140" t="s">
+      <c r="A42" s="153" t="s">
         <v>49</v>
       </c>
-      <c r="B42" s="140"/>
-      <c r="C42" s="140"/>
-      <c r="D42" s="140"/>
-      <c r="E42" s="140"/>
-      <c r="F42" s="140"/>
-      <c r="G42" s="140"/>
+      <c r="B42" s="153"/>
+      <c r="C42" s="153"/>
+      <c r="D42" s="153"/>
+      <c r="E42" s="153"/>
+      <c r="F42" s="153"/>
+      <c r="G42" s="153"/>
       <c r="M42" s="54"/>
       <c r="N42" s="54"/>
     </row>
@@ -2877,27 +2877,27 @@
       <c r="J43" s="52"/>
     </row>
     <row r="44" spans="1:14" s="4" customFormat="1" ht="30" customHeight="1">
-      <c r="A44" s="126" t="s">
+      <c r="A44" s="139" t="s">
         <v>50</v>
       </c>
-      <c r="B44" s="126"/>
-      <c r="C44" s="126"/>
-      <c r="D44" s="126"/>
-      <c r="E44" s="126"/>
-      <c r="F44" s="126"/>
-      <c r="G44" s="126"/>
+      <c r="B44" s="139"/>
+      <c r="C44" s="139"/>
+      <c r="D44" s="139"/>
+      <c r="E44" s="139"/>
+      <c r="F44" s="139"/>
+      <c r="G44" s="139"/>
       <c r="J44" s="52"/>
     </row>
     <row r="45" spans="1:14" s="6" customFormat="1" ht="58.5" customHeight="1">
-      <c r="A45" s="141" t="s">
+      <c r="A45" s="154" t="s">
         <v>51</v>
       </c>
-      <c r="B45" s="142"/>
-      <c r="C45" s="142"/>
-      <c r="D45" s="142"/>
-      <c r="E45" s="142"/>
-      <c r="F45" s="142"/>
-      <c r="G45" s="142"/>
+      <c r="B45" s="155"/>
+      <c r="C45" s="155"/>
+      <c r="D45" s="155"/>
+      <c r="E45" s="155"/>
+      <c r="F45" s="155"/>
+      <c r="G45" s="155"/>
       <c r="M45" s="54"/>
       <c r="N45" s="54"/>
     </row>
@@ -2912,27 +2912,27 @@
       <c r="J46" s="52"/>
     </row>
     <row r="47" spans="1:14" s="4" customFormat="1" ht="30" customHeight="1">
-      <c r="A47" s="126" t="s">
+      <c r="A47" s="139" t="s">
         <v>52</v>
       </c>
-      <c r="B47" s="126"/>
-      <c r="C47" s="126"/>
-      <c r="D47" s="126"/>
-      <c r="E47" s="126"/>
-      <c r="F47" s="126"/>
-      <c r="G47" s="126"/>
+      <c r="B47" s="139"/>
+      <c r="C47" s="139"/>
+      <c r="D47" s="139"/>
+      <c r="E47" s="139"/>
+      <c r="F47" s="139"/>
+      <c r="G47" s="139"/>
       <c r="J47" s="52"/>
     </row>
     <row r="48" spans="1:14" s="6" customFormat="1" ht="46.5" customHeight="1">
-      <c r="A48" s="143" t="s">
+      <c r="A48" s="156" t="s">
         <v>53</v>
       </c>
-      <c r="B48" s="143"/>
-      <c r="C48" s="143"/>
-      <c r="D48" s="143"/>
-      <c r="E48" s="143"/>
-      <c r="F48" s="143"/>
-      <c r="G48" s="143"/>
+      <c r="B48" s="156"/>
+      <c r="C48" s="156"/>
+      <c r="D48" s="156"/>
+      <c r="E48" s="156"/>
+      <c r="F48" s="156"/>
+      <c r="G48" s="156"/>
       <c r="M48" s="54"/>
       <c r="N48" s="54"/>
     </row>
@@ -2945,15 +2945,15 @@
       <c r="N49" s="54"/>
     </row>
     <row r="50" spans="1:14" s="6" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A50" s="126" t="s">
+      <c r="A50" s="139" t="s">
         <v>54</v>
       </c>
-      <c r="B50" s="126"/>
-      <c r="C50" s="126"/>
-      <c r="D50" s="126"/>
-      <c r="E50" s="126"/>
-      <c r="F50" s="126"/>
-      <c r="G50" s="126"/>
+      <c r="B50" s="139"/>
+      <c r="C50" s="139"/>
+      <c r="D50" s="139"/>
+      <c r="E50" s="139"/>
+      <c r="F50" s="139"/>
+      <c r="G50" s="139"/>
       <c r="M50" s="54"/>
       <c r="N50" s="54"/>
     </row>
@@ -3009,21 +3009,6 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B8:G8"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A22:G22"/>
     <mergeCell ref="A50:G50"/>
     <mergeCell ref="E19:E20"/>
     <mergeCell ref="F19:F20"/>
@@ -3040,6 +3025,21 @@
     <mergeCell ref="A37:G37"/>
     <mergeCell ref="A40:G40"/>
     <mergeCell ref="A41:G41"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="A10:G10"/>
   </mergeCells>
   <phoneticPr fontId="26" type="noConversion"/>
   <printOptions horizontalCentered="1"/>

--- a/excel-template/PO-template.xlsx
+++ b/excel-template/PO-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\exportcrm\excel-template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C635979A-D64B-4D65-A0D4-F56874E2BD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17B1CD13-4059-4C12-8137-114EEB609417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="813" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,9 +40,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="77">
-  <si>
-    <t>VAT 91500109MADTT20C92</t>
-  </si>
   <si>
     <t>www.alustars.com</t>
   </si>
@@ -469,6 +466,10 @@
   </si>
   <si>
     <t>以上单价不含税，开票时付税金。</t>
+    <phoneticPr fontId="26" type="noConversion"/>
+  </si>
+  <si>
+    <t>VAT 91500109MADTT20C93</t>
     <phoneticPr fontId="26" type="noConversion"/>
   </si>
 </sst>
@@ -1252,6 +1253,33 @@
     <xf numFmtId="43" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="186" fontId="34" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="32" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="15" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1259,35 +1287,86 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="43" fontId="19" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="178" fontId="16" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="11" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="11" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="32" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="15" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1303,84 +1382,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="11" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="11" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="186" fontId="34" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1751,33 +1752,33 @@
   <sheetData>
     <row r="1" spans="1:20" s="55" customFormat="1" ht="66" customHeight="1">
       <c r="A1" s="68" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B1" s="68"/>
       <c r="C1" s="68"/>
       <c r="D1" s="68"/>
       <c r="E1" s="68"/>
       <c r="F1" s="68"/>
-      <c r="G1" s="121" t="s">
-        <v>72</v>
-      </c>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
+      <c r="G1" s="116" t="s">
+        <v>71</v>
+      </c>
+      <c r="H1" s="116"/>
+      <c r="I1" s="116"/>
       <c r="O1" s="88"/>
       <c r="P1" s="88"/>
     </row>
     <row r="2" spans="1:20" ht="26.25" customHeight="1">
       <c r="A2" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="H2" s="122" t="s">
-        <v>59</v>
-      </c>
-      <c r="I2" s="122"/>
+        <v>76</v>
+      </c>
+      <c r="H2" s="117" t="s">
+        <v>58</v>
+      </c>
+      <c r="I2" s="117"/>
     </row>
     <row r="3" spans="1:20" s="56" customFormat="1" ht="21.75" customHeight="1">
       <c r="A3" s="112" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B3" s="70"/>
       <c r="C3" s="58"/>
@@ -1786,10 +1787,10 @@
       <c r="F3" s="58"/>
       <c r="G3" s="58"/>
       <c r="H3" s="106" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I3" s="113" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O3" s="71"/>
       <c r="P3" s="71"/>
@@ -1810,7 +1811,7 @@
     </row>
     <row r="5" spans="1:20" s="57" customFormat="1" ht="24.9" customHeight="1">
       <c r="A5" s="111" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C5" s="72"/>
       <c r="D5" s="72"/>
@@ -1871,43 +1872,43 @@
     </row>
     <row r="8" spans="1:20" s="59" customFormat="1" ht="24.9" customHeight="1">
       <c r="A8" s="98" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="118" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="123" t="s">
-        <v>61</v>
-      </c>
-      <c r="C8" s="124"/>
+      <c r="C8" s="119"/>
       <c r="D8" s="82" t="s">
+        <v>64</v>
+      </c>
+      <c r="E8" s="82" t="s">
         <v>65</v>
       </c>
-      <c r="E8" s="82" t="s">
+      <c r="F8" s="82" t="s">
         <v>66</v>
       </c>
-      <c r="F8" s="82" t="s">
+      <c r="G8" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="G8" s="82" t="s">
+      <c r="H8" s="82" t="s">
         <v>68</v>
       </c>
-      <c r="H8" s="82" t="s">
+      <c r="I8" s="82" t="s">
         <v>69</v>
       </c>
-      <c r="I8" s="82" t="s">
-        <v>70</v>
-      </c>
-      <c r="M8" s="119"/>
-      <c r="N8" s="119"/>
-      <c r="O8" s="119"/>
-      <c r="P8" s="119"/>
-      <c r="Q8" s="119"/>
-      <c r="R8" s="119"/>
-      <c r="S8" s="119"/>
-      <c r="T8" s="119"/>
+      <c r="M8" s="127"/>
+      <c r="N8" s="127"/>
+      <c r="O8" s="127"/>
+      <c r="P8" s="127"/>
+      <c r="Q8" s="127"/>
+      <c r="R8" s="127"/>
+      <c r="S8" s="127"/>
+      <c r="T8" s="127"/>
     </row>
     <row r="9" spans="1:20" s="58" customFormat="1" ht="24.9" customHeight="1">
       <c r="A9" s="99"/>
-      <c r="B9" s="120"/>
-      <c r="C9" s="120"/>
+      <c r="B9" s="128"/>
+      <c r="C9" s="128"/>
       <c r="D9" s="99"/>
       <c r="E9" s="99"/>
       <c r="F9" s="101"/>
@@ -1922,8 +1923,8 @@
     </row>
     <row r="10" spans="1:20" s="58" customFormat="1" ht="24.9" customHeight="1">
       <c r="A10" s="99"/>
-      <c r="B10" s="120"/>
-      <c r="C10" s="120"/>
+      <c r="B10" s="128"/>
+      <c r="C10" s="128"/>
       <c r="D10" s="99"/>
       <c r="E10" s="99"/>
       <c r="F10" s="101"/>
@@ -1938,8 +1939,8 @@
     </row>
     <row r="11" spans="1:20" s="58" customFormat="1" ht="24.9" customHeight="1">
       <c r="A11" s="99"/>
-      <c r="B11" s="120"/>
-      <c r="C11" s="120"/>
+      <c r="B11" s="128"/>
+      <c r="C11" s="128"/>
       <c r="D11" s="105"/>
       <c r="E11" s="99"/>
       <c r="F11" s="101"/>
@@ -1954,8 +1955,8 @@
     </row>
     <row r="12" spans="1:20" s="58" customFormat="1" ht="24.9" customHeight="1">
       <c r="A12" s="99"/>
-      <c r="B12" s="120"/>
-      <c r="C12" s="120"/>
+      <c r="B12" s="128"/>
+      <c r="C12" s="128"/>
       <c r="D12" s="105"/>
       <c r="E12" s="100"/>
       <c r="F12" s="101"/>
@@ -1970,14 +1971,14 @@
     </row>
     <row r="13" spans="1:20" s="58" customFormat="1" ht="24.9" customHeight="1">
       <c r="A13" s="99"/>
-      <c r="B13" s="120"/>
-      <c r="C13" s="120"/>
+      <c r="B13" s="128"/>
+      <c r="C13" s="128"/>
       <c r="D13" s="105"/>
       <c r="E13" s="100"/>
       <c r="F13" s="101"/>
       <c r="G13" s="101"/>
       <c r="H13" s="103" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I13" s="102">
         <f>SUM(I9:I12)</f>
@@ -1991,14 +1992,14 @@
     </row>
     <row r="14" spans="1:20" s="58" customFormat="1" ht="24.9" customHeight="1">
       <c r="A14" s="99"/>
-      <c r="B14" s="120"/>
-      <c r="C14" s="120"/>
+      <c r="B14" s="128"/>
+      <c r="C14" s="128"/>
       <c r="D14" s="105"/>
       <c r="E14" s="100"/>
       <c r="F14" s="101"/>
       <c r="G14" s="101"/>
       <c r="H14" s="103" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I14" s="102">
         <f>I13*0.13</f>
@@ -2016,51 +2017,51 @@
     </row>
     <row r="15" spans="1:20" s="60" customFormat="1" ht="24.9" customHeight="1">
       <c r="A15" s="110" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B15" s="110"/>
       <c r="C15" s="110"/>
       <c r="D15" s="99"/>
       <c r="E15" s="99"/>
       <c r="F15" s="109" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G15" s="104"/>
       <c r="H15" s="110" t="s">
-        <v>62</v>
-      </c>
-      <c r="I15" s="158">
+        <v>61</v>
+      </c>
+      <c r="I15" s="115">
         <f>I14+I13</f>
         <v>0</v>
       </c>
       <c r="J15" s="83"/>
     </row>
     <row r="16" spans="1:20" s="60" customFormat="1" ht="30" customHeight="1">
-      <c r="A16" s="127" t="s">
-        <v>71</v>
-      </c>
-      <c r="B16" s="127"/>
-      <c r="C16" s="127"/>
-      <c r="D16" s="127"/>
-      <c r="E16" s="127"/>
-      <c r="F16" s="127"/>
-      <c r="G16" s="127"/>
-      <c r="H16" s="127"/>
-      <c r="I16" s="127"/>
+      <c r="A16" s="122" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="122"/>
+      <c r="C16" s="122"/>
+      <c r="D16" s="122"/>
+      <c r="E16" s="122"/>
+      <c r="F16" s="122"/>
+      <c r="G16" s="122"/>
+      <c r="H16" s="122"/>
+      <c r="I16" s="122"/>
       <c r="L16" s="95"/>
     </row>
     <row r="17" spans="1:20" s="106" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A17" s="118" t="s">
-        <v>76</v>
-      </c>
-      <c r="B17" s="125"/>
-      <c r="C17" s="125"/>
-      <c r="D17" s="125"/>
-      <c r="E17" s="125"/>
-      <c r="F17" s="125"/>
-      <c r="G17" s="125"/>
-      <c r="H17" s="125"/>
-      <c r="I17" s="125"/>
+      <c r="A17" s="123" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="120"/>
+      <c r="C17" s="120"/>
+      <c r="D17" s="120"/>
+      <c r="E17" s="120"/>
+      <c r="F17" s="120"/>
+      <c r="G17" s="120"/>
+      <c r="H17" s="120"/>
+      <c r="I17" s="120"/>
       <c r="L17" s="107"/>
       <c r="M17" s="108"/>
       <c r="N17" s="108"/>
@@ -2072,15 +2073,15 @@
       <c r="T17" s="108"/>
     </row>
     <row r="18" spans="1:20" s="106" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A18" s="118"/>
-      <c r="B18" s="118"/>
-      <c r="C18" s="118"/>
-      <c r="D18" s="118"/>
-      <c r="E18" s="118"/>
-      <c r="F18" s="118"/>
-      <c r="G18" s="118"/>
-      <c r="H18" s="118"/>
-      <c r="I18" s="118"/>
+      <c r="A18" s="123"/>
+      <c r="B18" s="123"/>
+      <c r="C18" s="123"/>
+      <c r="D18" s="123"/>
+      <c r="E18" s="123"/>
+      <c r="F18" s="123"/>
+      <c r="G18" s="123"/>
+      <c r="H18" s="123"/>
+      <c r="I18" s="123"/>
       <c r="L18" s="107"/>
       <c r="M18" s="108"/>
       <c r="N18" s="108"/>
@@ -2092,26 +2093,26 @@
       <c r="T18" s="108"/>
     </row>
     <row r="19" spans="1:20" s="108" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A19" s="125"/>
-      <c r="B19" s="125"/>
-      <c r="C19" s="125"/>
-      <c r="D19" s="125"/>
-      <c r="E19" s="125"/>
-      <c r="F19" s="125"/>
-      <c r="G19" s="125"/>
-      <c r="H19" s="125"/>
-      <c r="I19" s="125"/>
+      <c r="A19" s="120"/>
+      <c r="B19" s="120"/>
+      <c r="C19" s="120"/>
+      <c r="D19" s="120"/>
+      <c r="E19" s="120"/>
+      <c r="F19" s="120"/>
+      <c r="G19" s="120"/>
+      <c r="H19" s="120"/>
+      <c r="I19" s="120"/>
     </row>
     <row r="20" spans="1:20" s="108" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A20" s="125"/>
-      <c r="B20" s="125"/>
-      <c r="C20" s="125"/>
-      <c r="D20" s="125"/>
-      <c r="E20" s="125"/>
-      <c r="F20" s="125"/>
-      <c r="G20" s="125"/>
-      <c r="H20" s="125"/>
-      <c r="I20" s="125"/>
+      <c r="A20" s="120"/>
+      <c r="B20" s="120"/>
+      <c r="C20" s="120"/>
+      <c r="D20" s="120"/>
+      <c r="E20" s="120"/>
+      <c r="F20" s="120"/>
+      <c r="G20" s="120"/>
+      <c r="H20" s="120"/>
+      <c r="I20" s="120"/>
       <c r="M20" s="106"/>
       <c r="N20" s="106"/>
       <c r="O20" s="106"/>
@@ -2122,56 +2123,56 @@
       <c r="T20" s="106"/>
     </row>
     <row r="21" spans="1:20" s="106" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A21" s="125"/>
-      <c r="B21" s="125"/>
-      <c r="C21" s="125"/>
-      <c r="D21" s="125"/>
-      <c r="E21" s="125"/>
-      <c r="F21" s="125"/>
-      <c r="G21" s="125"/>
-      <c r="H21" s="125"/>
-      <c r="I21" s="125"/>
+      <c r="A21" s="120"/>
+      <c r="B21" s="120"/>
+      <c r="C21" s="120"/>
+      <c r="D21" s="120"/>
+      <c r="E21" s="120"/>
+      <c r="F21" s="120"/>
+      <c r="G21" s="120"/>
+      <c r="H21" s="120"/>
+      <c r="I21" s="120"/>
       <c r="L21" s="107"/>
     </row>
     <row r="22" spans="1:20" s="106" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A22" s="126" t="s">
-        <v>59</v>
-      </c>
-      <c r="B22" s="126"/>
-      <c r="C22" s="126"/>
-      <c r="D22" s="126"/>
-      <c r="E22" s="126"/>
-      <c r="F22" s="126"/>
-      <c r="G22" s="126"/>
-      <c r="H22" s="126"/>
-      <c r="I22" s="126"/>
+      <c r="A22" s="121" t="s">
+        <v>58</v>
+      </c>
+      <c r="B22" s="121"/>
+      <c r="C22" s="121"/>
+      <c r="D22" s="121"/>
+      <c r="E22" s="121"/>
+      <c r="F22" s="121"/>
+      <c r="G22" s="121"/>
+      <c r="H22" s="121"/>
+      <c r="I22" s="121"/>
       <c r="L22" s="107"/>
     </row>
     <row r="23" spans="1:20" s="62" customFormat="1" ht="24" customHeight="1">
-      <c r="A23" s="115"/>
-      <c r="B23" s="115"/>
-      <c r="C23" s="115"/>
-      <c r="D23" s="115"/>
-      <c r="E23" s="115"/>
-      <c r="F23" s="115"/>
-      <c r="G23" s="115"/>
-      <c r="H23" s="115"/>
-      <c r="I23" s="115"/>
+      <c r="A23" s="124"/>
+      <c r="B23" s="124"/>
+      <c r="C23" s="124"/>
+      <c r="D23" s="124"/>
+      <c r="E23" s="124"/>
+      <c r="F23" s="124"/>
+      <c r="G23" s="124"/>
+      <c r="H23" s="124"/>
+      <c r="I23" s="124"/>
       <c r="J23" s="114"/>
       <c r="K23" s="114"/>
       <c r="O23" s="96"/>
       <c r="P23" s="96"/>
     </row>
     <row r="24" spans="1:20" s="62" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A24" s="116"/>
-      <c r="B24" s="116"/>
-      <c r="C24" s="116"/>
-      <c r="D24" s="116"/>
-      <c r="E24" s="116"/>
-      <c r="F24" s="116"/>
-      <c r="G24" s="116"/>
-      <c r="H24" s="116"/>
-      <c r="I24" s="116"/>
+      <c r="A24" s="125"/>
+      <c r="B24" s="125"/>
+      <c r="C24" s="125"/>
+      <c r="D24" s="125"/>
+      <c r="E24" s="125"/>
+      <c r="F24" s="125"/>
+      <c r="G24" s="125"/>
+      <c r="H24" s="125"/>
+      <c r="I24" s="125"/>
       <c r="J24" s="114"/>
       <c r="K24" s="114"/>
       <c r="M24" s="64"/>
@@ -2184,15 +2185,15 @@
       <c r="T24" s="64"/>
     </row>
     <row r="25" spans="1:20">
-      <c r="A25" s="117"/>
-      <c r="B25" s="117"/>
-      <c r="C25" s="117"/>
-      <c r="D25" s="117"/>
-      <c r="E25" s="117"/>
-      <c r="F25" s="117"/>
-      <c r="G25" s="117"/>
-      <c r="H25" s="117"/>
-      <c r="I25" s="117"/>
+      <c r="A25" s="126"/>
+      <c r="B25" s="126"/>
+      <c r="C25" s="126"/>
+      <c r="D25" s="126"/>
+      <c r="E25" s="126"/>
+      <c r="F25" s="126"/>
+      <c r="G25" s="126"/>
+      <c r="H25" s="126"/>
+      <c r="I25" s="126"/>
     </row>
     <row r="26" spans="1:20">
       <c r="A26" s="85"/>
@@ -2223,15 +2224,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="A21:I21"/>
-    <mergeCell ref="A22:I22"/>
-    <mergeCell ref="A16:I16"/>
-    <mergeCell ref="A17:I17"/>
-    <mergeCell ref="A19:I19"/>
-    <mergeCell ref="A20:I20"/>
     <mergeCell ref="A23:I23"/>
     <mergeCell ref="A24:I24"/>
     <mergeCell ref="A25:I25"/>
@@ -2243,6 +2235,15 @@
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A16:I16"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A20:I20"/>
   </mergeCells>
   <phoneticPr fontId="26" type="noConversion"/>
   <hyperlinks>
@@ -2280,43 +2281,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A1" s="128" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" s="128"/>
-      <c r="C1" s="128"/>
-      <c r="D1" s="128"/>
-      <c r="E1" s="128"/>
-      <c r="F1" s="128"/>
-      <c r="G1" s="128"/>
+      <c r="A1" s="154" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="154"/>
+      <c r="C1" s="154"/>
+      <c r="D1" s="154"/>
+      <c r="E1" s="154"/>
+      <c r="F1" s="154"/>
+      <c r="G1" s="154"/>
       <c r="M1" s="45"/>
       <c r="N1" s="45"/>
     </row>
     <row r="2" spans="1:15" ht="13.5" customHeight="1">
       <c r="F2" s="12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="15" customHeight="1">
       <c r="F3" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="13" t="s">
         <v>20</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="15" t="s">
         <v>22</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>23</v>
       </c>
       <c r="C4" s="15"/>
       <c r="D4" s="15"/>
@@ -2326,14 +2327,14 @@
     </row>
     <row r="5" spans="1:15" s="2" customFormat="1" ht="33" customHeight="1">
       <c r="A5" s="17"/>
-      <c r="B5" s="129" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="129"/>
-      <c r="D5" s="129"/>
-      <c r="E5" s="129"/>
-      <c r="F5" s="129"/>
-      <c r="G5" s="129"/>
+      <c r="B5" s="155" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="155"/>
+      <c r="D5" s="155"/>
+      <c r="E5" s="155"/>
+      <c r="F5" s="155"/>
+      <c r="G5" s="155"/>
       <c r="H5" s="18"/>
       <c r="M5" s="46"/>
       <c r="N5" s="46"/>
@@ -2351,29 +2352,29 @@
     </row>
     <row r="7" spans="1:15" s="2" customFormat="1">
       <c r="A7" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="130" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="130"/>
-      <c r="D7" s="130"/>
-      <c r="E7" s="130"/>
-      <c r="F7" s="130"/>
+        <v>24</v>
+      </c>
+      <c r="B7" s="156" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="156"/>
+      <c r="D7" s="156"/>
+      <c r="E7" s="156"/>
+      <c r="F7" s="156"/>
       <c r="G7" s="20"/>
       <c r="M7" s="46"/>
       <c r="N7" s="46"/>
     </row>
     <row r="8" spans="1:15" s="2" customFormat="1" ht="54" customHeight="1">
       <c r="A8" s="17"/>
-      <c r="B8" s="131" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="131"/>
-      <c r="D8" s="131"/>
-      <c r="E8" s="131"/>
-      <c r="F8" s="131"/>
-      <c r="G8" s="131"/>
+      <c r="B8" s="157" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="157"/>
+      <c r="D8" s="157"/>
+      <c r="E8" s="157"/>
+      <c r="F8" s="157"/>
+      <c r="G8" s="157"/>
       <c r="M8" s="46"/>
       <c r="N8" s="46"/>
     </row>
@@ -2389,66 +2390,66 @@
       <c r="N9" s="46"/>
     </row>
     <row r="10" spans="1:15" s="3" customFormat="1" ht="49.5" customHeight="1">
-      <c r="A10" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="132"/>
-      <c r="C10" s="132"/>
-      <c r="D10" s="132"/>
-      <c r="E10" s="132"/>
-      <c r="F10" s="132"/>
-      <c r="G10" s="132"/>
+      <c r="A10" s="158" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="158"/>
+      <c r="C10" s="158"/>
+      <c r="D10" s="158"/>
+      <c r="E10" s="158"/>
+      <c r="F10" s="158"/>
+      <c r="G10" s="158"/>
       <c r="M10" s="4"/>
       <c r="N10" s="4"/>
     </row>
     <row r="11" spans="1:15" s="3" customFormat="1" ht="27" customHeight="1">
-      <c r="A11" s="133" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="133"/>
-      <c r="C11" s="133"/>
-      <c r="D11" s="133"/>
-      <c r="E11" s="133"/>
-      <c r="F11" s="133"/>
-      <c r="G11" s="133"/>
+      <c r="A11" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="151"/>
+      <c r="C11" s="151"/>
+      <c r="D11" s="151"/>
+      <c r="E11" s="151"/>
+      <c r="F11" s="151"/>
+      <c r="G11" s="151"/>
       <c r="M11" s="4"/>
       <c r="N11" s="4"/>
     </row>
     <row r="12" spans="1:15" s="4" customFormat="1" ht="30.75" customHeight="1">
       <c r="A12" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="152" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" s="153"/>
+      <c r="D12" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="134" t="s">
-        <v>4</v>
-      </c>
-      <c r="C12" s="135"/>
-      <c r="D12" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" s="24" t="s">
+      <c r="G12" s="24" t="s">
         <v>30</v>
-      </c>
-      <c r="G12" s="24" t="s">
-        <v>31</v>
       </c>
       <c r="L12" s="47"/>
       <c r="M12" s="48"/>
       <c r="N12" s="49"/>
-      <c r="O12" s="146"/>
+      <c r="O12" s="136"/>
     </row>
     <row r="13" spans="1:15" s="3" customFormat="1" ht="18" customHeight="1">
       <c r="A13" s="25">
         <v>1</v>
       </c>
-      <c r="B13" s="136">
+      <c r="B13" s="148">
         <v>50655</v>
       </c>
-      <c r="C13" s="137"/>
+      <c r="C13" s="149"/>
       <c r="D13" s="26" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E13" s="27">
         <v>1000</v>
@@ -2463,18 +2464,18 @@
       <c r="J13" s="51"/>
       <c r="M13" s="4"/>
       <c r="N13" s="4"/>
-      <c r="O13" s="146"/>
+      <c r="O13" s="136"/>
     </row>
     <row r="14" spans="1:15" s="3" customFormat="1" ht="18" customHeight="1">
       <c r="A14" s="25">
         <v>2</v>
       </c>
-      <c r="B14" s="136">
+      <c r="B14" s="148">
         <v>50755</v>
       </c>
-      <c r="C14" s="137"/>
+      <c r="C14" s="149"/>
       <c r="D14" s="26" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E14" s="27">
         <v>1000</v>
@@ -2495,12 +2496,12 @@
       <c r="A15" s="25">
         <v>3</v>
       </c>
-      <c r="B15" s="136">
+      <c r="B15" s="148">
         <v>50665</v>
       </c>
-      <c r="C15" s="137"/>
+      <c r="C15" s="149"/>
       <c r="D15" s="26" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E15" s="27">
         <v>1000</v>
@@ -2521,12 +2522,12 @@
       <c r="A16" s="25">
         <v>4</v>
       </c>
-      <c r="B16" s="136">
+      <c r="B16" s="148">
         <v>50765</v>
       </c>
-      <c r="C16" s="137"/>
+      <c r="C16" s="149"/>
       <c r="D16" s="26" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E16" s="27">
         <v>1000</v>
@@ -2547,12 +2548,12 @@
       <c r="A17" s="25">
         <v>5</v>
       </c>
-      <c r="B17" s="136">
+      <c r="B17" s="148">
         <v>50720</v>
       </c>
-      <c r="C17" s="137"/>
+      <c r="C17" s="149"/>
       <c r="D17" s="26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E17" s="27">
         <v>1000</v>
@@ -2573,12 +2574,12 @@
       <c r="A18" s="30">
         <v>6</v>
       </c>
-      <c r="B18" s="136">
+      <c r="B18" s="148">
         <v>50730</v>
       </c>
-      <c r="C18" s="137"/>
+      <c r="C18" s="149"/>
       <c r="D18" s="31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E18" s="27">
         <v>1000</v>
@@ -2596,59 +2597,59 @@
       <c r="O18" s="50"/>
     </row>
     <row r="19" spans="1:15" s="4" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A19" s="147" t="s">
-        <v>13</v>
-      </c>
-      <c r="B19" s="148"/>
-      <c r="C19" s="149"/>
+      <c r="A19" s="137" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="138"/>
+      <c r="C19" s="139"/>
       <c r="D19" s="32"/>
-      <c r="E19" s="140">
+      <c r="E19" s="130">
         <f>SUM(E13:E18)</f>
         <v>6000</v>
       </c>
-      <c r="F19" s="142"/>
-      <c r="G19" s="144">
+      <c r="F19" s="132"/>
+      <c r="G19" s="134">
         <f>SUM(G13:G18)</f>
         <v>73120</v>
       </c>
       <c r="H19" s="33"/>
     </row>
     <row r="20" spans="1:15" s="4" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A20" s="150"/>
-      <c r="B20" s="151"/>
-      <c r="C20" s="152"/>
+      <c r="A20" s="140"/>
+      <c r="B20" s="141"/>
+      <c r="C20" s="142"/>
       <c r="D20" s="34"/>
-      <c r="E20" s="141"/>
-      <c r="F20" s="143"/>
-      <c r="G20" s="145"/>
+      <c r="E20" s="131"/>
+      <c r="F20" s="133"/>
+      <c r="G20" s="135"/>
     </row>
     <row r="21" spans="1:15" s="4" customFormat="1" ht="30" hidden="1" customHeight="1">
-      <c r="A21" s="138" t="s">
+      <c r="A21" s="150" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="150"/>
+      <c r="C21" s="150"/>
+      <c r="D21" s="150"/>
+      <c r="E21" s="150"/>
+      <c r="F21" s="150"/>
+      <c r="G21" s="150"/>
+      <c r="J21" s="52"/>
+    </row>
+    <row r="22" spans="1:15" s="4" customFormat="1" ht="30" customHeight="1">
+      <c r="A22" s="129" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="138"/>
-      <c r="C21" s="138"/>
-      <c r="D21" s="138"/>
-      <c r="E21" s="138"/>
-      <c r="F21" s="138"/>
-      <c r="G21" s="138"/>
-      <c r="J21" s="52"/>
-    </row>
-    <row r="22" spans="1:15" s="4" customFormat="1" ht="30" customHeight="1">
-      <c r="A22" s="139" t="s">
-        <v>33</v>
-      </c>
-      <c r="B22" s="139"/>
-      <c r="C22" s="139"/>
-      <c r="D22" s="139"/>
-      <c r="E22" s="139"/>
-      <c r="F22" s="139"/>
-      <c r="G22" s="139"/>
+      <c r="B22" s="129"/>
+      <c r="C22" s="129"/>
+      <c r="D22" s="129"/>
+      <c r="E22" s="129"/>
+      <c r="F22" s="129"/>
+      <c r="G22" s="129"/>
       <c r="J22" s="52"/>
     </row>
     <row r="23" spans="1:15" s="4" customFormat="1" ht="21.75" customHeight="1">
       <c r="A23" s="36" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B23" s="35"/>
       <c r="C23" s="35"/>
@@ -2660,7 +2661,7 @@
     </row>
     <row r="24" spans="1:15" s="4" customFormat="1" ht="21.75" customHeight="1">
       <c r="A24" s="36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B24" s="35"/>
       <c r="C24" s="35"/>
@@ -2672,7 +2673,7 @@
     </row>
     <row r="25" spans="1:15" s="4" customFormat="1" ht="21.75" customHeight="1">
       <c r="A25" s="36" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B25" s="35"/>
       <c r="C25" s="35"/>
@@ -2693,20 +2694,20 @@
       <c r="J26" s="52"/>
     </row>
     <row r="27" spans="1:15" s="4" customFormat="1" ht="30" customHeight="1">
-      <c r="A27" s="139" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="139"/>
-      <c r="C27" s="139"/>
-      <c r="D27" s="139"/>
-      <c r="E27" s="139"/>
-      <c r="F27" s="139"/>
-      <c r="G27" s="139"/>
+      <c r="A27" s="129" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="129"/>
+      <c r="C27" s="129"/>
+      <c r="D27" s="129"/>
+      <c r="E27" s="129"/>
+      <c r="F27" s="129"/>
+      <c r="G27" s="129"/>
       <c r="J27" s="52"/>
     </row>
     <row r="28" spans="1:15" s="5" customFormat="1" ht="19.5" customHeight="1">
       <c r="A28" s="36" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C28" s="36"/>
       <c r="D28" s="36"/>
@@ -2716,7 +2717,7 @@
     </row>
     <row r="29" spans="1:15" s="5" customFormat="1" ht="19.5" customHeight="1">
       <c r="A29" s="36" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C29" s="36"/>
       <c r="D29" s="36"/>
@@ -2726,7 +2727,7 @@
     </row>
     <row r="30" spans="1:15" s="6" customFormat="1" ht="19.5" customHeight="1">
       <c r="A30" s="36" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C30" s="37"/>
       <c r="D30" s="37"/>
@@ -2736,7 +2737,7 @@
     </row>
     <row r="31" spans="1:15" s="6" customFormat="1" ht="19.5" customHeight="1">
       <c r="A31" s="36" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C31" s="36"/>
       <c r="D31" s="36"/>
@@ -2746,7 +2747,7 @@
     </row>
     <row r="32" spans="1:15" s="6" customFormat="1" ht="19.5" customHeight="1">
       <c r="A32" s="36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C32" s="36"/>
       <c r="D32" s="36"/>
@@ -2756,7 +2757,7 @@
     </row>
     <row r="33" spans="1:14" s="6" customFormat="1" ht="19.5" customHeight="1">
       <c r="A33" s="36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C33" s="36"/>
       <c r="D33" s="36"/>
@@ -2765,20 +2766,20 @@
       <c r="N33" s="54"/>
     </row>
     <row r="34" spans="1:14" s="4" customFormat="1" ht="30" customHeight="1">
-      <c r="A34" s="139" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" s="139"/>
-      <c r="C34" s="139"/>
-      <c r="D34" s="139"/>
-      <c r="E34" s="139"/>
-      <c r="F34" s="139"/>
-      <c r="G34" s="139"/>
+      <c r="A34" s="129" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="129"/>
+      <c r="C34" s="129"/>
+      <c r="D34" s="129"/>
+      <c r="E34" s="129"/>
+      <c r="F34" s="129"/>
+      <c r="G34" s="129"/>
       <c r="J34" s="52"/>
     </row>
     <row r="35" spans="1:14" s="5" customFormat="1" ht="19.5" customHeight="1">
       <c r="A35" s="36" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C35" s="36"/>
       <c r="D35" s="36"/>
@@ -2788,7 +2789,7 @@
     </row>
     <row r="36" spans="1:14" s="5" customFormat="1" ht="19.5" customHeight="1">
       <c r="A36" s="36" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C36" s="36"/>
       <c r="D36" s="36"/>
@@ -2797,20 +2798,20 @@
       <c r="N36" s="53"/>
     </row>
     <row r="37" spans="1:14" s="4" customFormat="1" ht="30" customHeight="1">
-      <c r="A37" s="139" t="s">
-        <v>44</v>
-      </c>
-      <c r="B37" s="139"/>
-      <c r="C37" s="139"/>
-      <c r="D37" s="139"/>
-      <c r="E37" s="139"/>
-      <c r="F37" s="139"/>
-      <c r="G37" s="139"/>
+      <c r="A37" s="129" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="129"/>
+      <c r="C37" s="129"/>
+      <c r="D37" s="129"/>
+      <c r="E37" s="129"/>
+      <c r="F37" s="129"/>
+      <c r="G37" s="129"/>
       <c r="J37" s="52"/>
     </row>
     <row r="38" spans="1:14" s="6" customFormat="1" ht="19.5" customHeight="1">
       <c r="A38" s="36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C38" s="36"/>
       <c r="D38" s="36"/>
@@ -2820,7 +2821,7 @@
     </row>
     <row r="39" spans="1:14" s="6" customFormat="1" ht="19.5" customHeight="1">
       <c r="A39" s="36" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C39" s="36"/>
       <c r="D39" s="36"/>
@@ -2829,40 +2830,40 @@
       <c r="N39" s="54"/>
     </row>
     <row r="40" spans="1:14" s="4" customFormat="1" ht="30" customHeight="1">
-      <c r="A40" s="139" t="s">
+      <c r="A40" s="129" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="129"/>
+      <c r="C40" s="129"/>
+      <c r="D40" s="129"/>
+      <c r="E40" s="129"/>
+      <c r="F40" s="129"/>
+      <c r="G40" s="129"/>
+      <c r="J40" s="52"/>
+    </row>
+    <row r="41" spans="1:14" s="6" customFormat="1" ht="19.5" customHeight="1">
+      <c r="A41" s="147" t="s">
         <v>47</v>
       </c>
-      <c r="B40" s="139"/>
-      <c r="C40" s="139"/>
-      <c r="D40" s="139"/>
-      <c r="E40" s="139"/>
-      <c r="F40" s="139"/>
-      <c r="G40" s="139"/>
-      <c r="J40" s="52"/>
-    </row>
-    <row r="41" spans="1:14" s="6" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A41" s="157" t="s">
-        <v>48</v>
-      </c>
-      <c r="B41" s="157"/>
-      <c r="C41" s="157"/>
-      <c r="D41" s="157"/>
-      <c r="E41" s="157"/>
-      <c r="F41" s="157"/>
-      <c r="G41" s="157"/>
+      <c r="B41" s="147"/>
+      <c r="C41" s="147"/>
+      <c r="D41" s="147"/>
+      <c r="E41" s="147"/>
+      <c r="F41" s="147"/>
+      <c r="G41" s="147"/>
       <c r="M41" s="54"/>
       <c r="N41" s="54"/>
     </row>
     <row r="42" spans="1:14" s="6" customFormat="1" ht="44.25" customHeight="1">
-      <c r="A42" s="153" t="s">
-        <v>49</v>
-      </c>
-      <c r="B42" s="153"/>
-      <c r="C42" s="153"/>
-      <c r="D42" s="153"/>
-      <c r="E42" s="153"/>
-      <c r="F42" s="153"/>
-      <c r="G42" s="153"/>
+      <c r="A42" s="143" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="143"/>
+      <c r="C42" s="143"/>
+      <c r="D42" s="143"/>
+      <c r="E42" s="143"/>
+      <c r="F42" s="143"/>
+      <c r="G42" s="143"/>
       <c r="M42" s="54"/>
       <c r="N42" s="54"/>
     </row>
@@ -2877,27 +2878,27 @@
       <c r="J43" s="52"/>
     </row>
     <row r="44" spans="1:14" s="4" customFormat="1" ht="30" customHeight="1">
-      <c r="A44" s="139" t="s">
+      <c r="A44" s="129" t="s">
+        <v>49</v>
+      </c>
+      <c r="B44" s="129"/>
+      <c r="C44" s="129"/>
+      <c r="D44" s="129"/>
+      <c r="E44" s="129"/>
+      <c r="F44" s="129"/>
+      <c r="G44" s="129"/>
+      <c r="J44" s="52"/>
+    </row>
+    <row r="45" spans="1:14" s="6" customFormat="1" ht="58.5" customHeight="1">
+      <c r="A45" s="144" t="s">
         <v>50</v>
       </c>
-      <c r="B44" s="139"/>
-      <c r="C44" s="139"/>
-      <c r="D44" s="139"/>
-      <c r="E44" s="139"/>
-      <c r="F44" s="139"/>
-      <c r="G44" s="139"/>
-      <c r="J44" s="52"/>
-    </row>
-    <row r="45" spans="1:14" s="6" customFormat="1" ht="58.5" customHeight="1">
-      <c r="A45" s="154" t="s">
-        <v>51</v>
-      </c>
-      <c r="B45" s="155"/>
-      <c r="C45" s="155"/>
-      <c r="D45" s="155"/>
-      <c r="E45" s="155"/>
-      <c r="F45" s="155"/>
-      <c r="G45" s="155"/>
+      <c r="B45" s="145"/>
+      <c r="C45" s="145"/>
+      <c r="D45" s="145"/>
+      <c r="E45" s="145"/>
+      <c r="F45" s="145"/>
+      <c r="G45" s="145"/>
       <c r="M45" s="54"/>
       <c r="N45" s="54"/>
     </row>
@@ -2912,27 +2913,27 @@
       <c r="J46" s="52"/>
     </row>
     <row r="47" spans="1:14" s="4" customFormat="1" ht="30" customHeight="1">
-      <c r="A47" s="139" t="s">
+      <c r="A47" s="129" t="s">
+        <v>51</v>
+      </c>
+      <c r="B47" s="129"/>
+      <c r="C47" s="129"/>
+      <c r="D47" s="129"/>
+      <c r="E47" s="129"/>
+      <c r="F47" s="129"/>
+      <c r="G47" s="129"/>
+      <c r="J47" s="52"/>
+    </row>
+    <row r="48" spans="1:14" s="6" customFormat="1" ht="46.5" customHeight="1">
+      <c r="A48" s="146" t="s">
         <v>52</v>
       </c>
-      <c r="B47" s="139"/>
-      <c r="C47" s="139"/>
-      <c r="D47" s="139"/>
-      <c r="E47" s="139"/>
-      <c r="F47" s="139"/>
-      <c r="G47" s="139"/>
-      <c r="J47" s="52"/>
-    </row>
-    <row r="48" spans="1:14" s="6" customFormat="1" ht="46.5" customHeight="1">
-      <c r="A48" s="156" t="s">
-        <v>53</v>
-      </c>
-      <c r="B48" s="156"/>
-      <c r="C48" s="156"/>
-      <c r="D48" s="156"/>
-      <c r="E48" s="156"/>
-      <c r="F48" s="156"/>
-      <c r="G48" s="156"/>
+      <c r="B48" s="146"/>
+      <c r="C48" s="146"/>
+      <c r="D48" s="146"/>
+      <c r="E48" s="146"/>
+      <c r="F48" s="146"/>
+      <c r="G48" s="146"/>
       <c r="M48" s="54"/>
       <c r="N48" s="54"/>
     </row>
@@ -2945,27 +2946,27 @@
       <c r="N49" s="54"/>
     </row>
     <row r="50" spans="1:14" s="6" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A50" s="139" t="s">
-        <v>54</v>
-      </c>
-      <c r="B50" s="139"/>
-      <c r="C50" s="139"/>
-      <c r="D50" s="139"/>
-      <c r="E50" s="139"/>
-      <c r="F50" s="139"/>
-      <c r="G50" s="139"/>
+      <c r="A50" s="129" t="s">
+        <v>53</v>
+      </c>
+      <c r="B50" s="129"/>
+      <c r="C50" s="129"/>
+      <c r="D50" s="129"/>
+      <c r="E50" s="129"/>
+      <c r="F50" s="129"/>
+      <c r="G50" s="129"/>
       <c r="M50" s="54"/>
       <c r="N50" s="54"/>
     </row>
     <row r="51" spans="1:14" s="6" customFormat="1" ht="19.5" customHeight="1">
       <c r="A51" s="39" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B51" s="39"/>
       <c r="C51" s="39"/>
       <c r="D51" s="39"/>
       <c r="E51" s="39" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F51" s="39"/>
       <c r="G51" s="39"/>
@@ -2990,25 +2991,40 @@
     </row>
     <row r="53" spans="1:14">
       <c r="A53" s="36" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C53" s="43"/>
       <c r="D53" s="2"/>
       <c r="E53" s="36" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G53" s="44"/>
     </row>
     <row r="54" spans="1:14">
       <c r="A54" s="36" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E54" s="36" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A22:G22"/>
     <mergeCell ref="A50:G50"/>
     <mergeCell ref="E19:E20"/>
     <mergeCell ref="F19:F20"/>
@@ -3025,21 +3041,6 @@
     <mergeCell ref="A37:G37"/>
     <mergeCell ref="A40:G40"/>
     <mergeCell ref="A41:G41"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B8:G8"/>
-    <mergeCell ref="A10:G10"/>
   </mergeCells>
   <phoneticPr fontId="26" type="noConversion"/>
   <printOptions horizontalCentered="1"/>

--- a/excel-template/PO-template.xlsx
+++ b/excel-template/PO-template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\exportcrm\excel-template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17B1CD13-4059-4C12-8137-114EEB609417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E8449A2-FE2E-48F5-9F81-D763FA073DAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="813" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1164" yWindow="3648" windowWidth="17280" windowHeight="8880" tabRatio="813" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PO" sheetId="10" r:id="rId1"/>
@@ -263,18 +263,6 @@
   </si>
   <si>
     <t>零件号</t>
-    <phoneticPr fontId="26" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="DengXian"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>合计</t>
-    </r>
     <phoneticPr fontId="26" type="noConversion"/>
   </si>
   <si>
@@ -435,21 +423,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">13% </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="DengXian"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>增值税</t>
-    </r>
-    <phoneticPr fontId="26" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <rPr>
         <sz val="10"/>
         <rFont val="DengXian"/>
@@ -461,15 +434,51 @@
     <phoneticPr fontId="26" type="noConversion"/>
   </si>
   <si>
-    <t>供应商：</t>
+    <t>VAT 91500109MADTT20C93</t>
     <phoneticPr fontId="26" type="noConversion"/>
   </si>
   <si>
-    <t>以上单价不含税，开票时付税金。</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="DengXian"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>以上单价不含税，开票时付税金。</t>
+    </r>
     <phoneticPr fontId="26" type="noConversion"/>
   </si>
   <si>
-    <t>VAT 91500109MADTT20C93</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="DengXian"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>供应商：</t>
+    </r>
+    <phoneticPr fontId="26" type="noConversion"/>
+  </si>
+  <si>
+    <t>合计</t>
+    <phoneticPr fontId="26" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">13% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="DengXian"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>增值税</t>
+    </r>
     <phoneticPr fontId="26" type="noConversion"/>
   </si>
 </sst>
@@ -491,7 +500,7 @@
     <numFmt numFmtId="185" formatCode="_ * #,##0.00000_ ;_ * \-#,##0.00000_ ;_ * &quot;-&quot;??.000_ ;_ @_ "/>
     <numFmt numFmtId="186" formatCode="[$¥-804]#,##0.00"/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="38">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -708,6 +717,17 @@
     <font>
       <b/>
       <sz val="12"/>
+      <name val="DengXian"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="DengXian"/>
       <family val="2"/>
       <charset val="134"/>
@@ -913,7 +933,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="159">
+  <cellXfs count="161">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1241,9 +1261,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1256,29 +1273,8 @@
     <xf numFmtId="186" fontId="34" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="32" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="15" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1287,11 +1283,68 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="43" fontId="19" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="178" fontId="16" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="32" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="15" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1350,38 +1403,11 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="36" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1418,13 +1444,13 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>33617</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>100852</xdr:rowOff>
+      <xdr:rowOff>123712</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1516474</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>616324</xdr:rowOff>
+      <xdr:rowOff>639184</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1454,8 +1480,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="33617" y="100852"/>
-          <a:ext cx="3482693" cy="515472"/>
+          <a:off x="33617" y="123712"/>
+          <a:ext cx="3288797" cy="515472"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1752,32 +1778,32 @@
   <sheetData>
     <row r="1" spans="1:20" s="55" customFormat="1" ht="66" customHeight="1">
       <c r="A1" s="68" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B1" s="68"/>
       <c r="C1" s="68"/>
       <c r="D1" s="68"/>
       <c r="E1" s="68"/>
       <c r="F1" s="68"/>
-      <c r="G1" s="116" t="s">
-        <v>71</v>
-      </c>
-      <c r="H1" s="116"/>
-      <c r="I1" s="116"/>
+      <c r="G1" s="122" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
       <c r="O1" s="88"/>
       <c r="P1" s="88"/>
     </row>
     <row r="2" spans="1:20" ht="26.25" customHeight="1">
       <c r="A2" s="69" t="s">
-        <v>76</v>
-      </c>
-      <c r="H2" s="117" t="s">
+        <v>72</v>
+      </c>
+      <c r="H2" s="123" t="s">
         <v>58</v>
       </c>
-      <c r="I2" s="117"/>
+      <c r="I2" s="123"/>
     </row>
     <row r="3" spans="1:20" s="56" customFormat="1" ht="21.75" customHeight="1">
-      <c r="A3" s="112" t="s">
+      <c r="A3" s="111" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="70"/>
@@ -1787,9 +1813,9 @@
       <c r="F3" s="58"/>
       <c r="G3" s="58"/>
       <c r="H3" s="106" t="s">
-        <v>63</v>
-      </c>
-      <c r="I3" s="113" t="s">
+        <v>62</v>
+      </c>
+      <c r="I3" s="112" t="s">
         <v>58</v>
       </c>
       <c r="O3" s="71"/>
@@ -1810,7 +1836,7 @@
       <c r="R4" s="77"/>
     </row>
     <row r="5" spans="1:20" s="57" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A5" s="111" t="s">
+      <c r="A5" s="115" t="s">
         <v>74</v>
       </c>
       <c r="C5" s="72"/>
@@ -1874,41 +1900,41 @@
       <c r="A8" s="98" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="118" t="s">
+      <c r="B8" s="124" t="s">
         <v>60</v>
       </c>
-      <c r="C8" s="119"/>
+      <c r="C8" s="125"/>
       <c r="D8" s="82" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="82" t="s">
         <v>64</v>
       </c>
-      <c r="E8" s="82" t="s">
+      <c r="F8" s="82" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="82" t="s">
+      <c r="G8" s="82" t="s">
         <v>66</v>
       </c>
-      <c r="G8" s="82" t="s">
+      <c r="H8" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="H8" s="82" t="s">
+      <c r="I8" s="82" t="s">
         <v>68</v>
       </c>
-      <c r="I8" s="82" t="s">
-        <v>69</v>
-      </c>
-      <c r="M8" s="127"/>
-      <c r="N8" s="127"/>
-      <c r="O8" s="127"/>
-      <c r="P8" s="127"/>
-      <c r="Q8" s="127"/>
-      <c r="R8" s="127"/>
-      <c r="S8" s="127"/>
-      <c r="T8" s="127"/>
+      <c r="M8" s="120"/>
+      <c r="N8" s="120"/>
+      <c r="O8" s="120"/>
+      <c r="P8" s="120"/>
+      <c r="Q8" s="120"/>
+      <c r="R8" s="120"/>
+      <c r="S8" s="120"/>
+      <c r="T8" s="120"/>
     </row>
     <row r="9" spans="1:20" s="58" customFormat="1" ht="24.9" customHeight="1">
       <c r="A9" s="99"/>
-      <c r="B9" s="128"/>
-      <c r="C9" s="128"/>
+      <c r="B9" s="121"/>
+      <c r="C9" s="121"/>
       <c r="D9" s="99"/>
       <c r="E9" s="99"/>
       <c r="F9" s="101"/>
@@ -1923,8 +1949,8 @@
     </row>
     <row r="10" spans="1:20" s="58" customFormat="1" ht="24.9" customHeight="1">
       <c r="A10" s="99"/>
-      <c r="B10" s="128"/>
-      <c r="C10" s="128"/>
+      <c r="B10" s="121"/>
+      <c r="C10" s="121"/>
       <c r="D10" s="99"/>
       <c r="E10" s="99"/>
       <c r="F10" s="101"/>
@@ -1939,8 +1965,8 @@
     </row>
     <row r="11" spans="1:20" s="58" customFormat="1" ht="24.9" customHeight="1">
       <c r="A11" s="99"/>
-      <c r="B11" s="128"/>
-      <c r="C11" s="128"/>
+      <c r="B11" s="121"/>
+      <c r="C11" s="121"/>
       <c r="D11" s="105"/>
       <c r="E11" s="99"/>
       <c r="F11" s="101"/>
@@ -1955,8 +1981,8 @@
     </row>
     <row r="12" spans="1:20" s="58" customFormat="1" ht="24.9" customHeight="1">
       <c r="A12" s="99"/>
-      <c r="B12" s="128"/>
-      <c r="C12" s="128"/>
+      <c r="B12" s="121"/>
+      <c r="C12" s="121"/>
       <c r="D12" s="105"/>
       <c r="E12" s="100"/>
       <c r="F12" s="101"/>
@@ -1971,14 +1997,14 @@
     </row>
     <row r="13" spans="1:20" s="58" customFormat="1" ht="24.9" customHeight="1">
       <c r="A13" s="99"/>
-      <c r="B13" s="128"/>
-      <c r="C13" s="128"/>
+      <c r="B13" s="121"/>
+      <c r="C13" s="121"/>
       <c r="D13" s="105"/>
       <c r="E13" s="100"/>
       <c r="F13" s="101"/>
       <c r="G13" s="101"/>
       <c r="H13" s="103" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I13" s="102">
         <f>SUM(I9:I12)</f>
@@ -1992,14 +2018,14 @@
     </row>
     <row r="14" spans="1:20" s="58" customFormat="1" ht="24.9" customHeight="1">
       <c r="A14" s="99"/>
-      <c r="B14" s="128"/>
-      <c r="C14" s="128"/>
+      <c r="B14" s="121"/>
+      <c r="C14" s="121"/>
       <c r="D14" s="105"/>
       <c r="E14" s="100"/>
       <c r="F14" s="101"/>
       <c r="G14" s="101"/>
-      <c r="H14" s="103" t="s">
-        <v>72</v>
+      <c r="H14" s="160" t="s">
+        <v>76</v>
       </c>
       <c r="I14" s="102">
         <f>I13*0.13</f>
@@ -2027,41 +2053,41 @@
         <v>13</v>
       </c>
       <c r="G15" s="104"/>
-      <c r="H15" s="110" t="s">
-        <v>61</v>
-      </c>
-      <c r="I15" s="115">
+      <c r="H15" s="159" t="s">
+        <v>75</v>
+      </c>
+      <c r="I15" s="114">
         <f>I14+I13</f>
         <v>0</v>
       </c>
       <c r="J15" s="83"/>
     </row>
     <row r="16" spans="1:20" s="60" customFormat="1" ht="30" customHeight="1">
-      <c r="A16" s="122" t="s">
-        <v>70</v>
-      </c>
-      <c r="B16" s="122"/>
-      <c r="C16" s="122"/>
-      <c r="D16" s="122"/>
-      <c r="E16" s="122"/>
-      <c r="F16" s="122"/>
-      <c r="G16" s="122"/>
-      <c r="H16" s="122"/>
-      <c r="I16" s="122"/>
+      <c r="A16" s="128" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" s="128"/>
+      <c r="C16" s="128"/>
+      <c r="D16" s="128"/>
+      <c r="E16" s="128"/>
+      <c r="F16" s="128"/>
+      <c r="G16" s="128"/>
+      <c r="H16" s="128"/>
+      <c r="I16" s="128"/>
       <c r="L16" s="95"/>
     </row>
     <row r="17" spans="1:20" s="106" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A17" s="123" t="s">
-        <v>75</v>
-      </c>
-      <c r="B17" s="120"/>
-      <c r="C17" s="120"/>
-      <c r="D17" s="120"/>
-      <c r="E17" s="120"/>
-      <c r="F17" s="120"/>
-      <c r="G17" s="120"/>
-      <c r="H17" s="120"/>
-      <c r="I17" s="120"/>
+      <c r="A17" s="126" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" s="126"/>
+      <c r="C17" s="126"/>
+      <c r="D17" s="126"/>
+      <c r="E17" s="126"/>
+      <c r="F17" s="126"/>
+      <c r="G17" s="126"/>
+      <c r="H17" s="126"/>
+      <c r="I17" s="126"/>
       <c r="L17" s="107"/>
       <c r="M17" s="108"/>
       <c r="N17" s="108"/>
@@ -2073,15 +2099,15 @@
       <c r="T17" s="108"/>
     </row>
     <row r="18" spans="1:20" s="106" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A18" s="123"/>
-      <c r="B18" s="123"/>
-      <c r="C18" s="123"/>
-      <c r="D18" s="123"/>
-      <c r="E18" s="123"/>
-      <c r="F18" s="123"/>
-      <c r="G18" s="123"/>
-      <c r="H18" s="123"/>
-      <c r="I18" s="123"/>
+      <c r="A18" s="119"/>
+      <c r="B18" s="119"/>
+      <c r="C18" s="119"/>
+      <c r="D18" s="119"/>
+      <c r="E18" s="119"/>
+      <c r="F18" s="119"/>
+      <c r="G18" s="119"/>
+      <c r="H18" s="119"/>
+      <c r="I18" s="119"/>
       <c r="L18" s="107"/>
       <c r="M18" s="108"/>
       <c r="N18" s="108"/>
@@ -2093,26 +2119,26 @@
       <c r="T18" s="108"/>
     </row>
     <row r="19" spans="1:20" s="108" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A19" s="120"/>
-      <c r="B19" s="120"/>
-      <c r="C19" s="120"/>
-      <c r="D19" s="120"/>
-      <c r="E19" s="120"/>
-      <c r="F19" s="120"/>
-      <c r="G19" s="120"/>
-      <c r="H19" s="120"/>
-      <c r="I19" s="120"/>
+      <c r="A19" s="126"/>
+      <c r="B19" s="126"/>
+      <c r="C19" s="126"/>
+      <c r="D19" s="126"/>
+      <c r="E19" s="126"/>
+      <c r="F19" s="126"/>
+      <c r="G19" s="126"/>
+      <c r="H19" s="126"/>
+      <c r="I19" s="126"/>
     </row>
     <row r="20" spans="1:20" s="108" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A20" s="120"/>
-      <c r="B20" s="120"/>
-      <c r="C20" s="120"/>
-      <c r="D20" s="120"/>
-      <c r="E20" s="120"/>
-      <c r="F20" s="120"/>
-      <c r="G20" s="120"/>
-      <c r="H20" s="120"/>
-      <c r="I20" s="120"/>
+      <c r="A20" s="126"/>
+      <c r="B20" s="126"/>
+      <c r="C20" s="126"/>
+      <c r="D20" s="126"/>
+      <c r="E20" s="126"/>
+      <c r="F20" s="126"/>
+      <c r="G20" s="126"/>
+      <c r="H20" s="126"/>
+      <c r="I20" s="126"/>
       <c r="M20" s="106"/>
       <c r="N20" s="106"/>
       <c r="O20" s="106"/>
@@ -2123,58 +2149,58 @@
       <c r="T20" s="106"/>
     </row>
     <row r="21" spans="1:20" s="106" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A21" s="120"/>
-      <c r="B21" s="120"/>
-      <c r="C21" s="120"/>
-      <c r="D21" s="120"/>
-      <c r="E21" s="120"/>
-      <c r="F21" s="120"/>
-      <c r="G21" s="120"/>
-      <c r="H21" s="120"/>
-      <c r="I21" s="120"/>
+      <c r="A21" s="126"/>
+      <c r="B21" s="126"/>
+      <c r="C21" s="126"/>
+      <c r="D21" s="126"/>
+      <c r="E21" s="126"/>
+      <c r="F21" s="126"/>
+      <c r="G21" s="126"/>
+      <c r="H21" s="126"/>
+      <c r="I21" s="126"/>
       <c r="L21" s="107"/>
     </row>
     <row r="22" spans="1:20" s="106" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A22" s="121" t="s">
+      <c r="A22" s="127" t="s">
         <v>58</v>
       </c>
-      <c r="B22" s="121"/>
-      <c r="C22" s="121"/>
-      <c r="D22" s="121"/>
-      <c r="E22" s="121"/>
-      <c r="F22" s="121"/>
-      <c r="G22" s="121"/>
-      <c r="H22" s="121"/>
-      <c r="I22" s="121"/>
+      <c r="B22" s="127"/>
+      <c r="C22" s="127"/>
+      <c r="D22" s="127"/>
+      <c r="E22" s="127"/>
+      <c r="F22" s="127"/>
+      <c r="G22" s="127"/>
+      <c r="H22" s="127"/>
+      <c r="I22" s="127"/>
       <c r="L22" s="107"/>
     </row>
     <row r="23" spans="1:20" s="62" customFormat="1" ht="24" customHeight="1">
-      <c r="A23" s="124"/>
-      <c r="B23" s="124"/>
-      <c r="C23" s="124"/>
-      <c r="D23" s="124"/>
-      <c r="E23" s="124"/>
-      <c r="F23" s="124"/>
-      <c r="G23" s="124"/>
-      <c r="H23" s="124"/>
-      <c r="I23" s="124"/>
-      <c r="J23" s="114"/>
-      <c r="K23" s="114"/>
+      <c r="A23" s="116"/>
+      <c r="B23" s="116"/>
+      <c r="C23" s="116"/>
+      <c r="D23" s="116"/>
+      <c r="E23" s="116"/>
+      <c r="F23" s="116"/>
+      <c r="G23" s="116"/>
+      <c r="H23" s="116"/>
+      <c r="I23" s="116"/>
+      <c r="J23" s="113"/>
+      <c r="K23" s="113"/>
       <c r="O23" s="96"/>
       <c r="P23" s="96"/>
     </row>
     <row r="24" spans="1:20" s="62" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A24" s="125"/>
-      <c r="B24" s="125"/>
-      <c r="C24" s="125"/>
-      <c r="D24" s="125"/>
-      <c r="E24" s="125"/>
-      <c r="F24" s="125"/>
-      <c r="G24" s="125"/>
-      <c r="H24" s="125"/>
-      <c r="I24" s="125"/>
-      <c r="J24" s="114"/>
-      <c r="K24" s="114"/>
+      <c r="A24" s="117"/>
+      <c r="B24" s="117"/>
+      <c r="C24" s="117"/>
+      <c r="D24" s="117"/>
+      <c r="E24" s="117"/>
+      <c r="F24" s="117"/>
+      <c r="G24" s="117"/>
+      <c r="H24" s="117"/>
+      <c r="I24" s="117"/>
+      <c r="J24" s="113"/>
+      <c r="K24" s="113"/>
       <c r="M24" s="64"/>
       <c r="N24" s="64"/>
       <c r="O24" s="67"/>
@@ -2185,15 +2211,15 @@
       <c r="T24" s="64"/>
     </row>
     <row r="25" spans="1:20">
-      <c r="A25" s="126"/>
-      <c r="B25" s="126"/>
-      <c r="C25" s="126"/>
-      <c r="D25" s="126"/>
-      <c r="E25" s="126"/>
-      <c r="F25" s="126"/>
-      <c r="G25" s="126"/>
-      <c r="H25" s="126"/>
-      <c r="I25" s="126"/>
+      <c r="A25" s="118"/>
+      <c r="B25" s="118"/>
+      <c r="C25" s="118"/>
+      <c r="D25" s="118"/>
+      <c r="E25" s="118"/>
+      <c r="F25" s="118"/>
+      <c r="G25" s="118"/>
+      <c r="H25" s="118"/>
+      <c r="I25" s="118"/>
     </row>
     <row r="26" spans="1:20">
       <c r="A26" s="85"/>
@@ -2224,6 +2250,15 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A16:I16"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A20:I20"/>
     <mergeCell ref="A23:I23"/>
     <mergeCell ref="A24:I24"/>
     <mergeCell ref="A25:I25"/>
@@ -2235,15 +2270,6 @@
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="A21:I21"/>
-    <mergeCell ref="A22:I22"/>
-    <mergeCell ref="A16:I16"/>
-    <mergeCell ref="A17:I17"/>
-    <mergeCell ref="A19:I19"/>
-    <mergeCell ref="A20:I20"/>
   </mergeCells>
   <phoneticPr fontId="26" type="noConversion"/>
   <hyperlinks>
@@ -2281,15 +2307,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A1" s="154" t="s">
+      <c r="A1" s="129" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="154"/>
-      <c r="C1" s="154"/>
-      <c r="D1" s="154"/>
-      <c r="E1" s="154"/>
-      <c r="F1" s="154"/>
-      <c r="G1" s="154"/>
+      <c r="B1" s="129"/>
+      <c r="C1" s="129"/>
+      <c r="D1" s="129"/>
+      <c r="E1" s="129"/>
+      <c r="F1" s="129"/>
+      <c r="G1" s="129"/>
       <c r="M1" s="45"/>
       <c r="N1" s="45"/>
     </row>
@@ -2327,14 +2353,14 @@
     </row>
     <row r="5" spans="1:15" s="2" customFormat="1" ht="33" customHeight="1">
       <c r="A5" s="17"/>
-      <c r="B5" s="155" t="s">
+      <c r="B5" s="130" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="155"/>
-      <c r="D5" s="155"/>
-      <c r="E5" s="155"/>
-      <c r="F5" s="155"/>
-      <c r="G5" s="155"/>
+      <c r="C5" s="130"/>
+      <c r="D5" s="130"/>
+      <c r="E5" s="130"/>
+      <c r="F5" s="130"/>
+      <c r="G5" s="130"/>
       <c r="H5" s="18"/>
       <c r="M5" s="46"/>
       <c r="N5" s="46"/>
@@ -2354,27 +2380,27 @@
       <c r="A7" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="156" t="s">
+      <c r="B7" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="156"/>
-      <c r="D7" s="156"/>
-      <c r="E7" s="156"/>
-      <c r="F7" s="156"/>
+      <c r="C7" s="131"/>
+      <c r="D7" s="131"/>
+      <c r="E7" s="131"/>
+      <c r="F7" s="131"/>
       <c r="G7" s="20"/>
       <c r="M7" s="46"/>
       <c r="N7" s="46"/>
     </row>
     <row r="8" spans="1:15" s="2" customFormat="1" ht="54" customHeight="1">
       <c r="A8" s="17"/>
-      <c r="B8" s="157" t="s">
+      <c r="B8" s="132" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="157"/>
-      <c r="D8" s="157"/>
-      <c r="E8" s="157"/>
-      <c r="F8" s="157"/>
-      <c r="G8" s="157"/>
+      <c r="C8" s="132"/>
+      <c r="D8" s="132"/>
+      <c r="E8" s="132"/>
+      <c r="F8" s="132"/>
+      <c r="G8" s="132"/>
       <c r="M8" s="46"/>
       <c r="N8" s="46"/>
     </row>
@@ -2390,28 +2416,28 @@
       <c r="N9" s="46"/>
     </row>
     <row r="10" spans="1:15" s="3" customFormat="1" ht="49.5" customHeight="1">
-      <c r="A10" s="158" t="s">
+      <c r="A10" s="133" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="158"/>
-      <c r="C10" s="158"/>
-      <c r="D10" s="158"/>
-      <c r="E10" s="158"/>
-      <c r="F10" s="158"/>
-      <c r="G10" s="158"/>
+      <c r="B10" s="133"/>
+      <c r="C10" s="133"/>
+      <c r="D10" s="133"/>
+      <c r="E10" s="133"/>
+      <c r="F10" s="133"/>
+      <c r="G10" s="133"/>
       <c r="M10" s="4"/>
       <c r="N10" s="4"/>
     </row>
     <row r="11" spans="1:15" s="3" customFormat="1" ht="27" customHeight="1">
-      <c r="A11" s="151" t="s">
+      <c r="A11" s="134" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="151"/>
-      <c r="C11" s="151"/>
-      <c r="D11" s="151"/>
-      <c r="E11" s="151"/>
-      <c r="F11" s="151"/>
-      <c r="G11" s="151"/>
+      <c r="B11" s="134"/>
+      <c r="C11" s="134"/>
+      <c r="D11" s="134"/>
+      <c r="E11" s="134"/>
+      <c r="F11" s="134"/>
+      <c r="G11" s="134"/>
       <c r="M11" s="4"/>
       <c r="N11" s="4"/>
     </row>
@@ -2419,10 +2445,10 @@
       <c r="A12" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="152" t="s">
+      <c r="B12" s="135" t="s">
         <v>3</v>
       </c>
-      <c r="C12" s="153"/>
+      <c r="C12" s="136"/>
       <c r="D12" s="23" t="s">
         <v>4</v>
       </c>
@@ -2438,16 +2464,16 @@
       <c r="L12" s="47"/>
       <c r="M12" s="48"/>
       <c r="N12" s="49"/>
-      <c r="O12" s="136"/>
+      <c r="O12" s="147"/>
     </row>
     <row r="13" spans="1:15" s="3" customFormat="1" ht="18" customHeight="1">
       <c r="A13" s="25">
         <v>1</v>
       </c>
-      <c r="B13" s="148">
+      <c r="B13" s="137">
         <v>50655</v>
       </c>
-      <c r="C13" s="149"/>
+      <c r="C13" s="138"/>
       <c r="D13" s="26" t="s">
         <v>6</v>
       </c>
@@ -2464,16 +2490,16 @@
       <c r="J13" s="51"/>
       <c r="M13" s="4"/>
       <c r="N13" s="4"/>
-      <c r="O13" s="136"/>
+      <c r="O13" s="147"/>
     </row>
     <row r="14" spans="1:15" s="3" customFormat="1" ht="18" customHeight="1">
       <c r="A14" s="25">
         <v>2</v>
       </c>
-      <c r="B14" s="148">
+      <c r="B14" s="137">
         <v>50755</v>
       </c>
-      <c r="C14" s="149"/>
+      <c r="C14" s="138"/>
       <c r="D14" s="26" t="s">
         <v>7</v>
       </c>
@@ -2496,10 +2522,10 @@
       <c r="A15" s="25">
         <v>3</v>
       </c>
-      <c r="B15" s="148">
+      <c r="B15" s="137">
         <v>50665</v>
       </c>
-      <c r="C15" s="149"/>
+      <c r="C15" s="138"/>
       <c r="D15" s="26" t="s">
         <v>8</v>
       </c>
@@ -2522,10 +2548,10 @@
       <c r="A16" s="25">
         <v>4</v>
       </c>
-      <c r="B16" s="148">
+      <c r="B16" s="137">
         <v>50765</v>
       </c>
-      <c r="C16" s="149"/>
+      <c r="C16" s="138"/>
       <c r="D16" s="26" t="s">
         <v>9</v>
       </c>
@@ -2548,10 +2574,10 @@
       <c r="A17" s="25">
         <v>5</v>
       </c>
-      <c r="B17" s="148">
+      <c r="B17" s="137">
         <v>50720</v>
       </c>
-      <c r="C17" s="149"/>
+      <c r="C17" s="138"/>
       <c r="D17" s="26" t="s">
         <v>10</v>
       </c>
@@ -2574,10 +2600,10 @@
       <c r="A18" s="30">
         <v>6</v>
       </c>
-      <c r="B18" s="148">
+      <c r="B18" s="137">
         <v>50730</v>
       </c>
-      <c r="C18" s="149"/>
+      <c r="C18" s="138"/>
       <c r="D18" s="31" t="s">
         <v>11</v>
       </c>
@@ -2597,54 +2623,54 @@
       <c r="O18" s="50"/>
     </row>
     <row r="19" spans="1:15" s="4" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A19" s="137" t="s">
+      <c r="A19" s="148" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="138"/>
-      <c r="C19" s="139"/>
+      <c r="B19" s="149"/>
+      <c r="C19" s="150"/>
       <c r="D19" s="32"/>
-      <c r="E19" s="130">
+      <c r="E19" s="141">
         <f>SUM(E13:E18)</f>
         <v>6000</v>
       </c>
-      <c r="F19" s="132"/>
-      <c r="G19" s="134">
+      <c r="F19" s="143"/>
+      <c r="G19" s="145">
         <f>SUM(G13:G18)</f>
         <v>73120</v>
       </c>
       <c r="H19" s="33"/>
     </row>
     <row r="20" spans="1:15" s="4" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A20" s="140"/>
-      <c r="B20" s="141"/>
-      <c r="C20" s="142"/>
+      <c r="A20" s="151"/>
+      <c r="B20" s="152"/>
+      <c r="C20" s="153"/>
       <c r="D20" s="34"/>
-      <c r="E20" s="131"/>
-      <c r="F20" s="133"/>
-      <c r="G20" s="135"/>
+      <c r="E20" s="142"/>
+      <c r="F20" s="144"/>
+      <c r="G20" s="146"/>
     </row>
     <row r="21" spans="1:15" s="4" customFormat="1" ht="30" hidden="1" customHeight="1">
-      <c r="A21" s="150" t="s">
+      <c r="A21" s="139" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="150"/>
-      <c r="C21" s="150"/>
-      <c r="D21" s="150"/>
-      <c r="E21" s="150"/>
-      <c r="F21" s="150"/>
-      <c r="G21" s="150"/>
+      <c r="B21" s="139"/>
+      <c r="C21" s="139"/>
+      <c r="D21" s="139"/>
+      <c r="E21" s="139"/>
+      <c r="F21" s="139"/>
+      <c r="G21" s="139"/>
       <c r="J21" s="52"/>
     </row>
     <row r="22" spans="1:15" s="4" customFormat="1" ht="30" customHeight="1">
-      <c r="A22" s="129" t="s">
+      <c r="A22" s="140" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="129"/>
-      <c r="C22" s="129"/>
-      <c r="D22" s="129"/>
-      <c r="E22" s="129"/>
-      <c r="F22" s="129"/>
-      <c r="G22" s="129"/>
+      <c r="B22" s="140"/>
+      <c r="C22" s="140"/>
+      <c r="D22" s="140"/>
+      <c r="E22" s="140"/>
+      <c r="F22" s="140"/>
+      <c r="G22" s="140"/>
       <c r="J22" s="52"/>
     </row>
     <row r="23" spans="1:15" s="4" customFormat="1" ht="21.75" customHeight="1">
@@ -2694,15 +2720,15 @@
       <c r="J26" s="52"/>
     </row>
     <row r="27" spans="1:15" s="4" customFormat="1" ht="30" customHeight="1">
-      <c r="A27" s="129" t="s">
+      <c r="A27" s="140" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="129"/>
-      <c r="C27" s="129"/>
-      <c r="D27" s="129"/>
-      <c r="E27" s="129"/>
-      <c r="F27" s="129"/>
-      <c r="G27" s="129"/>
+      <c r="B27" s="140"/>
+      <c r="C27" s="140"/>
+      <c r="D27" s="140"/>
+      <c r="E27" s="140"/>
+      <c r="F27" s="140"/>
+      <c r="G27" s="140"/>
       <c r="J27" s="52"/>
     </row>
     <row r="28" spans="1:15" s="5" customFormat="1" ht="19.5" customHeight="1">
@@ -2766,15 +2792,15 @@
       <c r="N33" s="54"/>
     </row>
     <row r="34" spans="1:14" s="4" customFormat="1" ht="30" customHeight="1">
-      <c r="A34" s="129" t="s">
+      <c r="A34" s="140" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="129"/>
-      <c r="C34" s="129"/>
-      <c r="D34" s="129"/>
-      <c r="E34" s="129"/>
-      <c r="F34" s="129"/>
-      <c r="G34" s="129"/>
+      <c r="B34" s="140"/>
+      <c r="C34" s="140"/>
+      <c r="D34" s="140"/>
+      <c r="E34" s="140"/>
+      <c r="F34" s="140"/>
+      <c r="G34" s="140"/>
       <c r="J34" s="52"/>
     </row>
     <row r="35" spans="1:14" s="5" customFormat="1" ht="19.5" customHeight="1">
@@ -2798,15 +2824,15 @@
       <c r="N36" s="53"/>
     </row>
     <row r="37" spans="1:14" s="4" customFormat="1" ht="30" customHeight="1">
-      <c r="A37" s="129" t="s">
+      <c r="A37" s="140" t="s">
         <v>43</v>
       </c>
-      <c r="B37" s="129"/>
-      <c r="C37" s="129"/>
-      <c r="D37" s="129"/>
-      <c r="E37" s="129"/>
-      <c r="F37" s="129"/>
-      <c r="G37" s="129"/>
+      <c r="B37" s="140"/>
+      <c r="C37" s="140"/>
+      <c r="D37" s="140"/>
+      <c r="E37" s="140"/>
+      <c r="F37" s="140"/>
+      <c r="G37" s="140"/>
       <c r="J37" s="52"/>
     </row>
     <row r="38" spans="1:14" s="6" customFormat="1" ht="19.5" customHeight="1">
@@ -2830,40 +2856,40 @@
       <c r="N39" s="54"/>
     </row>
     <row r="40" spans="1:14" s="4" customFormat="1" ht="30" customHeight="1">
-      <c r="A40" s="129" t="s">
+      <c r="A40" s="140" t="s">
         <v>46</v>
       </c>
-      <c r="B40" s="129"/>
-      <c r="C40" s="129"/>
-      <c r="D40" s="129"/>
-      <c r="E40" s="129"/>
-      <c r="F40" s="129"/>
-      <c r="G40" s="129"/>
+      <c r="B40" s="140"/>
+      <c r="C40" s="140"/>
+      <c r="D40" s="140"/>
+      <c r="E40" s="140"/>
+      <c r="F40" s="140"/>
+      <c r="G40" s="140"/>
       <c r="J40" s="52"/>
     </row>
     <row r="41" spans="1:14" s="6" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A41" s="147" t="s">
+      <c r="A41" s="158" t="s">
         <v>47</v>
       </c>
-      <c r="B41" s="147"/>
-      <c r="C41" s="147"/>
-      <c r="D41" s="147"/>
-      <c r="E41" s="147"/>
-      <c r="F41" s="147"/>
-      <c r="G41" s="147"/>
+      <c r="B41" s="158"/>
+      <c r="C41" s="158"/>
+      <c r="D41" s="158"/>
+      <c r="E41" s="158"/>
+      <c r="F41" s="158"/>
+      <c r="G41" s="158"/>
       <c r="M41" s="54"/>
       <c r="N41" s="54"/>
     </row>
     <row r="42" spans="1:14" s="6" customFormat="1" ht="44.25" customHeight="1">
-      <c r="A42" s="143" t="s">
+      <c r="A42" s="154" t="s">
         <v>48</v>
       </c>
-      <c r="B42" s="143"/>
-      <c r="C42" s="143"/>
-      <c r="D42" s="143"/>
-      <c r="E42" s="143"/>
-      <c r="F42" s="143"/>
-      <c r="G42" s="143"/>
+      <c r="B42" s="154"/>
+      <c r="C42" s="154"/>
+      <c r="D42" s="154"/>
+      <c r="E42" s="154"/>
+      <c r="F42" s="154"/>
+      <c r="G42" s="154"/>
       <c r="M42" s="54"/>
       <c r="N42" s="54"/>
     </row>
@@ -2878,27 +2904,27 @@
       <c r="J43" s="52"/>
     </row>
     <row r="44" spans="1:14" s="4" customFormat="1" ht="30" customHeight="1">
-      <c r="A44" s="129" t="s">
+      <c r="A44" s="140" t="s">
         <v>49</v>
       </c>
-      <c r="B44" s="129"/>
-      <c r="C44" s="129"/>
-      <c r="D44" s="129"/>
-      <c r="E44" s="129"/>
-      <c r="F44" s="129"/>
-      <c r="G44" s="129"/>
+      <c r="B44" s="140"/>
+      <c r="C44" s="140"/>
+      <c r="D44" s="140"/>
+      <c r="E44" s="140"/>
+      <c r="F44" s="140"/>
+      <c r="G44" s="140"/>
       <c r="J44" s="52"/>
     </row>
     <row r="45" spans="1:14" s="6" customFormat="1" ht="58.5" customHeight="1">
-      <c r="A45" s="144" t="s">
+      <c r="A45" s="155" t="s">
         <v>50</v>
       </c>
-      <c r="B45" s="145"/>
-      <c r="C45" s="145"/>
-      <c r="D45" s="145"/>
-      <c r="E45" s="145"/>
-      <c r="F45" s="145"/>
-      <c r="G45" s="145"/>
+      <c r="B45" s="156"/>
+      <c r="C45" s="156"/>
+      <c r="D45" s="156"/>
+      <c r="E45" s="156"/>
+      <c r="F45" s="156"/>
+      <c r="G45" s="156"/>
       <c r="M45" s="54"/>
       <c r="N45" s="54"/>
     </row>
@@ -2913,27 +2939,27 @@
       <c r="J46" s="52"/>
     </row>
     <row r="47" spans="1:14" s="4" customFormat="1" ht="30" customHeight="1">
-      <c r="A47" s="129" t="s">
+      <c r="A47" s="140" t="s">
         <v>51</v>
       </c>
-      <c r="B47" s="129"/>
-      <c r="C47" s="129"/>
-      <c r="D47" s="129"/>
-      <c r="E47" s="129"/>
-      <c r="F47" s="129"/>
-      <c r="G47" s="129"/>
+      <c r="B47" s="140"/>
+      <c r="C47" s="140"/>
+      <c r="D47" s="140"/>
+      <c r="E47" s="140"/>
+      <c r="F47" s="140"/>
+      <c r="G47" s="140"/>
       <c r="J47" s="52"/>
     </row>
     <row r="48" spans="1:14" s="6" customFormat="1" ht="46.5" customHeight="1">
-      <c r="A48" s="146" t="s">
+      <c r="A48" s="157" t="s">
         <v>52</v>
       </c>
-      <c r="B48" s="146"/>
-      <c r="C48" s="146"/>
-      <c r="D48" s="146"/>
-      <c r="E48" s="146"/>
-      <c r="F48" s="146"/>
-      <c r="G48" s="146"/>
+      <c r="B48" s="157"/>
+      <c r="C48" s="157"/>
+      <c r="D48" s="157"/>
+      <c r="E48" s="157"/>
+      <c r="F48" s="157"/>
+      <c r="G48" s="157"/>
       <c r="M48" s="54"/>
       <c r="N48" s="54"/>
     </row>
@@ -2946,15 +2972,15 @@
       <c r="N49" s="54"/>
     </row>
     <row r="50" spans="1:14" s="6" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A50" s="129" t="s">
+      <c r="A50" s="140" t="s">
         <v>53</v>
       </c>
-      <c r="B50" s="129"/>
-      <c r="C50" s="129"/>
-      <c r="D50" s="129"/>
-      <c r="E50" s="129"/>
-      <c r="F50" s="129"/>
-      <c r="G50" s="129"/>
+      <c r="B50" s="140"/>
+      <c r="C50" s="140"/>
+      <c r="D50" s="140"/>
+      <c r="E50" s="140"/>
+      <c r="F50" s="140"/>
+      <c r="G50" s="140"/>
       <c r="M50" s="54"/>
       <c r="N50" s="54"/>
     </row>
@@ -3010,21 +3036,6 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B8:G8"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A22:G22"/>
     <mergeCell ref="A50:G50"/>
     <mergeCell ref="E19:E20"/>
     <mergeCell ref="F19:F20"/>
@@ -3041,6 +3052,21 @@
     <mergeCell ref="A37:G37"/>
     <mergeCell ref="A40:G40"/>
     <mergeCell ref="A41:G41"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="A10:G10"/>
   </mergeCells>
   <phoneticPr fontId="26" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
